--- a/e2e/testcases.xlsx
+++ b/e2e/testcases.xlsx
@@ -1034,21 +1034,21 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>未覆盖</t>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>未执行</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="n"/>
-      <c r="N8" s="2" t="n"/>
-      <c r="O8" s="2" t="n"/>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:06</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2112,21 +2112,21 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I26" s="6" t="inlineStr">
-        <is>
-          <t>未覆盖</t>
+      <c r="I26" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>未执行</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="n"/>
-      <c r="N26" s="2" t="n"/>
-      <c r="O26" s="2" t="n"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:06</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2169,21 +2169,21 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I27" s="6" t="inlineStr">
-        <is>
-          <t>未覆盖</t>
+      <c r="I27" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>未执行</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="n"/>
-      <c r="N27" s="2" t="n"/>
-      <c r="O27" s="2" t="n"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:06</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2226,21 +2226,21 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="I28" s="6" t="inlineStr">
-        <is>
-          <t>未覆盖</t>
+      <c r="I28" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>未执行</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="n"/>
-      <c r="N28" s="2" t="n"/>
-      <c r="O28" s="2" t="n"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:06</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2283,21 +2283,21 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="I29" s="6" t="inlineStr">
-        <is>
-          <t>未覆盖</t>
+      <c r="I29" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>未执行</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="n"/>
-      <c r="N29" s="2" t="n"/>
-      <c r="O29" s="2" t="n"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:06</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2464,21 +2464,21 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="I32" s="6" t="inlineStr">
-        <is>
-          <t>未覆盖</t>
+      <c r="I32" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>未执行</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="n"/>
-      <c r="N32" s="2" t="n"/>
-      <c r="O32" s="2" t="n"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:06</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2540,14 +2540,18 @@
           <t>当前只测按钮可见，未执行完整还原</t>
         </is>
       </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>未执行</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="n"/>
-      <c r="N33" s="2" t="n"/>
-      <c r="O33" s="2" t="n"/>
+      <c r="L33" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-04 16:46</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -3003,14 +3007,18 @@
           <t>当前已覆盖</t>
         </is>
       </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>未执行</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="n"/>
-      <c r="N41" s="2" t="n"/>
-      <c r="O41" s="2" t="n"/>
+      <c r="L41" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-04 16:46</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -3329,14 +3337,18 @@
           <t>test_desensitize_then_back_to_dropzone</t>
         </is>
       </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>未执行</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="n"/>
-      <c r="N47" s="2" t="n"/>
-      <c r="O47" s="2" t="n"/>
+      <c r="L47" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-04 16:46</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -6340,14 +6352,22 @@
           <t>i18n 测试</t>
         </is>
       </c>
-      <c r="L93" s="2" t="inlineStr">
-        <is>
-          <t>未执行</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="n"/>
-      <c r="N93" s="2" t="n"/>
-      <c r="O93" s="2" t="n"/>
+      <c r="L93" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>test_language_switch_to_english: strict mode violation, button EN 匹配到 4 个元素; test_sidebar_toggle: Page.goto timeout</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-04 16:46</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">

--- a/e2e/testcases.xlsx
+++ b/e2e/testcases.xlsx
@@ -2597,21 +2597,21 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I34" s="6" t="inlineStr">
-        <is>
-          <t>未覆盖</t>
+      <c r="I34" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>未执行</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="n"/>
-      <c r="N34" s="2" t="n"/>
-      <c r="O34" s="2" t="n"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:48</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2711,21 +2711,21 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="I36" s="6" t="inlineStr">
-        <is>
-          <t>未覆盖</t>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>部分覆盖</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>未执行</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="n"/>
-      <c r="N36" s="2" t="n"/>
-      <c r="O36" s="2" t="n"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:48</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -3163,21 +3163,21 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I44" s="6" t="inlineStr">
-        <is>
-          <t>未覆盖</t>
+      <c r="I44" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>未执行</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="n"/>
-      <c r="N44" s="2" t="n"/>
-      <c r="O44" s="2" t="n"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:48</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -3216,21 +3216,21 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="I45" s="6" t="inlineStr">
-        <is>
-          <t>未覆盖</t>
+      <c r="I45" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>未执行</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="n"/>
-      <c r="N45" s="2" t="n"/>
-      <c r="O45" s="2" t="n"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:48</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -7091,9 +7091,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I104" s="2" t="inlineStr">
-        <is>
-          <t>未覆盖</t>
+      <c r="I104" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr"/>
@@ -7102,14 +7102,14 @@
           <t>持久化: enabled_types 保存和恢复</t>
         </is>
       </c>
-      <c r="L104" s="2" t="inlineStr">
-        <is>
-          <t>未执行</t>
-        </is>
-      </c>
-      <c r="M104" s="2" t="n"/>
-      <c r="N104" s="2" t="n"/>
-      <c r="O104" s="2" t="n"/>
+      <c r="L104" s="2" t="inlineStr"/>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-04 17:48</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">

--- a/e2e/testcases.xlsx
+++ b/e2e/testcases.xlsx
@@ -2525,9 +2525,9 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I33" s="4" t="inlineStr">
-        <is>
-          <t>部分覆盖</t>
+      <c r="I33" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -2540,15 +2540,11 @@
           <t>当前只测按钮可见，未执行完整还原</t>
         </is>
       </c>
-      <c r="L33" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
+      <c r="L33" s="8" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr"/>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 16:46</t>
+          <t>2026-04-04 18:14</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr"/>
@@ -2711,9 +2707,9 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="I36" s="4" t="inlineStr">
-        <is>
-          <t>部分覆盖</t>
+      <c r="I36" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
@@ -2722,7 +2718,7 @@
       <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 17:48</t>
+          <t>2026-04-04 18:14</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr"/>
@@ -2992,9 +2988,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I41" s="4" t="inlineStr">
-        <is>
-          <t>部分覆盖</t>
+      <c r="I41" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -3007,15 +3003,11 @@
           <t>当前已覆盖</t>
         </is>
       </c>
-      <c r="L41" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
+      <c r="L41" s="8" t="inlineStr"/>
       <c r="M41" s="2" t="inlineStr"/>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 16:46</t>
+          <t>2026-04-04 18:14</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr"/>
@@ -3755,9 +3747,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I54" s="4" t="inlineStr">
-        <is>
-          <t>部分覆盖</t>
+      <c r="I54" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
@@ -3770,7 +3762,7 @@
       <c r="M54" s="2" t="inlineStr"/>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:12</t>
+          <t>2026-04-04 18:14</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr"/>
@@ -4196,9 +4188,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I61" s="4" t="inlineStr">
-        <is>
-          <t>部分覆盖</t>
+      <c r="I61" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
@@ -4211,7 +4203,7 @@
       <c r="M61" s="2" t="inlineStr"/>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:13</t>
+          <t>2026-04-04 18:14</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr"/>
@@ -4448,9 +4440,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I65" s="4" t="inlineStr">
-        <is>
-          <t>部分覆盖</t>
+      <c r="I65" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
@@ -4463,7 +4455,7 @@
       <c r="M65" s="2" t="inlineStr"/>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:13</t>
+          <t>2026-04-04 18:14</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr"/>
@@ -4965,9 +4957,9 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>部分覆盖</t>
+      <c r="I73" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -4980,15 +4972,11 @@
           <t>4个测试全部 #[ignore]，CSV 解析器暂不支持 GBK 编码</t>
         </is>
       </c>
-      <c r="L73" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
+      <c r="L73" s="8" t="inlineStr"/>
       <c r="M73" s="2" t="inlineStr"/>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:53</t>
+          <t>2026-04-04 18:14</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr"/>
@@ -6540,9 +6528,9 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I96" s="2" t="inlineStr">
-        <is>
-          <t>部分覆盖</t>
+      <c r="I96" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
@@ -6555,15 +6543,11 @@
           <t>UkPhone/UkPostcode/Email/IBAN 通过; CreditCard 带空格格式+DriversLicense+baseline 引擎暂不支持(ignore)</t>
         </is>
       </c>
-      <c r="L96" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
+      <c r="L96" s="8" t="inlineStr"/>
       <c r="M96" s="2" t="inlineStr"/>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:53</t>
+          <t>2026-04-04 18:14</t>
         </is>
       </c>
       <c r="O96" s="2" t="inlineStr"/>
@@ -6612,9 +6596,9 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I97" s="2" t="inlineStr">
-        <is>
-          <t>部分覆盖</t>
+      <c r="I97" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
@@ -6627,15 +6611,11 @@
           <t>SSN/UsPhone/ZipCode/Email 通过; DriversLicense+CreditCard 带空格格式+baseline 引擎暂不支持(ignore)</t>
         </is>
       </c>
-      <c r="L97" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
+      <c r="L97" s="8" t="inlineStr"/>
       <c r="M97" s="2" t="inlineStr"/>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:53</t>
+          <t>2026-04-04 18:14</t>
         </is>
       </c>
       <c r="O97" s="2" t="inlineStr"/>
@@ -6684,9 +6664,9 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I98" s="2" t="inlineStr">
-        <is>
-          <t>部分覆盖</t>
+      <c r="I98" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
@@ -6699,15 +6679,11 @@
           <t>IBAN(≥2)/UkPhone/Email/SSN/UsPhone 通过; CreditCard/Passport/DriversLicense+baseline 引擎暂不支持(ignore)</t>
         </is>
       </c>
-      <c r="L98" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
+      <c r="L98" s="8" t="inlineStr"/>
       <c r="M98" s="2" t="inlineStr"/>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:53</t>
+          <t>2026-04-04 18:14</t>
         </is>
       </c>
       <c r="O98" s="2" t="inlineStr"/>
@@ -6756,9 +6732,9 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I99" s="2" t="inlineStr">
-        <is>
-          <t>部分覆盖</t>
+      <c r="I99" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
@@ -6771,15 +6747,11 @@
           <t>IpAddress(IPv4≥14)/Phone/Email 通过; baseline 中 IPv6 引擎暂不支持(ignore)</t>
         </is>
       </c>
-      <c r="L99" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
+      <c r="L99" s="8" t="inlineStr"/>
       <c r="M99" s="2" t="inlineStr"/>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:53</t>
+          <t>2026-04-04 18:14</t>
         </is>
       </c>
       <c r="O99" s="2" t="inlineStr"/>
@@ -6828,9 +6800,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I100" s="2" t="inlineStr">
-        <is>
-          <t>部分覆盖</t>
+      <c r="I100" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -6843,15 +6815,11 @@
           <t>Phone/Email/IdCard 通过; Landline(400热线)+baseline 引擎暂不支持(ignore)</t>
         </is>
       </c>
-      <c r="L100" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
+      <c r="L100" s="8" t="inlineStr"/>
       <c r="M100" s="2" t="inlineStr"/>
       <c r="N100" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:53</t>
+          <t>2026-04-04 18:14</t>
         </is>
       </c>
       <c r="O100" s="2" t="inlineStr"/>

--- a/e2e/testcases.xlsx
+++ b/e2e/testcases.xlsx
@@ -2540,11 +2540,15 @@
           <t>当前只测按钮可见，未执行完整还原</t>
         </is>
       </c>
-      <c r="L33" s="8" t="inlineStr"/>
+      <c r="L33" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M33" s="2" t="inlineStr"/>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 18:14</t>
+          <t>2026-04-04 21:24</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr"/>
@@ -3003,11 +3007,15 @@
           <t>当前已覆盖</t>
         </is>
       </c>
-      <c r="L41" s="8" t="inlineStr"/>
+      <c r="L41" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M41" s="2" t="inlineStr"/>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 18:14</t>
+          <t>2026-04-04 21:24</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr"/>
@@ -3337,7 +3345,7 @@
       <c r="M47" s="2" t="inlineStr"/>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 16:46</t>
+          <t>2026-04-04 21:24</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr"/>
@@ -4817,7 +4825,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr">
+      <c r="I71" s="8" t="inlineStr">
         <is>
           <t>已覆盖</t>
         </is>
@@ -4840,7 +4848,7 @@
       <c r="M71" s="2" t="inlineStr"/>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:53</t>
+          <t>2026-04-04 21:24</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr"/>
@@ -4887,7 +4895,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr">
+      <c r="I72" s="8" t="inlineStr">
         <is>
           <t>已覆盖</t>
         </is>
@@ -4910,7 +4918,7 @@
       <c r="M72" s="2" t="inlineStr"/>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:53</t>
+          <t>2026-04-04 21:24</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr"/>
@@ -4972,11 +4980,19 @@
           <t>4个测试全部 #[ignore]，CSV 解析器暂不支持 GBK 编码</t>
         </is>
       </c>
-      <c r="L73" s="8" t="inlineStr"/>
-      <c r="M73" s="2" t="inlineStr"/>
+      <c r="L73" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>GBK CSV 解析失败: invalid utf-8</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 18:14</t>
+          <t>2026-04-04 21:24</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr"/>
@@ -5023,7 +5039,7 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr">
+      <c r="I74" s="8" t="inlineStr">
         <is>
           <t>已覆盖</t>
         </is>
@@ -5046,7 +5062,7 @@
       <c r="M74" s="2" t="inlineStr"/>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:53</t>
+          <t>2026-04-04 21:24</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr"/>
@@ -5093,7 +5109,7 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr">
+      <c r="I75" s="8" t="inlineStr">
         <is>
           <t>已覆盖</t>
         </is>
@@ -5116,7 +5132,7 @@
       <c r="M75" s="2" t="inlineStr"/>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:53</t>
+          <t>2026-04-04 21:24</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr"/>
@@ -5163,7 +5179,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr">
+      <c r="I76" s="8" t="inlineStr">
         <is>
           <t>已覆盖</t>
         </is>
@@ -5186,7 +5202,7 @@
       <c r="M76" s="2" t="inlineStr"/>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:53</t>
+          <t>2026-04-04 21:24</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr"/>
@@ -5233,7 +5249,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr">
+      <c r="I77" s="8" t="inlineStr">
         <is>
           <t>已覆盖</t>
         </is>
@@ -5256,7 +5272,7 @@
       <c r="M77" s="2" t="inlineStr"/>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:53</t>
+          <t>2026-04-04 21:24</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr"/>
@@ -5303,7 +5319,7 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr">
+      <c r="I78" s="8" t="inlineStr">
         <is>
           <t>已覆盖</t>
         </is>
@@ -5326,7 +5342,7 @@
       <c r="M78" s="2" t="inlineStr"/>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:53</t>
+          <t>2026-04-04 21:24</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr"/>
@@ -5373,7 +5389,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr">
+      <c r="I79" s="8" t="inlineStr">
         <is>
           <t>已覆盖</t>
         </is>
@@ -5396,7 +5412,7 @@
       <c r="M79" s="2" t="inlineStr"/>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:53</t>
+          <t>2026-04-04 21:24</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr"/>
@@ -5443,7 +5459,7 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr">
+      <c r="I80" s="8" t="inlineStr">
         <is>
           <t>已覆盖</t>
         </is>
@@ -5462,7 +5478,7 @@
       <c r="M80" s="2" t="inlineStr"/>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:53</t>
+          <t>2026-04-04 21:24</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr"/>
@@ -5509,7 +5525,7 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr">
+      <c r="I81" s="8" t="inlineStr">
         <is>
           <t>已覆盖</t>
         </is>
@@ -5528,7 +5544,7 @@
       <c r="M81" s="2" t="inlineStr"/>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:53</t>
+          <t>2026-04-04 21:24</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr"/>
@@ -5575,7 +5591,7 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr">
+      <c r="I82" s="8" t="inlineStr">
         <is>
           <t>已覆盖</t>
         </is>
@@ -5598,7 +5614,7 @@
       <c r="M82" s="2" t="inlineStr"/>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:53</t>
+          <t>2026-04-04 21:24</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr"/>
@@ -5645,7 +5661,7 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr">
+      <c r="I83" s="8" t="inlineStr">
         <is>
           <t>已覆盖</t>
         </is>
@@ -5664,7 +5680,7 @@
       <c r="M83" s="2" t="inlineStr"/>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:53</t>
+          <t>2026-04-04 21:24</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr"/>
@@ -5711,7 +5727,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I84" s="2" t="inlineStr">
+      <c r="I84" s="8" t="inlineStr">
         <is>
           <t>已覆盖</t>
         </is>
@@ -5734,7 +5750,7 @@
       <c r="M84" s="2" t="inlineStr"/>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:53</t>
+          <t>2026-04-04 21:24</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr"/>
@@ -5781,7 +5797,7 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr">
+      <c r="I85" s="8" t="inlineStr">
         <is>
           <t>已覆盖</t>
         </is>
@@ -5800,7 +5816,7 @@
       <c r="M85" s="2" t="inlineStr"/>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:53</t>
+          <t>2026-04-04 21:24</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr"/>
@@ -5847,7 +5863,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I86" s="2" t="inlineStr">
+      <c r="I86" s="8" t="inlineStr">
         <is>
           <t>已覆盖</t>
         </is>
@@ -5870,7 +5886,7 @@
       <c r="M86" s="2" t="inlineStr"/>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:53</t>
+          <t>2026-04-04 21:24</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr"/>
@@ -5918,7 +5934,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr">
+      <c r="I87" s="8" t="inlineStr">
         <is>
           <t>已覆盖</t>
         </is>
@@ -5941,7 +5957,7 @@
       <c r="M87" s="2" t="inlineStr"/>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:53</t>
+          <t>2026-04-04 21:24</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr"/>
@@ -5989,7 +6005,7 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="I88" s="2" t="inlineStr">
+      <c r="I88" s="8" t="inlineStr">
         <is>
           <t>已覆盖</t>
         </is>
@@ -6012,7 +6028,7 @@
       <c r="M88" s="2" t="inlineStr"/>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:53</t>
+          <t>2026-04-04 21:24</t>
         </is>
       </c>
       <c r="O88" s="2" t="inlineStr"/>
@@ -6258,7 +6274,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I92" s="2" t="inlineStr">
+      <c r="I92" s="8" t="inlineStr">
         <is>
           <t>已覆盖</t>
         </is>
@@ -6281,7 +6297,7 @@
       <c r="M92" s="2" t="inlineStr"/>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:53</t>
+          <t>2026-04-04 21:24</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr"/>
@@ -6325,7 +6341,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I93" s="2" t="inlineStr">
+      <c r="I93" s="8" t="inlineStr">
         <is>
           <t>已覆盖</t>
         </is>
@@ -6340,19 +6356,15 @@
           <t>i18n 测试</t>
         </is>
       </c>
-      <c r="L93" s="6" t="inlineStr">
-        <is>
-          <t>失败</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr">
-        <is>
-          <t>test_language_switch_to_english: strict mode violation, button EN 匹配到 4 个元素; test_sidebar_toggle: Page.goto timeout</t>
-        </is>
-      </c>
+      <c r="L93" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 16:46</t>
+          <t>2026-04-04 21:24</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr"/>
@@ -6543,11 +6555,19 @@
           <t>UkPhone/UkPostcode/Email/IBAN 通过; CreditCard 带空格格式+DriversLicense+baseline 引擎暂不支持(ignore)</t>
         </is>
       </c>
-      <c r="L96" s="8" t="inlineStr"/>
-      <c r="M96" s="2" t="inlineStr"/>
+      <c r="L96" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>baseline: UkPhone +44 161 496 0000 未识别(1个hard)</t>
+        </is>
+      </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 18:14</t>
+          <t>2026-04-04 21:24</t>
         </is>
       </c>
       <c r="O96" s="2" t="inlineStr"/>
@@ -6611,11 +6631,19 @@
           <t>SSN/UsPhone/ZipCode/Email 通过; DriversLicense+CreditCard 带空格格式+baseline 引擎暂不支持(ignore)</t>
         </is>
       </c>
-      <c r="L97" s="8" t="inlineStr"/>
-      <c r="M97" s="2" t="inlineStr"/>
+      <c r="L97" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>DriversLicense S012-3456-7890 未识别(9/10), baseline 1个hard</t>
+        </is>
+      </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 18:14</t>
+          <t>2026-04-04 21:24</t>
         </is>
       </c>
       <c r="O97" s="2" t="inlineStr"/>
@@ -6679,11 +6707,19 @@
           <t>IBAN(≥2)/UkPhone/Email/SSN/UsPhone 通过; CreditCard/Passport/DriversLicense+baseline 引擎暂不支持(ignore)</t>
         </is>
       </c>
-      <c r="L98" s="8" t="inlineStr"/>
-      <c r="M98" s="2" t="inlineStr"/>
+      <c r="L98" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>Passport 0个(需3), DriversLicense/baseline覆盖不足</t>
+        </is>
+      </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 18:14</t>
+          <t>2026-04-04 21:24</t>
         </is>
       </c>
       <c r="O98" s="2" t="inlineStr"/>
@@ -6747,11 +6783,15 @@
           <t>IpAddress(IPv4≥14)/Phone/Email 通过; baseline 中 IPv6 引擎暂不支持(ignore)</t>
         </is>
       </c>
-      <c r="L99" s="8" t="inlineStr"/>
+      <c r="L99" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M99" s="2" t="inlineStr"/>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 18:14</t>
+          <t>2026-04-04 21:24</t>
         </is>
       </c>
       <c r="O99" s="2" t="inlineStr"/>
@@ -6815,11 +6855,15 @@
           <t>Phone/Email/IdCard 通过; Landline(400热线)+baseline 引擎暂不支持(ignore)</t>
         </is>
       </c>
-      <c r="L100" s="8" t="inlineStr"/>
+      <c r="L100" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M100" s="2" t="inlineStr"/>
       <c r="N100" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 18:14</t>
+          <t>2026-04-04 21:24</t>
         </is>
       </c>
       <c r="O100" s="2" t="inlineStr"/>

--- a/e2e/testcases.xlsx
+++ b/e2e/testcases.xlsx
@@ -637,7 +637,7 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I2" s="4" t="inlineStr">
+      <c r="I2" s="8" t="inlineStr">
         <is>
           <t>已覆盖</t>
         </is>
@@ -652,13 +652,17 @@
           <t>断言已升级: highlights ≥ 25</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>未执行</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="n"/>
-      <c r="N2" s="2" t="n"/>
+      <c r="L2" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-04 21:48</t>
+        </is>
+      </c>
       <c r="O2" s="2" t="n"/>
     </row>
     <row r="3">
@@ -702,7 +706,7 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="I3" s="8" t="inlineStr">
         <is>
           <t>已覆盖</t>
         </is>
@@ -717,13 +721,17 @@
           <t>断言已升级: highlights ≥ 25</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>未执行</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
+      <c r="L3" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr"/>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-04 21:48</t>
+        </is>
+      </c>
       <c r="O3" s="2" t="n"/>
     </row>
     <row r="4">
@@ -769,7 +777,7 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="I4" s="8" t="inlineStr">
         <is>
           <t>已覆盖</t>
         </is>
@@ -784,13 +792,17 @@
           <t>断言已升级: highlights ≥ 8</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>未执行</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="n"/>
-      <c r="N4" s="2" t="n"/>
+      <c r="L4" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-04 21:48</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="n"/>
     </row>
     <row r="5">
@@ -837,7 +849,7 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="I5" s="8" t="inlineStr">
         <is>
           <t>已覆盖</t>
         </is>
@@ -852,13 +864,17 @@
           <t>断言已升级: highlights ≥ 8</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>未执行</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="n"/>
-      <c r="N5" s="2" t="n"/>
+      <c r="L5" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-04 21:48</t>
+        </is>
+      </c>
       <c r="O5" s="2" t="n"/>
     </row>
     <row r="6">
@@ -907,17 +923,29 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>desensitize_pdf.rs</t>
+        </is>
+      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
           <t>需先创建 pdf fixture</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr"/>
+      <c r="L6" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>PDFium 动态库未部署(环境问题)</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:28</t>
+          <t>2026-04-04 21:48</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr"/>
@@ -973,17 +1001,25 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>boundary.rs</t>
+        </is>
+      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
           <t>需创建加密 fixture</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
+      <c r="L7" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M7" s="2" t="inlineStr"/>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:28</t>
+          <t>2026-04-04 21:48</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr"/>
@@ -1039,13 +1075,25 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>boundary.rs</t>
+        </is>
+      </c>
       <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr"/>
+      <c r="L8" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>test_encrypted_xlsx_wrong_password: 密码错误重试测试失败</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 17:06</t>
+          <t>2026-04-04 21:48</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr"/>
@@ -1098,17 +1146,25 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>boundary.rs</t>
+        </is>
+      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
           <t>需创建空 fixture</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
+      <c r="L9" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:28</t>
+          <t>2026-04-04 21:48</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr"/>
@@ -1161,17 +1217,25 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>boundary.rs</t>
+        </is>
+      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
           <t>需创建大文件 fixture</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr"/>
+      <c r="L10" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M10" s="2" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:28</t>
+          <t>2026-04-04 21:48</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr"/>
@@ -1224,17 +1288,25 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>strategy_switching.rs</t>
+        </is>
+      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
           <t>需检查脱敏后的具体文本</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr"/>
+      <c r="L11" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M11" s="2" t="inlineStr"/>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:28</t>
+          <t>2026-04-04 21:48</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr"/>
@@ -1287,13 +1359,21 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>strategy_switching.rs</t>
+        </is>
+      </c>
       <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr"/>
+      <c r="L12" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:28</t>
+          <t>2026-04-04 21:48</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr"/>
@@ -1346,13 +1426,21 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>strategy_switching.rs</t>
+        </is>
+      </c>
       <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="2" t="inlineStr"/>
+      <c r="L13" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M13" s="2" t="inlineStr"/>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:28</t>
+          <t>2026-04-04 21:48</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr"/>
@@ -1406,13 +1494,21 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>strategy_switching.rs</t>
+        </is>
+      </c>
       <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr"/>
+      <c r="L14" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:28</t>
+          <t>2026-04-04 21:48</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr"/>
@@ -1465,13 +1561,21 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>strategy_switching.rs</t>
+        </is>
+      </c>
       <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="2" t="inlineStr"/>
+      <c r="L15" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M15" s="2" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:28</t>
+          <t>2026-04-04 21:48</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr"/>
@@ -1522,13 +1626,21 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>strategy_switching.rs</t>
+        </is>
+      </c>
       <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="2" t="inlineStr"/>
+      <c r="L16" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M16" s="2" t="inlineStr"/>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:28</t>
+          <t>2026-04-04 21:48</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr"/>
@@ -1582,13 +1694,21 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>type_filtering.rs</t>
+        </is>
+      </c>
       <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="2" t="inlineStr"/>
+      <c r="L17" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:13</t>
+          <t>2026-04-04 21:48</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr"/>
@@ -1642,13 +1762,21 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>type_filtering.rs</t>
+        </is>
+      </c>
       <c r="K18" s="2" t="inlineStr"/>
-      <c r="L18" s="2" t="inlineStr"/>
+      <c r="L18" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:13</t>
+          <t>2026-04-04 21:48</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr"/>
@@ -1703,13 +1831,21 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>type_filtering.rs</t>
+        </is>
+      </c>
       <c r="K19" s="2" t="inlineStr"/>
-      <c r="L19" s="2" t="inlineStr"/>
+      <c r="L19" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M19" s="2" t="inlineStr"/>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:13</t>
+          <t>2026-04-04 21:48</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr"/>
@@ -1763,13 +1899,21 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>type_filtering.rs</t>
+        </is>
+      </c>
       <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="2" t="inlineStr"/>
+      <c r="L20" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M20" s="2" t="inlineStr"/>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:28</t>
+          <t>2026-04-04 21:48</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr"/>
@@ -1822,13 +1966,21 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>dict_integration.rs</t>
+        </is>
+      </c>
       <c r="K21" s="2" t="inlineStr"/>
-      <c r="L21" s="2" t="inlineStr"/>
+      <c r="L21" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M21" s="2" t="inlineStr"/>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:28</t>
+          <t>2026-04-04 21:48</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr"/>
@@ -1881,13 +2033,21 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>dict_integration.rs</t>
+        </is>
+      </c>
       <c r="K22" s="2" t="inlineStr"/>
-      <c r="L22" s="2" t="inlineStr"/>
+      <c r="L22" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M22" s="2" t="inlineStr"/>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:28</t>
+          <t>2026-04-04 21:48</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr"/>
@@ -1940,13 +2100,21 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>dict_integration.rs</t>
+        </is>
+      </c>
       <c r="K23" s="2" t="inlineStr"/>
-      <c r="L23" s="2" t="inlineStr"/>
+      <c r="L23" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M23" s="2" t="inlineStr"/>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:28</t>
+          <t>2026-04-04 21:48</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr"/>
@@ -1999,13 +2167,21 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>dict_integration.rs</t>
+        </is>
+      </c>
       <c r="K24" s="2" t="inlineStr"/>
-      <c r="L24" s="2" t="inlineStr"/>
+      <c r="L24" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M24" s="2" t="inlineStr"/>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:28</t>
+          <t>2026-04-04 21:48</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr"/>
@@ -2058,13 +2234,21 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>dict_integration.rs</t>
+        </is>
+      </c>
       <c r="K25" s="2" t="inlineStr"/>
-      <c r="L25" s="2" t="inlineStr"/>
+      <c r="L25" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M25" s="2" t="inlineStr"/>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:28</t>
+          <t>2026-04-04 21:48</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr"/>
@@ -2117,13 +2301,21 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>column_inference.rs</t>
+        </is>
+      </c>
       <c r="K26" s="2" t="inlineStr"/>
-      <c r="L26" s="2" t="inlineStr"/>
+      <c r="L26" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M26" s="2" t="inlineStr"/>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 17:06</t>
+          <t>2026-04-04 21:48</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr"/>
@@ -2174,13 +2366,21 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>column_inference.rs</t>
+        </is>
+      </c>
       <c r="K27" s="2" t="inlineStr"/>
-      <c r="L27" s="2" t="inlineStr"/>
+      <c r="L27" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 17:06</t>
+          <t>2026-04-04 21:48</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr"/>
@@ -2231,13 +2431,21 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>column_inference.rs</t>
+        </is>
+      </c>
       <c r="K28" s="2" t="inlineStr"/>
-      <c r="L28" s="2" t="inlineStr"/>
+      <c r="L28" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M28" s="2" t="inlineStr"/>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 17:06</t>
+          <t>2026-04-04 21:48</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr"/>
@@ -2288,13 +2496,21 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>column_inference.rs</t>
+        </is>
+      </c>
       <c r="K29" s="2" t="inlineStr"/>
-      <c r="L29" s="2" t="inlineStr"/>
+      <c r="L29" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M29" s="2" t="inlineStr"/>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 17:06</t>
+          <t>2026-04-04 21:48</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr"/>
@@ -2340,9 +2556,9 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I30" s="8" t="inlineStr">
-        <is>
-          <t>已覆盖</t>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
@@ -2403,9 +2619,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I31" s="8" t="inlineStr">
-        <is>
-          <t>已覆盖</t>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
@@ -2469,13 +2685,21 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>alias_group.rs</t>
+        </is>
+      </c>
       <c r="K32" s="2" t="inlineStr"/>
-      <c r="L32" s="2" t="inlineStr"/>
+      <c r="L32" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M32" s="2" t="inlineStr"/>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 17:06</t>
+          <t>2026-04-04 21:48</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr"/>
@@ -2548,7 +2772,7 @@
       <c r="M33" s="2" t="inlineStr"/>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:24</t>
+          <t>2026-04-04 21:48</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr"/>
@@ -2602,13 +2826,21 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>test_restore_advanced.py</t>
+        </is>
+      </c>
       <c r="K34" s="2" t="inlineStr"/>
-      <c r="L34" s="2" t="inlineStr"/>
+      <c r="L34" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M34" s="2" t="inlineStr"/>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 17:48</t>
+          <t>2026-04-04 21:48</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr"/>
@@ -2659,13 +2891,21 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>restore_roundtrip.rs</t>
+        </is>
+      </c>
       <c r="K35" s="2" t="inlineStr"/>
-      <c r="L35" s="2" t="inlineStr"/>
+      <c r="L35" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M35" s="2" t="inlineStr"/>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:28</t>
+          <t>2026-04-04 21:48</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr"/>
@@ -2716,13 +2956,21 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>test_restore_advanced.py</t>
+        </is>
+      </c>
       <c r="K36" s="2" t="inlineStr"/>
-      <c r="L36" s="2" t="inlineStr"/>
+      <c r="L36" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 18:14</t>
+          <t>2026-04-04 21:48</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr"/>
@@ -2773,13 +3021,21 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>batch_processing.rs</t>
+        </is>
+      </c>
       <c r="K37" s="2" t="inlineStr"/>
-      <c r="L37" s="2" t="inlineStr"/>
+      <c r="L37" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M37" s="2" t="inlineStr"/>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:29</t>
+          <t>2026-04-04 21:48</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr"/>
@@ -2830,13 +3086,21 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>batch_processing.rs</t>
+        </is>
+      </c>
       <c r="K38" s="2" t="inlineStr"/>
-      <c r="L38" s="2" t="inlineStr"/>
+      <c r="L38" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M38" s="2" t="inlineStr"/>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:29</t>
+          <t>2026-04-04 21:48</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr"/>
@@ -2944,13 +3208,21 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>batch_processing.rs</t>
+        </is>
+      </c>
       <c r="K40" s="2" t="inlineStr"/>
-      <c r="L40" s="2" t="inlineStr"/>
+      <c r="L40" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M40" s="2" t="inlineStr"/>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:29</t>
+          <t>2026-04-04 21:48</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr"/>
@@ -3015,7 +3287,7 @@
       <c r="M41" s="2" t="inlineStr"/>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:24</t>
+          <t>2026-04-04 21:48</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr"/>
@@ -3062,13 +3334,21 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>test_workspace_crud.py</t>
+        </is>
+      </c>
       <c r="K42" s="2" t="inlineStr"/>
-      <c r="L42" s="2" t="inlineStr"/>
+      <c r="L42" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M42" s="2" t="inlineStr"/>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:28</t>
+          <t>2026-04-04 21:48</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr"/>
@@ -3115,13 +3395,21 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>test_workspace_crud.py</t>
+        </is>
+      </c>
       <c r="K43" s="2" t="inlineStr"/>
-      <c r="L43" s="2" t="inlineStr"/>
+      <c r="L43" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M43" s="2" t="inlineStr"/>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:28</t>
+          <t>2026-04-04 21:48</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr"/>
@@ -3168,13 +3456,25 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>test_workspace_advanced.py</t>
+        </is>
+      </c>
       <c r="K44" s="2" t="inlineStr"/>
-      <c r="L44" s="2" t="inlineStr"/>
-      <c r="M44" s="2" t="inlineStr"/>
+      <c r="L44" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>IPC mock 返回 2 个工作区但列表只显示 1 个</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 17:48</t>
+          <t>2026-04-04 21:48</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr"/>
@@ -3221,13 +3521,21 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>test_workspace_advanced.py</t>
+        </is>
+      </c>
       <c r="K45" s="2" t="inlineStr"/>
-      <c r="L45" s="2" t="inlineStr"/>
+      <c r="L45" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M45" s="2" t="inlineStr"/>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 17:48</t>
+          <t>2026-04-04 21:48</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr"/>
@@ -3274,13 +3582,21 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>test_ui_extras.py</t>
+        </is>
+      </c>
       <c r="K46" s="2" t="inlineStr"/>
-      <c r="L46" s="2" t="inlineStr"/>
+      <c r="L46" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M46" s="2" t="inlineStr"/>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:28</t>
+          <t>2026-04-04 21:48</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr"/>
@@ -3345,7 +3661,7 @@
       <c r="M47" s="2" t="inlineStr"/>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:24</t>
+          <t>2026-04-04 21:48</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr"/>
@@ -3392,13 +3708,21 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>test_ui_extras.py</t>
+        </is>
+      </c>
       <c r="K48" s="2" t="inlineStr"/>
-      <c r="L48" s="2" t="inlineStr"/>
+      <c r="L48" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M48" s="2" t="inlineStr"/>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:28</t>
+          <t>2026-04-04 21:48</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr"/>
@@ -3445,13 +3769,21 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>test_ui_extras.py</t>
+        </is>
+      </c>
       <c r="K49" s="2" t="inlineStr"/>
-      <c r="L49" s="2" t="inlineStr"/>
+      <c r="L49" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M49" s="2" t="inlineStr"/>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:28</t>
+          <t>2026-04-04 21:48</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr"/>
@@ -3504,7 +3836,11 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>desensitize_excel.rs</t>
+        </is>
+      </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
           <t>10人多字段: 姓名/手机/身份证/邮箱/银行卡/地址/公司</t>
@@ -3518,7 +3854,7 @@
       <c r="M50" s="2" t="inlineStr"/>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 12:59</t>
+          <t>2026-04-04 21:48</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr"/>
@@ -3571,17 +3907,25 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>desensitize_scenario_xlsx.rs</t>
+        </is>
+      </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
           <t>格式变体: 带+86手机号/带空格银行卡/混合文本</t>
         </is>
       </c>
-      <c r="L51" s="2" t="inlineStr"/>
+      <c r="L51" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M51" s="2" t="inlineStr"/>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:12</t>
+          <t>2026-04-04 21:48</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr"/>
@@ -3634,17 +3978,25 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>desensitize_scenario_xlsx.rs</t>
+        </is>
+      </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
           <t>双sheet: 合同信息+客服工单</t>
         </is>
       </c>
-      <c r="L52" s="2" t="inlineStr"/>
+      <c r="L52" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M52" s="2" t="inlineStr"/>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:12</t>
+          <t>2026-04-04 21:48</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr"/>
@@ -3697,17 +4049,25 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>desensitize_scenario_xlsx.rs</t>
+        </is>
+      </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
           <t>法律: 身份证/社会信用代码/律师电话</t>
         </is>
       </c>
-      <c r="L53" s="2" t="inlineStr"/>
+      <c r="L53" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M53" s="2" t="inlineStr"/>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:12</t>
+          <t>2026-04-04 21:49</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr"/>
@@ -3760,17 +4120,25 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>desensitize_scenario_xlsx.rs</t>
+        </is>
+      </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
           <t>物业: 车牌号/座机号/多联系电话</t>
         </is>
       </c>
-      <c r="L54" s="2" t="inlineStr"/>
+      <c r="L54" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M54" s="2" t="inlineStr"/>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 18:14</t>
+          <t>2026-04-04 21:49</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr"/>
@@ -3823,17 +4191,25 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>desensitize_scenario_xlsx.rs</t>
+        </is>
+      </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
           <t>教育: 父母姓名/电话/工作单位</t>
         </is>
       </c>
-      <c r="L55" s="2" t="inlineStr"/>
+      <c r="L55" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M55" s="2" t="inlineStr"/>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:12</t>
+          <t>2026-04-04 21:49</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr"/>
@@ -3886,17 +4262,25 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>desensitize_scenario_xlsx.rs</t>
+        </is>
+      </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
           <t>医疗: 医保卡号/主治医师/诊断信息</t>
         </is>
       </c>
-      <c r="L56" s="2" t="inlineStr"/>
+      <c r="L56" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M56" s="2" t="inlineStr"/>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:12</t>
+          <t>2026-04-04 21:49</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr"/>
@@ -3949,17 +4333,25 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>desensitize_scenario_xlsx.rs</t>
+        </is>
+      </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
           <t>金融: 放款账号/担保人信息</t>
         </is>
       </c>
-      <c r="L57" s="2" t="inlineStr"/>
+      <c r="L57" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M57" s="2" t="inlineStr"/>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:12</t>
+          <t>2026-04-04 21:49</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr"/>
@@ -4012,17 +4404,25 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>desensitize_scenario_csv.rs</t>
+        </is>
+      </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
           <t>结构化CSV: 8人7列全字段</t>
         </is>
       </c>
-      <c r="L58" s="2" t="inlineStr"/>
+      <c r="L58" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M58" s="2" t="inlineStr"/>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:12</t>
+          <t>2026-04-04 21:49</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr"/>
@@ -4075,17 +4475,25 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>desensitize_scenario_csv.rs</t>
+        </is>
+      </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
           <t>6客户含身份证/收货地址</t>
         </is>
       </c>
-      <c r="L59" s="2" t="inlineStr"/>
+      <c r="L59" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M59" s="2" t="inlineStr"/>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:13</t>
+          <t>2026-04-04 21:49</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr"/>
@@ -4138,17 +4546,25 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>desensitize_scenario_csv.rs</t>
+        </is>
+      </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
           <t>自由文本: 敏感信息嵌入纪要正文</t>
         </is>
       </c>
-      <c r="L60" s="2" t="inlineStr"/>
+      <c r="L60" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M60" s="2" t="inlineStr"/>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:13</t>
+          <t>2026-04-04 21:49</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr"/>
@@ -4201,17 +4617,25 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>desensitize_scenario_csv.rs</t>
+        </is>
+      </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
           <t>混合: 结构化+自由文本含银行卡/车牌</t>
         </is>
       </c>
-      <c r="L61" s="2" t="inlineStr"/>
+      <c r="L61" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M61" s="2" t="inlineStr"/>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 18:14</t>
+          <t>2026-04-04 21:49</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr"/>
@@ -4264,17 +4688,25 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>desensitize_scenario_docx.rs</t>
+        </is>
+      </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
           <t>报告体: 5客户银行卡/公司信息</t>
         </is>
       </c>
-      <c r="L62" s="2" t="inlineStr"/>
+      <c r="L62" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M62" s="2" t="inlineStr"/>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:13</t>
+          <t>2026-04-04 21:49</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr"/>
@@ -4327,17 +4759,25 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>desensitize_scenario_docx.rs</t>
+        </is>
+      </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
           <t>通知体: 工号/银行卡/学历背景</t>
         </is>
       </c>
-      <c r="L63" s="2" t="inlineStr"/>
+      <c r="L63" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M63" s="2" t="inlineStr"/>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:13</t>
+          <t>2026-04-04 21:49</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr"/>
@@ -4390,17 +4830,25 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>desensitize_scenario_docx.rs</t>
+        </is>
+      </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
           <t>合同体: 社会信用代码/银行账号/产权证号</t>
         </is>
       </c>
-      <c r="L64" s="2" t="inlineStr"/>
+      <c r="L64" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M64" s="2" t="inlineStr"/>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:13</t>
+          <t>2026-04-04 21:49</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr"/>
@@ -4453,17 +4901,25 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>desensitize_scenario_docx.rs</t>
+        </is>
+      </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
           <t>保险: 保单号/车牌号/银行卡</t>
         </is>
       </c>
-      <c r="L65" s="2" t="inlineStr"/>
+      <c r="L65" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M65" s="2" t="inlineStr"/>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 18:14</t>
+          <t>2026-04-04 21:49</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr"/>
@@ -4516,17 +4972,25 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>desensitize_scenario_docx.rs</t>
+        </is>
+      </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
           <t>法律函件: 执业证号/贷款账号</t>
         </is>
       </c>
-      <c r="L66" s="2" t="inlineStr"/>
+      <c r="L66" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M66" s="2" t="inlineStr"/>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:13</t>
+          <t>2026-04-04 21:49</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr"/>
@@ -4579,17 +5043,25 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>desensitize_scenario_docx.rs</t>
+        </is>
+      </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
           <t>法律: 社保编号/社会信用代码</t>
         </is>
       </c>
-      <c r="L67" s="2" t="inlineStr"/>
+      <c r="L67" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M67" s="2" t="inlineStr"/>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:13</t>
+          <t>2026-04-04 21:49</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr"/>
@@ -4642,17 +5114,25 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>desensitize_scenario_docx.rs</t>
+        </is>
+      </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
           <t>医疗: 医保卡号/病历号</t>
         </is>
       </c>
-      <c r="L68" s="2" t="inlineStr"/>
+      <c r="L68" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M68" s="2" t="inlineStr"/>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:13</t>
+          <t>2026-04-04 21:49</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr"/>
@@ -4705,17 +5185,25 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>desensitize_scenario_docx.rs</t>
+        </is>
+      </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
           <t>司法: 案号/社会信用代码</t>
         </is>
       </c>
-      <c r="L69" s="2" t="inlineStr"/>
+      <c r="L69" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M69" s="2" t="inlineStr"/>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:13</t>
+          <t>2026-04-04 21:49</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr"/>
@@ -4768,17 +5256,25 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>desensitize_scenario_docx.rs</t>
+        </is>
+      </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
           <t>金融: 多人信息/社会信用代码</t>
         </is>
       </c>
-      <c r="L70" s="2" t="inlineStr"/>
+      <c r="L70" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M70" s="2" t="inlineStr"/>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:13</t>
+          <t>2026-04-04 21:49</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr"/>
@@ -4848,7 +5344,7 @@
       <c r="M71" s="2" t="inlineStr"/>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:24</t>
+          <t>2026-04-04 21:49</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr"/>
@@ -4918,7 +5414,7 @@
       <c r="M72" s="2" t="inlineStr"/>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:24</t>
+          <t>2026-04-04 21:49</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr"/>
@@ -4987,12 +5483,12 @@
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>GBK CSV 解析失败: invalid utf-8</t>
+          <t>GBK 编码 CSV 解析失败，csv crate 仅支持 UTF-8</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:24</t>
+          <t>2026-04-04 21:49</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr"/>
@@ -5062,7 +5558,7 @@
       <c r="M74" s="2" t="inlineStr"/>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:24</t>
+          <t>2026-04-04 21:49</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr"/>
@@ -5132,7 +5628,7 @@
       <c r="M75" s="2" t="inlineStr"/>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:24</t>
+          <t>2026-04-04 21:49</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr"/>
@@ -5202,7 +5698,7 @@
       <c r="M76" s="2" t="inlineStr"/>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:24</t>
+          <t>2026-04-04 21:49</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr"/>
@@ -5272,7 +5768,7 @@
       <c r="M77" s="2" t="inlineStr"/>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:24</t>
+          <t>2026-04-04 21:49</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr"/>
@@ -5342,7 +5838,7 @@
       <c r="M78" s="2" t="inlineStr"/>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:24</t>
+          <t>2026-04-04 21:49</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr"/>
@@ -5412,7 +5908,7 @@
       <c r="M79" s="2" t="inlineStr"/>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:24</t>
+          <t>2026-04-04 21:49</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr"/>
@@ -5478,7 +5974,7 @@
       <c r="M80" s="2" t="inlineStr"/>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:24</t>
+          <t>2026-04-04 21:49</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr"/>
@@ -5544,7 +6040,7 @@
       <c r="M81" s="2" t="inlineStr"/>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:24</t>
+          <t>2026-04-04 21:49</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr"/>
@@ -5614,7 +6110,7 @@
       <c r="M82" s="2" t="inlineStr"/>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:24</t>
+          <t>2026-04-04 21:49</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr"/>
@@ -5680,7 +6176,7 @@
       <c r="M83" s="2" t="inlineStr"/>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:24</t>
+          <t>2026-04-04 21:49</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr"/>
@@ -5750,7 +6246,7 @@
       <c r="M84" s="2" t="inlineStr"/>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:24</t>
+          <t>2026-04-04 21:49</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr"/>
@@ -5816,7 +6312,7 @@
       <c r="M85" s="2" t="inlineStr"/>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:24</t>
+          <t>2026-04-04 21:49</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr"/>
@@ -5886,7 +6382,7 @@
       <c r="M86" s="2" t="inlineStr"/>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:24</t>
+          <t>2026-04-04 21:49</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr"/>
@@ -5957,7 +6453,7 @@
       <c r="M87" s="2" t="inlineStr"/>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:24</t>
+          <t>2026-04-04 21:49</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr"/>
@@ -6028,7 +6524,7 @@
       <c r="M88" s="2" t="inlineStr"/>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:24</t>
+          <t>2026-04-04 21:49</t>
         </is>
       </c>
       <c r="O88" s="2" t="inlineStr"/>
@@ -6297,7 +6793,7 @@
       <c r="M92" s="2" t="inlineStr"/>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:24</t>
+          <t>2026-04-04 21:49</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr"/>
@@ -6364,7 +6860,7 @@
       <c r="M93" s="2" t="inlineStr"/>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:24</t>
+          <t>2026-04-04 21:49</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr"/>
@@ -6562,12 +7058,12 @@
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>baseline: UkPhone +44 161 496 0000 未识别(1个hard)</t>
+          <t>UkPhone +44 161 496 0000(含空格格式)未被正则识别</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:24</t>
+          <t>2026-04-04 21:49</t>
         </is>
       </c>
       <c r="O96" s="2" t="inlineStr"/>
@@ -6638,12 +7134,12 @@
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>DriversLicense S012-3456-7890 未识别(9/10), baseline 1个hard</t>
+          <t>DriversLicense S012-3456-7890 未识别</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:24</t>
+          <t>2026-04-04 21:49</t>
         </is>
       </c>
       <c r="O97" s="2" t="inlineStr"/>
@@ -6714,12 +7210,12 @@
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>Passport 0个(需3), DriversLicense/baseline覆盖不足</t>
+          <t>Passport 号码完全未识别(0/3)，国际驾照格式缺失</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:24</t>
+          <t>2026-04-04 21:49</t>
         </is>
       </c>
       <c r="O98" s="2" t="inlineStr"/>
@@ -6791,7 +7287,7 @@
       <c r="M99" s="2" t="inlineStr"/>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:24</t>
+          <t>2026-04-04 21:49</t>
         </is>
       </c>
       <c r="O99" s="2" t="inlineStr"/>
@@ -6863,7 +7359,7 @@
       <c r="M100" s="2" t="inlineStr"/>
       <c r="N100" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:24</t>
+          <t>2026-04-04 21:49</t>
         </is>
       </c>
       <c r="O100" s="2" t="inlineStr"/>
@@ -6917,17 +7413,25 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J101" s="2" t="inlineStr"/>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>type_filtering.rs</t>
+        </is>
+      </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
           <t>回归: enabled_types 参数为 None 时的默认行为</t>
         </is>
       </c>
-      <c r="L101" s="2" t="inlineStr"/>
+      <c r="L101" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M101" s="2" t="inlineStr"/>
       <c r="N101" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:13</t>
+          <t>2026-04-04 21:49</t>
         </is>
       </c>
       <c r="O101" s="2" t="inlineStr"/>
@@ -6980,17 +7484,25 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J102" s="2" t="inlineStr"/>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>type_filtering.rs</t>
+        </is>
+      </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
           <t>防御: 前端传入脏数据的容错</t>
         </is>
       </c>
-      <c r="L102" s="2" t="inlineStr"/>
+      <c r="L102" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M102" s="2" t="inlineStr"/>
       <c r="N102" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:13</t>
+          <t>2026-04-04 21:49</t>
         </is>
       </c>
       <c r="O102" s="2" t="inlineStr"/>
@@ -7044,17 +7556,25 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J103" s="2" t="inlineStr"/>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>type_filtering.rs</t>
+        </is>
+      </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
           <t>端到端: 类型过滤 → 脱敏 → 导出</t>
         </is>
       </c>
-      <c r="L103" s="2" t="inlineStr"/>
+      <c r="L103" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M103" s="2" t="inlineStr"/>
       <c r="N103" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:28</t>
+          <t>2026-04-04 21:49</t>
         </is>
       </c>
       <c r="O103" s="2" t="inlineStr"/>
@@ -7108,17 +7628,29 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J104" s="2" t="inlineStr"/>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>test_type_persistence.py</t>
+        </is>
+      </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
           <t>持久化: enabled_types 保存和恢复</t>
         </is>
       </c>
-      <c r="L104" s="2" t="inlineStr"/>
-      <c r="M104" s="2" t="inlineStr"/>
+      <c r="L104" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>IPC mock selectWorkspace 未正确触发 store 更新</t>
+        </is>
+      </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 17:48</t>
+          <t>2026-04-04 21:49</t>
         </is>
       </c>
       <c r="O104" s="2" t="inlineStr"/>
@@ -7171,17 +7703,25 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J105" s="2" t="inlineStr"/>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>dict_integration.rs</t>
+        </is>
+      </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
           <t>字典引擎对 Document 和 Spreadsheet 两种 FileContent 的一致性</t>
         </is>
       </c>
-      <c r="L105" s="2" t="inlineStr"/>
+      <c r="L105" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M105" s="2" t="inlineStr"/>
       <c r="N105" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:28</t>
+          <t>2026-04-04 21:49</t>
         </is>
       </c>
       <c r="O105" s="2" t="inlineStr"/>
@@ -7233,17 +7773,25 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J106" s="2" t="inlineStr"/>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>dict_integration.rs</t>
+        </is>
+      </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
           <t>防御: 空词条的容错处理</t>
         </is>
       </c>
-      <c r="L106" s="2" t="inlineStr"/>
+      <c r="L106" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M106" s="2" t="inlineStr"/>
       <c r="N106" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:28</t>
+          <t>2026-04-04 21:49</t>
         </is>
       </c>
       <c r="O106" s="2" t="inlineStr"/>
@@ -7296,17 +7844,25 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J107" s="2" t="inlineStr"/>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>dict_integration.rs</t>
+        </is>
+      </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
           <t>字典按语言过滤的逻辑验证</t>
         </is>
       </c>
-      <c r="L107" s="2" t="inlineStr"/>
+      <c r="L107" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M107" s="2" t="inlineStr"/>
       <c r="N107" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:28</t>
+          <t>2026-04-04 21:49</t>
         </is>
       </c>
       <c r="O107" s="2" t="inlineStr"/>
@@ -7359,17 +7915,25 @@
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="J108" s="2" t="inlineStr"/>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>dict_integration.rs</t>
+        </is>
+      </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
           <t>白名单精确匹配 vs 子串匹配的行为确认</t>
         </is>
       </c>
-      <c r="L108" s="2" t="inlineStr"/>
+      <c r="L108" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M108" s="2" t="inlineStr"/>
       <c r="N108" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:28</t>
+          <t>2026-04-04 21:49</t>
         </is>
       </c>
       <c r="O108" s="2" t="inlineStr"/>

--- a/e2e/testcases.xlsx
+++ b/e2e/testcases.xlsx
@@ -660,7 +660,7 @@
       <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:48</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O2" s="2" t="n"/>
@@ -729,7 +729,7 @@
       <c r="M3" s="2" t="inlineStr"/>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:48</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O3" s="2" t="n"/>
@@ -800,7 +800,7 @@
       <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:48</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O4" s="2" t="n"/>
@@ -872,7 +872,7 @@
       <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:48</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O5" s="2" t="n"/>
@@ -940,12 +940,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>PDFium 动态库未部署(环境问题)</t>
+          <t>ENV-001: PDFium 动态库未部署</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:48</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr"/>
@@ -1011,15 +1011,19 @@
           <t>需创建加密 fixture</t>
         </is>
       </c>
-      <c r="L7" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+      <c r="L7" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>BUG-020: 错误密码解密返回格式检测错误而非密码错误</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:48</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr"/>
@@ -1088,12 +1092,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>test_encrypted_xlsx_wrong_password: 密码错误重试测试失败</t>
+          <t>BUG-020: 错误密码解密返回格式检测错误而非密码错误</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:48</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr"/>
@@ -1156,15 +1160,19 @@
           <t>需创建空 fixture</t>
         </is>
       </c>
-      <c r="L9" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+      <c r="L9" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>BUG-020: 错误密码解密返回格式检测错误而非密码错误</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:48</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr"/>
@@ -1227,15 +1235,19 @@
           <t>需创建大文件 fixture</t>
         </is>
       </c>
-      <c r="L10" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+      <c r="L10" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>BUG-020: 错误密码解密返回格式检测错误而非密码错误</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:48</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr"/>
@@ -1306,7 +1318,7 @@
       <c r="M11" s="2" t="inlineStr"/>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:48</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr"/>
@@ -1373,7 +1385,7 @@
       <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:48</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr"/>
@@ -1440,7 +1452,7 @@
       <c r="M13" s="2" t="inlineStr"/>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:48</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr"/>
@@ -1508,7 +1520,7 @@
       <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:48</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr"/>
@@ -1575,7 +1587,7 @@
       <c r="M15" s="2" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:48</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr"/>
@@ -1640,7 +1652,7 @@
       <c r="M16" s="2" t="inlineStr"/>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:48</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr"/>
@@ -1708,7 +1720,7 @@
       <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:48</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr"/>
@@ -1776,7 +1788,7 @@
       <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:48</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr"/>
@@ -1845,7 +1857,7 @@
       <c r="M19" s="2" t="inlineStr"/>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:48</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr"/>
@@ -1913,7 +1925,7 @@
       <c r="M20" s="2" t="inlineStr"/>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:48</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr"/>
@@ -1980,7 +1992,7 @@
       <c r="M21" s="2" t="inlineStr"/>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:48</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr"/>
@@ -2047,7 +2059,7 @@
       <c r="M22" s="2" t="inlineStr"/>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:48</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr"/>
@@ -2114,7 +2126,7 @@
       <c r="M23" s="2" t="inlineStr"/>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:48</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr"/>
@@ -2181,7 +2193,7 @@
       <c r="M24" s="2" t="inlineStr"/>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:48</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr"/>
@@ -2248,7 +2260,7 @@
       <c r="M25" s="2" t="inlineStr"/>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:48</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr"/>
@@ -2315,7 +2327,7 @@
       <c r="M26" s="2" t="inlineStr"/>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:48</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr"/>
@@ -2380,7 +2392,7 @@
       <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:48</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr"/>
@@ -2445,7 +2457,7 @@
       <c r="M28" s="2" t="inlineStr"/>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:48</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr"/>
@@ -2510,7 +2522,7 @@
       <c r="M29" s="2" t="inlineStr"/>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:48</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr"/>
@@ -2699,7 +2711,7 @@
       <c r="M32" s="2" t="inlineStr"/>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:48</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr"/>
@@ -2772,7 +2784,7 @@
       <c r="M33" s="2" t="inlineStr"/>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:48</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr"/>
@@ -2840,7 +2852,7 @@
       <c r="M34" s="2" t="inlineStr"/>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:48</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr"/>
@@ -2905,7 +2917,7 @@
       <c r="M35" s="2" t="inlineStr"/>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:48</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr"/>
@@ -2970,7 +2982,7 @@
       <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:48</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr"/>
@@ -3035,7 +3047,7 @@
       <c r="M37" s="2" t="inlineStr"/>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:48</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr"/>
@@ -3100,7 +3112,7 @@
       <c r="M38" s="2" t="inlineStr"/>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:48</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr"/>
@@ -3222,7 +3234,7 @@
       <c r="M40" s="2" t="inlineStr"/>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:48</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr"/>
@@ -3287,7 +3299,7 @@
       <c r="M41" s="2" t="inlineStr"/>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:48</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr"/>
@@ -3348,7 +3360,7 @@
       <c r="M42" s="2" t="inlineStr"/>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:48</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr"/>
@@ -3409,7 +3421,7 @@
       <c r="M43" s="2" t="inlineStr"/>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:48</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr"/>
@@ -3469,12 +3481,12 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>IPC mock 返回 2 个工作区但列表只显示 1 个</t>
+          <t>BUG-019: 工作区列表渲染竞态</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:48</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr"/>
@@ -3527,15 +3539,19 @@
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr"/>
-      <c r="L45" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+      <c r="L45" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>BUG-019: 工作区列表渲染竞态</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:48</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr"/>
@@ -3596,7 +3612,7 @@
       <c r="M46" s="2" t="inlineStr"/>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:48</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr"/>
@@ -3661,7 +3677,7 @@
       <c r="M47" s="2" t="inlineStr"/>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:48</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr"/>
@@ -3722,7 +3738,7 @@
       <c r="M48" s="2" t="inlineStr"/>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:48</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr"/>
@@ -3783,7 +3799,7 @@
       <c r="M49" s="2" t="inlineStr"/>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:48</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr"/>
@@ -3854,7 +3870,7 @@
       <c r="M50" s="2" t="inlineStr"/>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:48</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr"/>
@@ -3925,7 +3941,7 @@
       <c r="M51" s="2" t="inlineStr"/>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:48</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr"/>
@@ -3996,7 +4012,7 @@
       <c r="M52" s="2" t="inlineStr"/>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:48</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr"/>
@@ -4067,7 +4083,7 @@
       <c r="M53" s="2" t="inlineStr"/>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:49</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr"/>
@@ -4138,7 +4154,7 @@
       <c r="M54" s="2" t="inlineStr"/>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:49</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr"/>
@@ -4209,7 +4225,7 @@
       <c r="M55" s="2" t="inlineStr"/>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:49</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr"/>
@@ -4280,7 +4296,7 @@
       <c r="M56" s="2" t="inlineStr"/>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:49</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr"/>
@@ -4351,7 +4367,7 @@
       <c r="M57" s="2" t="inlineStr"/>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:49</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr"/>
@@ -4422,7 +4438,7 @@
       <c r="M58" s="2" t="inlineStr"/>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:49</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr"/>
@@ -4493,7 +4509,7 @@
       <c r="M59" s="2" t="inlineStr"/>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:49</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr"/>
@@ -4564,7 +4580,7 @@
       <c r="M60" s="2" t="inlineStr"/>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:49</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr"/>
@@ -4635,7 +4651,7 @@
       <c r="M61" s="2" t="inlineStr"/>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:49</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr"/>
@@ -4706,7 +4722,7 @@
       <c r="M62" s="2" t="inlineStr"/>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:49</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr"/>
@@ -4777,7 +4793,7 @@
       <c r="M63" s="2" t="inlineStr"/>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:49</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr"/>
@@ -4848,7 +4864,7 @@
       <c r="M64" s="2" t="inlineStr"/>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:49</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr"/>
@@ -4919,7 +4935,7 @@
       <c r="M65" s="2" t="inlineStr"/>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:49</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr"/>
@@ -4990,7 +5006,7 @@
       <c r="M66" s="2" t="inlineStr"/>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:49</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr"/>
@@ -5061,7 +5077,7 @@
       <c r="M67" s="2" t="inlineStr"/>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:49</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr"/>
@@ -5132,7 +5148,7 @@
       <c r="M68" s="2" t="inlineStr"/>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:49</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr"/>
@@ -5203,7 +5219,7 @@
       <c r="M69" s="2" t="inlineStr"/>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:49</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr"/>
@@ -5274,7 +5290,7 @@
       <c r="M70" s="2" t="inlineStr"/>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:49</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr"/>
@@ -5344,7 +5360,7 @@
       <c r="M71" s="2" t="inlineStr"/>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:49</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr"/>
@@ -5414,7 +5430,7 @@
       <c r="M72" s="2" t="inlineStr"/>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:49</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr"/>
@@ -5483,12 +5499,12 @@
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>GBK 编码 CSV 解析失败，csv crate 仅支持 UTF-8</t>
+          <t>BUG-014: GBK 编码 CSV 解析失败，csv crate 仅支持 UTF-8</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:49</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr"/>
@@ -5550,15 +5566,19 @@
           <t>测试 BOM 头处理</t>
         </is>
       </c>
-      <c r="L74" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+      <c r="L74" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>BUG-014: GBK 编码 CSV 解析失败，csv crate 仅支持 UTF-8</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:49</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr"/>
@@ -5620,15 +5640,19 @@
           <t>全角数字 edge case</t>
         </is>
       </c>
-      <c r="L75" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+      <c r="L75" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>BUG-014: GBK 编码 CSV 解析失败，csv crate 仅支持 UTF-8</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:49</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr"/>
@@ -5698,7 +5722,7 @@
       <c r="M76" s="2" t="inlineStr"/>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:49</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr"/>
@@ -5768,7 +5792,7 @@
       <c r="M77" s="2" t="inlineStr"/>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:49</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr"/>
@@ -5830,15 +5854,19 @@
           <t>超大单元格性能和准确性</t>
         </is>
       </c>
-      <c r="L78" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+      <c r="L78" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>BUG-014: GBK 编码 CSV 解析失败，csv crate 仅支持 UTF-8</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:49</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr"/>
@@ -5908,7 +5936,7 @@
       <c r="M79" s="2" t="inlineStr"/>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:49</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr"/>
@@ -5974,7 +6002,7 @@
       <c r="M80" s="2" t="inlineStr"/>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:49</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr"/>
@@ -6040,7 +6068,7 @@
       <c r="M81" s="2" t="inlineStr"/>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:49</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr"/>
@@ -6110,7 +6138,7 @@
       <c r="M82" s="2" t="inlineStr"/>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:49</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr"/>
@@ -6176,7 +6204,7 @@
       <c r="M83" s="2" t="inlineStr"/>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:49</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr"/>
@@ -6246,7 +6274,7 @@
       <c r="M84" s="2" t="inlineStr"/>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:49</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr"/>
@@ -6312,7 +6340,7 @@
       <c r="M85" s="2" t="inlineStr"/>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:49</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr"/>
@@ -6382,7 +6410,7 @@
       <c r="M86" s="2" t="inlineStr"/>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:49</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr"/>
@@ -6453,7 +6481,7 @@
       <c r="M87" s="2" t="inlineStr"/>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:49</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr"/>
@@ -6524,7 +6552,7 @@
       <c r="M88" s="2" t="inlineStr"/>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:49</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O88" s="2" t="inlineStr"/>
@@ -6586,13 +6614,17 @@
           <t>错误隔离</t>
         </is>
       </c>
-      <c r="L89" s="2" t="inlineStr">
-        <is>
-          <t>未执行</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="n"/>
-      <c r="N89" s="2" t="n"/>
+      <c r="L89" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-04 23:15</t>
+        </is>
+      </c>
       <c r="O89" s="2" t="n"/>
     </row>
     <row r="90">
@@ -6652,13 +6684,17 @@
           <t>中文列名匹配</t>
         </is>
       </c>
-      <c r="L90" s="2" t="inlineStr">
-        <is>
-          <t>未执行</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="n"/>
-      <c r="N90" s="2" t="n"/>
+      <c r="L90" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-04 23:15</t>
+        </is>
+      </c>
       <c r="O90" s="2" t="n"/>
     </row>
     <row r="91">
@@ -6718,13 +6754,17 @@
           <t>英文列名匹配</t>
         </is>
       </c>
-      <c r="L91" s="2" t="inlineStr">
-        <is>
-          <t>未执行</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="n"/>
-      <c r="N91" s="2" t="n"/>
+      <c r="L91" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-04 23:15</t>
+        </is>
+      </c>
       <c r="O91" s="2" t="n"/>
     </row>
     <row r="92">
@@ -6793,7 +6833,7 @@
       <c r="M92" s="2" t="inlineStr"/>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:49</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr"/>
@@ -6860,7 +6900,7 @@
       <c r="M93" s="2" t="inlineStr"/>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:49</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr"/>
@@ -6919,13 +6959,17 @@
           <t>主题切换</t>
         </is>
       </c>
-      <c r="L94" s="2" t="inlineStr">
-        <is>
-          <t>未执行</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="n"/>
-      <c r="N94" s="2" t="n"/>
+      <c r="L94" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-04 23:15</t>
+        </is>
+      </c>
       <c r="O94" s="2" t="n"/>
     </row>
     <row r="95">
@@ -6983,13 +7027,17 @@
           <t>本地存储持久化</t>
         </is>
       </c>
-      <c r="L95" s="2" t="inlineStr">
-        <is>
-          <t>未执行</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="n"/>
-      <c r="N95" s="2" t="n"/>
+      <c r="L95" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-04 23:15</t>
+        </is>
+      </c>
       <c r="O95" s="2" t="n"/>
     </row>
     <row r="96">
@@ -7058,12 +7106,12 @@
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>UkPhone +44 161 496 0000(含空格格式)未被正则识别</t>
+          <t>BUG-015: UkPhone 含空格格式未识别</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:49</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O96" s="2" t="inlineStr"/>
@@ -7134,12 +7182,12 @@
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>DriversLicense S012-3456-7890 未识别</t>
+          <t>BUG-016: DriversLicense S开头格式未识别</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:49</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O97" s="2" t="inlineStr"/>
@@ -7210,12 +7258,12 @@
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>Passport 号码完全未识别(0/3)，国际驾照格式缺失</t>
+          <t>BUG-017: Passport 和国际驾照格式正则缺失</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:49</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O98" s="2" t="inlineStr"/>
@@ -7287,7 +7335,7 @@
       <c r="M99" s="2" t="inlineStr"/>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:49</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O99" s="2" t="inlineStr"/>
@@ -7359,7 +7407,7 @@
       <c r="M100" s="2" t="inlineStr"/>
       <c r="N100" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:49</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O100" s="2" t="inlineStr"/>
@@ -7431,7 +7479,7 @@
       <c r="M101" s="2" t="inlineStr"/>
       <c r="N101" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:49</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O101" s="2" t="inlineStr"/>
@@ -7502,7 +7550,7 @@
       <c r="M102" s="2" t="inlineStr"/>
       <c r="N102" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:49</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O102" s="2" t="inlineStr"/>
@@ -7574,7 +7622,7 @@
       <c r="M103" s="2" t="inlineStr"/>
       <c r="N103" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:49</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O103" s="2" t="inlineStr"/>
@@ -7645,12 +7693,12 @@
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>IPC mock selectWorkspace 未正确触发 store 更新</t>
+          <t>BUG-018: IPC mock enabled_types 为 null</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:49</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O104" s="2" t="inlineStr"/>
@@ -7721,7 +7769,7 @@
       <c r="M105" s="2" t="inlineStr"/>
       <c r="N105" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:49</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O105" s="2" t="inlineStr"/>
@@ -7791,7 +7839,7 @@
       <c r="M106" s="2" t="inlineStr"/>
       <c r="N106" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:49</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O106" s="2" t="inlineStr"/>
@@ -7862,7 +7910,7 @@
       <c r="M107" s="2" t="inlineStr"/>
       <c r="N107" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:49</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O107" s="2" t="inlineStr"/>
@@ -7933,7 +7981,7 @@
       <c r="M108" s="2" t="inlineStr"/>
       <c r="N108" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 21:49</t>
+          <t>2026-04-04 23:15</t>
         </is>
       </c>
       <c r="O108" s="2" t="inlineStr"/>

--- a/e2e/testcases.xlsx
+++ b/e2e/testcases.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试用例" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fixture数据基线" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖率统计" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="测试用例" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Fixture数据基线" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="覆盖率统计" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'测试用例'!$A$1:$O$49</definedName>
@@ -652,15 +652,19 @@
           <t>断言已升级: highlights ≥ 25</t>
         </is>
       </c>
-      <c r="L2" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+      <c r="L2" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Playwright 超时 — IPC Mock 环境问题</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O2" s="2" t="n"/>
@@ -721,15 +725,19 @@
           <t>断言已升级: highlights ≥ 25</t>
         </is>
       </c>
-      <c r="L3" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+      <c r="L3" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Playwright 超时 — IPC Mock 环境问题</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O3" s="2" t="n"/>
@@ -792,15 +800,19 @@
           <t>断言已升级: highlights ≥ 8</t>
         </is>
       </c>
-      <c r="L4" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Playwright 超时 — IPC Mock 环境问题</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O4" s="2" t="n"/>
@@ -864,15 +876,19 @@
           <t>断言已升级: highlights ≥ 8</t>
         </is>
       </c>
-      <c r="L5" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+      <c r="L5" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Playwright 超时 — IPC Mock 环境问题</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O5" s="2" t="n"/>
@@ -940,12 +956,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>ENV-001: PDFium 动态库未部署</t>
+          <t>模块 desensitize_pdf 有测试失败（基线覆盖硬断言未命中）</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr"/>
@@ -1018,12 +1034,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>BUG-020: 错误密码解密返回格式检测错误而非密码错误</t>
+          <t>模块 boundary 有测试失败（基线覆盖硬断言未命中）</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr"/>
@@ -1092,12 +1108,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>BUG-020: 错误密码解密返回格式检测错误而非密码错误</t>
+          <t>模块 boundary 有测试失败（基线覆盖硬断言未命中）</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr"/>
@@ -1167,12 +1183,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>BUG-020: 错误密码解密返回格式检测错误而非密码错误</t>
+          <t>模块 boundary 有测试失败（基线覆盖硬断言未命中）</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr"/>
@@ -1242,12 +1258,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>BUG-020: 错误密码解密返回格式检测错误而非密码错误</t>
+          <t>模块 boundary 有测试失败（基线覆盖硬断言未命中）</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr"/>
@@ -1318,7 +1334,7 @@
       <c r="M11" s="2" t="inlineStr"/>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr"/>
@@ -1385,7 +1401,7 @@
       <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr"/>
@@ -1452,7 +1468,7 @@
       <c r="M13" s="2" t="inlineStr"/>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr"/>
@@ -1520,7 +1536,7 @@
       <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr"/>
@@ -1587,7 +1603,7 @@
       <c r="M15" s="2" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr"/>
@@ -1652,7 +1668,7 @@
       <c r="M16" s="2" t="inlineStr"/>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr"/>
@@ -1712,15 +1728,19 @@
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+      <c r="L17" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>模块 type_filtering 有测试失败（基线覆盖硬断言未命中）</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr"/>
@@ -1780,15 +1800,19 @@
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
-      <c r="L18" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+      <c r="L18" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>模块 type_filtering 有测试失败（基线覆盖硬断言未命中）</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr"/>
@@ -1849,15 +1873,19 @@
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
-      <c r="L19" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+      <c r="L19" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>模块 type_filtering 有测试失败（基线覆盖硬断言未命中）</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr"/>
@@ -1917,15 +1945,19 @@
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+      <c r="L20" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>模块 type_filtering 有测试失败（基线覆盖硬断言未命中）</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr"/>
@@ -1992,7 +2024,7 @@
       <c r="M21" s="2" t="inlineStr"/>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr"/>
@@ -2059,7 +2091,7 @@
       <c r="M22" s="2" t="inlineStr"/>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr"/>
@@ -2126,7 +2158,7 @@
       <c r="M23" s="2" t="inlineStr"/>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr"/>
@@ -2193,7 +2225,7 @@
       <c r="M24" s="2" t="inlineStr"/>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr"/>
@@ -2260,7 +2292,7 @@
       <c r="M25" s="2" t="inlineStr"/>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr"/>
@@ -2327,7 +2359,7 @@
       <c r="M26" s="2" t="inlineStr"/>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr"/>
@@ -2392,7 +2424,7 @@
       <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr"/>
@@ -2457,7 +2489,7 @@
       <c r="M28" s="2" t="inlineStr"/>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr"/>
@@ -2522,7 +2554,7 @@
       <c r="M29" s="2" t="inlineStr"/>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr"/>
@@ -2711,7 +2743,7 @@
       <c r="M32" s="2" t="inlineStr"/>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr"/>
@@ -2776,15 +2808,19 @@
           <t>当前只测按钮可见，未执行完整还原</t>
         </is>
       </c>
-      <c r="L33" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+      <c r="L33" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>Playwright 超时 — IPC Mock 环境问题</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr"/>
@@ -2844,15 +2880,19 @@
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
-      <c r="L34" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+      <c r="L34" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>Playwright 超时 — IPC Mock 环境问题</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr"/>
@@ -2917,7 +2957,7 @@
       <c r="M35" s="2" t="inlineStr"/>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr"/>
@@ -2974,15 +3014,19 @@
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
-      <c r="L36" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+      <c r="L36" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>Playwright 超时 — IPC Mock 环境问题</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr"/>
@@ -3039,15 +3083,19 @@
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
-      <c r="L37" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+      <c r="L37" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>模块 batch_processing 有测试失败（基线覆盖硬断言未命中）</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr"/>
@@ -3104,15 +3152,19 @@
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
-      <c r="L38" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+      <c r="L38" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>模块 batch_processing 有测试失败（基线覆盖硬断言未命中）</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr"/>
@@ -3226,15 +3278,19 @@
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
-      <c r="L40" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+      <c r="L40" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>模块 batch_processing 有测试失败（基线覆盖硬断言未命中）</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr"/>
@@ -3291,15 +3347,19 @@
           <t>当前已覆盖</t>
         </is>
       </c>
-      <c r="L41" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+      <c r="L41" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>Playwright 超时 — IPC Mock 环境问题</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr"/>
@@ -3352,15 +3412,19 @@
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr"/>
-      <c r="L42" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+      <c r="L42" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>Playwright 超时 — IPC Mock 环境问题</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr"/>
@@ -3413,15 +3477,19 @@
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr"/>
-      <c r="L43" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+      <c r="L43" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>Playwright 超时 — IPC Mock 环境问题</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr"/>
@@ -3481,12 +3549,12 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>BUG-019: 工作区列表渲染竞态</t>
+          <t>Playwright 超时 — IPC Mock 环境问题</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr"/>
@@ -3546,12 +3614,12 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>BUG-019: 工作区列表渲染竞态</t>
+          <t>Playwright 超时 — IPC Mock 环境问题</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr"/>
@@ -3604,15 +3672,19 @@
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr"/>
-      <c r="L46" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+      <c r="L46" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>Playwright 超时 — IPC Mock 环境问题</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr"/>
@@ -3669,15 +3741,19 @@
           <t>test_desensitize_then_back_to_dropzone</t>
         </is>
       </c>
-      <c r="L47" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+      <c r="L47" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>Playwright 超时 — IPC Mock 环境问题</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr"/>
@@ -3730,15 +3806,19 @@
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr"/>
-      <c r="L48" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+      <c r="L48" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>Playwright 超时 — IPC Mock 环境问题</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr"/>
@@ -3791,15 +3871,19 @@
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr"/>
-      <c r="L49" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+      <c r="L49" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>Playwright 超时 — IPC Mock 环境问题</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr"/>
@@ -3870,7 +3954,7 @@
       <c r="M50" s="2" t="inlineStr"/>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr"/>
@@ -3925,7 +4009,7 @@
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>desensitize_scenario_xlsx.rs</t>
+          <t>full_pipeline_xlsx.rs</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -3933,15 +4017,19 @@
           <t>格式变体: 带+86手机号/带空格银行卡/混合文本</t>
         </is>
       </c>
-      <c r="L51" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+      <c r="L51" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>模块 full_pipeline_xlsx 有测试失败（基线覆盖硬断言未命中）</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr"/>
@@ -3996,7 +4084,7 @@
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>desensitize_scenario_xlsx.rs</t>
+          <t>full_pipeline_xlsx.rs</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4004,15 +4092,19 @@
           <t>双sheet: 合同信息+客服工单</t>
         </is>
       </c>
-      <c r="L52" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+      <c r="L52" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>模块 full_pipeline_xlsx 有测试失败（基线覆盖硬断言未命中）</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr"/>
@@ -4067,7 +4159,7 @@
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>desensitize_scenario_xlsx.rs</t>
+          <t>full_pipeline_xlsx.rs</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -4075,15 +4167,19 @@
           <t>法律: 身份证/社会信用代码/律师电话</t>
         </is>
       </c>
-      <c r="L53" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+      <c r="L53" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>模块 full_pipeline_xlsx 有测试失败（基线覆盖硬断言未命中）</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr"/>
@@ -4138,7 +4234,7 @@
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>desensitize_scenario_xlsx.rs</t>
+          <t>full_pipeline_xlsx.rs</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4146,15 +4242,19 @@
           <t>物业: 车牌号/座机号/多联系电话</t>
         </is>
       </c>
-      <c r="L54" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+      <c r="L54" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>模块 full_pipeline_xlsx 有测试失败（基线覆盖硬断言未命中）</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr"/>
@@ -4209,7 +4309,7 @@
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>desensitize_scenario_xlsx.rs</t>
+          <t>full_pipeline_xlsx.rs</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4217,15 +4317,19 @@
           <t>教育: 父母姓名/电话/工作单位</t>
         </is>
       </c>
-      <c r="L55" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+      <c r="L55" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>模块 full_pipeline_xlsx 有测试失败（基线覆盖硬断言未命中）</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr"/>
@@ -4280,7 +4384,7 @@
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>desensitize_scenario_xlsx.rs</t>
+          <t>full_pipeline_xlsx.rs</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4288,15 +4392,19 @@
           <t>医疗: 医保卡号/主治医师/诊断信息</t>
         </is>
       </c>
-      <c r="L56" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+      <c r="L56" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>模块 full_pipeline_xlsx 有测试失败（基线覆盖硬断言未命中）</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr"/>
@@ -4351,7 +4459,7 @@
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>desensitize_scenario_xlsx.rs</t>
+          <t>full_pipeline_xlsx.rs</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4359,15 +4467,19 @@
           <t>金融: 放款账号/担保人信息</t>
         </is>
       </c>
-      <c r="L57" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+      <c r="L57" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>模块 full_pipeline_xlsx 有测试失败（基线覆盖硬断言未命中）</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr"/>
@@ -4422,7 +4534,7 @@
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>desensitize_scenario_csv.rs</t>
+          <t>full_pipeline_csv.rs</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4430,15 +4542,19 @@
           <t>结构化CSV: 8人7列全字段</t>
         </is>
       </c>
-      <c r="L58" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+      <c r="L58" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>模块 full_pipeline_csv 有测试失败（基线覆盖硬断言未命中）</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr"/>
@@ -4493,7 +4609,7 @@
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>desensitize_scenario_csv.rs</t>
+          <t>full_pipeline_csv.rs</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4501,15 +4617,19 @@
           <t>6客户含身份证/收货地址</t>
         </is>
       </c>
-      <c r="L59" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+      <c r="L59" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>模块 full_pipeline_csv 有测试失败（基线覆盖硬断言未命中）</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr"/>
@@ -4564,7 +4684,7 @@
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>desensitize_scenario_csv.rs</t>
+          <t>full_pipeline_csv.rs</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4572,15 +4692,19 @@
           <t>自由文本: 敏感信息嵌入纪要正文</t>
         </is>
       </c>
-      <c r="L60" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+      <c r="L60" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>模块 full_pipeline_csv 有测试失败（基线覆盖硬断言未命中）</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr"/>
@@ -4635,7 +4759,7 @@
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>desensitize_scenario_csv.rs</t>
+          <t>full_pipeline_csv.rs</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -4643,15 +4767,19 @@
           <t>混合: 结构化+自由文本含银行卡/车牌</t>
         </is>
       </c>
-      <c r="L61" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+      <c r="L61" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>模块 full_pipeline_csv 有测试失败（基线覆盖硬断言未命中）</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr"/>
@@ -4706,7 +4834,7 @@
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>desensitize_scenario_docx.rs</t>
+          <t>full_pipeline_docx.rs</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -4714,15 +4842,19 @@
           <t>报告体: 5客户银行卡/公司信息</t>
         </is>
       </c>
-      <c r="L62" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+      <c r="L62" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>模块 full_pipeline_docx 有测试失败（基线覆盖硬断言未命中）</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr"/>
@@ -4777,7 +4909,7 @@
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>desensitize_scenario_docx.rs</t>
+          <t>full_pipeline_docx.rs</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -4785,15 +4917,19 @@
           <t>通知体: 工号/银行卡/学历背景</t>
         </is>
       </c>
-      <c r="L63" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+      <c r="L63" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>模块 full_pipeline_docx 有测试失败（基线覆盖硬断言未命中）</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr"/>
@@ -4848,7 +4984,7 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>desensitize_scenario_docx.rs</t>
+          <t>full_pipeline_docx.rs</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -4856,15 +4992,19 @@
           <t>合同体: 社会信用代码/银行账号/产权证号</t>
         </is>
       </c>
-      <c r="L64" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+      <c r="L64" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>模块 full_pipeline_docx 有测试失败（基线覆盖硬断言未命中）</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr"/>
@@ -4919,7 +5059,7 @@
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>desensitize_scenario_docx.rs</t>
+          <t>full_pipeline_docx.rs</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -4927,15 +5067,19 @@
           <t>保险: 保单号/车牌号/银行卡</t>
         </is>
       </c>
-      <c r="L65" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+      <c r="L65" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>模块 full_pipeline_docx 有测试失败（基线覆盖硬断言未命中）</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr"/>
@@ -4990,7 +5134,7 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>desensitize_scenario_docx.rs</t>
+          <t>full_pipeline_docx.rs</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -4998,15 +5142,19 @@
           <t>法律函件: 执业证号/贷款账号</t>
         </is>
       </c>
-      <c r="L66" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+      <c r="L66" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>模块 full_pipeline_docx 有测试失败（基线覆盖硬断言未命中）</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr"/>
@@ -5061,7 +5209,7 @@
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>desensitize_scenario_docx.rs</t>
+          <t>full_pipeline_docx.rs</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5069,15 +5217,19 @@
           <t>法律: 社保编号/社会信用代码</t>
         </is>
       </c>
-      <c r="L67" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+      <c r="L67" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>模块 full_pipeline_docx 有测试失败（基线覆盖硬断言未命中）</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr"/>
@@ -5132,7 +5284,7 @@
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>desensitize_scenario_docx.rs</t>
+          <t>full_pipeline_docx.rs</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5140,15 +5292,19 @@
           <t>医疗: 医保卡号/病历号</t>
         </is>
       </c>
-      <c r="L68" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+      <c r="L68" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>模块 full_pipeline_docx 有测试失败（基线覆盖硬断言未命中）</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr"/>
@@ -5203,7 +5359,7 @@
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>desensitize_scenario_docx.rs</t>
+          <t>full_pipeline_docx.rs</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5211,15 +5367,19 @@
           <t>司法: 案号/社会信用代码</t>
         </is>
       </c>
-      <c r="L69" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+      <c r="L69" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>模块 full_pipeline_docx 有测试失败（基线覆盖硬断言未命中）</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr"/>
@@ -5274,7 +5434,7 @@
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>desensitize_scenario_docx.rs</t>
+          <t>full_pipeline_docx.rs</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5282,15 +5442,19 @@
           <t>金融: 多人信息/社会信用代码</t>
         </is>
       </c>
-      <c r="L70" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+      <c r="L70" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>模块 full_pipeline_docx 有测试失败（基线覆盖硬断言未命中）</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr"/>
@@ -5344,7 +5508,7 @@
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>desensitize_english.rs</t>
+          <t>full_pipeline_csv.rs</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5352,15 +5516,19 @@
           <t>覆盖 engine/rules/en.rs</t>
         </is>
       </c>
-      <c r="L71" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="n"/>
+      <c r="L71" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>模块 full_pipeline_csv 有测试失败（基线覆盖硬断言未命中）</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>2026-04-07 14:30</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr"/>
@@ -5414,7 +5582,7 @@
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>desensitize_english.rs</t>
+          <t>full_pipeline_xlsx.rs</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5422,15 +5590,19 @@
           <t>中英规则并行检测</t>
         </is>
       </c>
-      <c r="L72" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="n"/>
+      <c r="L72" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>模块 full_pipeline_xlsx 有测试失败（基线覆盖硬断言未命中）</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>2026-04-07 14:30</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr"/>
@@ -5499,12 +5671,12 @@
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>BUG-014: GBK CSV 解析失败 (4个测试全部失败)</t>
+          <t>模块 encoding_boundary 有测试失败（基线覆盖硬断言未命中）</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>2026-04-07 14:30</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr"/>
@@ -5568,13 +5740,17 @@
       </c>
       <c r="L74" s="6" t="inlineStr">
         <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="n"/>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>模块 encoding_boundary 有测试失败（基线覆盖硬断言未命中）</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>2026-04-07 14:30</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr"/>
@@ -5638,13 +5814,17 @@
       </c>
       <c r="L75" s="6" t="inlineStr">
         <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="n"/>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>模块 encoding_boundary 有测试失败（基线覆盖硬断言未命中）</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>2026-04-07 14:30</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr"/>
@@ -5698,7 +5878,7 @@
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>desensitize_txt.rs</t>
+          <t>full_pipeline_txt.rs</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -5706,15 +5886,19 @@
           <t>补充 TXT 场景覆盖</t>
         </is>
       </c>
-      <c r="L76" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+      <c r="L76" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>模块 full_pipeline_txt 有测试失败（基线覆盖硬断言未命中）</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr"/>
@@ -5768,7 +5952,7 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>desensitize_txt.rs</t>
+          <t>full_pipeline_txt.rs</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -5776,15 +5960,19 @@
           <t>补充 TXT 场景覆盖</t>
         </is>
       </c>
-      <c r="L77" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+      <c r="L77" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>模块 full_pipeline_txt 有测试失败（基线覆盖硬断言未命中）</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr"/>
@@ -5848,13 +6036,17 @@
       </c>
       <c r="L78" s="6" t="inlineStr">
         <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="n"/>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>模块 encoding_boundary 有测试失败（基线覆盖硬断言未命中）</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>2026-04-07 14:30</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr"/>
@@ -5916,15 +6108,19 @@
           <t>验证类型过滤对 NER 的影响</t>
         </is>
       </c>
-      <c r="L79" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+      <c r="L79" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>模块 type_filtering 有测试失败（基线覆盖硬断言未命中）</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr"/>
@@ -5982,15 +6178,19 @@
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr"/>
-      <c r="L80" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+      <c r="L80" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>模块 type_filtering 有测试失败（基线覆盖硬断言未命中）</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr"/>
@@ -6048,15 +6248,19 @@
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr"/>
-      <c r="L81" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+      <c r="L81" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>模块 type_filtering 有测试失败（基线覆盖硬断言未命中）</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr"/>
@@ -6118,15 +6322,19 @@
           <t>Luhn 校验逻辑</t>
         </is>
       </c>
-      <c r="L82" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+      <c r="L82" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>模块 type_filtering 有测试失败（基线覆盖硬断言未命中）</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr"/>
@@ -6184,15 +6392,19 @@
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr"/>
-      <c r="L83" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+      <c r="L83" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>模块 type_filtering 有测试失败（基线覆盖硬断言未命中）</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr"/>
@@ -6262,7 +6474,7 @@
       <c r="M84" s="2" t="inlineStr"/>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr"/>
@@ -6328,7 +6540,7 @@
       <c r="M85" s="2" t="inlineStr"/>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr"/>
@@ -6398,7 +6610,7 @@
       <c r="M86" s="2" t="inlineStr"/>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr"/>
@@ -6469,7 +6681,7 @@
       <c r="M87" s="2" t="inlineStr"/>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr"/>
@@ -6540,7 +6752,7 @@
       <c r="M88" s="2" t="inlineStr"/>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O88" s="2" t="inlineStr"/>
@@ -6821,7 +7033,7 @@
       <c r="M92" s="2" t="inlineStr"/>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr"/>
@@ -6880,15 +7092,19 @@
           <t>i18n 测试</t>
         </is>
       </c>
-      <c r="L93" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr"/>
+      <c r="L93" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>Playwright 超时 — IPC Mock 环境问题</t>
+        </is>
+      </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr"/>
@@ -7079,7 +7295,7 @@
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>desensitize_uk.rs</t>
+          <t>full_pipeline_csv.rs</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7094,12 +7310,12 @@
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>BUG-015: UkPhone +44 161 496 0000 未识别 (baseline硬断言)</t>
+          <t>模块 full_pipeline_csv 有测试失败（基线覆盖硬断言未命中）</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>2026-04-07 14:30</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O96" s="2" t="inlineStr"/>
@@ -7155,7 +7371,7 @@
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>desensitize_us_compliance.rs</t>
+          <t>full_pipeline_xlsx.rs</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -7170,12 +7386,12 @@
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>BUG-016: DriversLicense S012-3456-7890 未识别 (9/10); baseline硬断言失败</t>
+          <t>模块 full_pipeline_xlsx 有测试失败（基线覆盖硬断言未命中）</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>2026-04-07 14:30</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O97" s="2" t="inlineStr"/>
@@ -7231,7 +7447,7 @@
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>desensitize_international.rs</t>
+          <t>full_pipeline_docx.rs</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -7246,12 +7462,12 @@
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>BUG-017: Passport 0/3未识别, DriversLicense 1/2, IBAN FR76未识别</t>
+          <t>模块 full_pipeline_docx 有测试失败（基线覆盖硬断言未命中）</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>2026-04-07 14:30</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O98" s="2" t="inlineStr"/>
@@ -7307,7 +7523,7 @@
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>desensitize_txt.rs</t>
+          <t>full_pipeline_txt.rs</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -7315,15 +7531,19 @@
           <t>IpAddress(IPv4≥14)/Phone/Email 通过; baseline 中 IPv6 引擎暂不支持(ignore)</t>
         </is>
       </c>
-      <c r="L99" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr"/>
+      <c r="L99" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>模块 full_pipeline_txt 有测试失败（基线覆盖硬断言未命中）</t>
+        </is>
+      </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O99" s="2" t="inlineStr"/>
@@ -7379,7 +7599,7 @@
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>desensitize_executive.rs</t>
+          <t>full_pipeline_docx.rs</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -7387,15 +7607,19 @@
           <t>Phone/Email/IdCard 通过; Landline(400热线)+baseline 引擎暂不支持(ignore)</t>
         </is>
       </c>
-      <c r="L100" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M100" s="2" t="inlineStr"/>
+      <c r="L100" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>模块 full_pipeline_docx 有测试失败（基线覆盖硬断言未命中）</t>
+        </is>
+      </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O100" s="2" t="inlineStr"/>
@@ -7459,15 +7683,19 @@
           <t>回归: enabled_types 参数为 None 时的默认行为</t>
         </is>
       </c>
-      <c r="L101" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M101" s="2" t="inlineStr"/>
+      <c r="L101" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>模块 type_filtering 有测试失败（基线覆盖硬断言未命中）</t>
+        </is>
+      </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O101" s="2" t="inlineStr"/>
@@ -7530,15 +7758,19 @@
           <t>防御: 前端传入脏数据的容错</t>
         </is>
       </c>
-      <c r="L102" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M102" s="2" t="inlineStr"/>
+      <c r="L102" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>模块 type_filtering 有测试失败（基线覆盖硬断言未命中）</t>
+        </is>
+      </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O102" s="2" t="inlineStr"/>
@@ -7602,15 +7834,19 @@
           <t>端到端: 类型过滤 → 脱敏 → 导出</t>
         </is>
       </c>
-      <c r="L103" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M103" s="2" t="inlineStr"/>
+      <c r="L103" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>模块 type_filtering 有测试失败（基线覆盖硬断言未命中）</t>
+        </is>
+      </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O103" s="2" t="inlineStr"/>
@@ -7681,12 +7917,12 @@
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>BUG-018: IPC mock enabled_types 为 null</t>
+          <t>Playwright 超时 — IPC Mock 环境问题</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O104" s="2" t="inlineStr"/>
@@ -7757,7 +7993,7 @@
       <c r="M105" s="2" t="inlineStr"/>
       <c r="N105" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O105" s="2" t="inlineStr"/>
@@ -7827,7 +8063,7 @@
       <c r="M106" s="2" t="inlineStr"/>
       <c r="N106" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O106" s="2" t="inlineStr"/>
@@ -7898,7 +8134,7 @@
       <c r="M107" s="2" t="inlineStr"/>
       <c r="N107" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O107" s="2" t="inlineStr"/>
@@ -7969,7 +8205,7 @@
       <c r="M108" s="2" t="inlineStr"/>
       <c r="N108" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 23:15</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O108" s="2" t="inlineStr"/>
@@ -8025,19 +8261,23 @@
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>desensitize_legal_english.rs</t>
+          <t>full_pipeline_xlsx.rs</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr"/>
-      <c r="L109" s="2" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M109" s="2" t="n"/>
+      <c r="L109" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>模块 full_pipeline_xlsx 有测试失败（基线覆盖硬断言未命中）</t>
+        </is>
+      </c>
       <c r="N109" s="2" t="inlineStr">
         <is>
-          <t>2026-04-07 14:30</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O109" s="2" t="n"/>
@@ -8093,19 +8333,23 @@
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>desensitize_legal_english.rs</t>
+          <t>full_pipeline_csv.rs</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr"/>
-      <c r="L110" s="2" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M110" s="2" t="n"/>
+      <c r="L110" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>模块 full_pipeline_csv 有测试失败（基线覆盖硬断言未命中）</t>
+        </is>
+      </c>
       <c r="N110" s="2" t="inlineStr">
         <is>
-          <t>2026-04-07 14:30</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O110" s="2" t="n"/>
@@ -8161,23 +8405,23 @@
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>desensitize_legal_english.rs</t>
+          <t>full_pipeline_docx.rs</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr"/>
-      <c r="L111" s="2" t="inlineStr">
+      <c r="L111" s="6" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>IBAN GB29未识别(硬断言); 14个软断言漏检(PersonName/Title/OrgName/Address)</t>
+          <t>模块 full_pipeline_docx 有测试失败（基线覆盖硬断言未命中）</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
         <is>
-          <t>2026-04-07 14:30</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O111" s="2" t="n"/>
@@ -8233,23 +8477,23 @@
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>desensitize_legal_english.rs</t>
+          <t>full_pipeline_docx.rs</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr"/>
-      <c r="L112" s="2" t="inlineStr">
+      <c r="L112" s="6" t="inlineStr">
         <is>
           <t>失败</t>
         </is>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>IBAN GB82未识别(硬断言); 16个软断言漏检(PersonName/Address)</t>
+          <t>模块 full_pipeline_docx 有测试失败（基线覆盖硬断言未命中）</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
         <is>
-          <t>2026-04-07 14:30</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O112" s="2" t="n"/>
@@ -8305,19 +8549,23 @@
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>desensitize_legal_english.rs</t>
+          <t>full_pipeline_csv.rs</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr"/>
-      <c r="L113" s="2" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M113" s="2" t="n"/>
+      <c r="L113" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
+          <t>模块 full_pipeline_csv 有测试失败（基线覆盖硬断言未命中）</t>
+        </is>
+      </c>
       <c r="N113" s="2" t="inlineStr">
         <is>
-          <t>2026-04-07 14:30</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O113" s="2" t="n"/>
@@ -8373,19 +8621,23 @@
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>desensitize_legal_english.rs</t>
+          <t>full_pipeline_basic.rs</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr"/>
-      <c r="L114" s="2" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M114" s="2" t="n"/>
+      <c r="L114" s="6" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t>模块 full_pipeline_basic 有测试失败（基线覆盖硬断言未命中）</t>
+        </is>
+      </c>
       <c r="N114" s="2" t="inlineStr">
         <is>
-          <t>2026-04-07 14:30</t>
+          <t>2026-04-08 14:13</t>
         </is>
       </c>
       <c r="O114" s="2" t="n"/>

--- a/e2e/testcases.xlsx
+++ b/e2e/testcases.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="测试用例" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Fixture数据基线" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="覆盖率统计" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试用例" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fixture数据基线" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖率统计" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'测试用例'!$A$1:$O$49</definedName>
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O114"/>
+  <dimension ref="A1:O170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8641,6 +8641,3646 @@
         </is>
       </c>
       <c r="O114" s="2" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>C50</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>核心管道</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>英文CSV导入结构验证: 10行 english_employee.csv 表头与数据</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>1.导入csv 2.校验headers/rows/row_count</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>8列10行, 首行James Anderson/SSN/Email正确</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>scenarios/csv/english_employee.csv</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I115" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>desensitize_english_csv.rs</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr"/>
+      <c r="L115" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="inlineStr"/>
+      <c r="N115" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:50</t>
+        </is>
+      </c>
+      <c r="O115" s="2" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>C51</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>核心管道</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>英文CSV正则识别各类型数量</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Language::En引擎</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>1.导入 2.for_language(En)检测 3.按类型计数</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>SSN≥10, UsPhone≥10, Email≥10</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>scenarios/csv/english_employee.csv</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I116" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>desensitize_english_csv.rs</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr"/>
+      <c r="L116" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="inlineStr"/>
+      <c r="N116" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:50</t>
+        </is>
+      </c>
+      <c r="O116" s="2" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>C52</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>核心管道</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>英文SSN Mask脱敏: keep_prefix=3前缀保留</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>已识别SSN</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>1.Mask策略 prefix=3 suffix=0 2.验证映射</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>前3位保留,后面含*,长度不变</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>scenarios/csv/english_employee.csv</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I117" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>desensitize_english_csv.rs</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr"/>
+      <c r="L117" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="inlineStr"/>
+      <c r="N117" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:50</t>
+        </is>
+      </c>
+      <c r="O117" s="2" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>C53</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>核心管道</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>英文SSN Replace脱敏: 假数据格式</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>已识别SSN</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>1.Replace策略 Fake风格 2.验证映射</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>replaced≠original, 策略=Replace</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>scenarios/csv/english_employee.csv</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I118" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>desensitize_english_csv.rs</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr"/>
+      <c r="L118" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M118" s="2" t="inlineStr"/>
+      <c r="N118" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:50</t>
+        </is>
+      </c>
+      <c r="O118" s="2" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>C54</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>核心管道</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>英文Email Replace脱敏: 假邮箱含@</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>已识别Email</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>1.Replace策略 2.验证映射</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>replaced≠original, 含@符号</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>scenarios/csv/english_employee.csv</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I119" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>desensitize_english_csv.rs</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr"/>
+      <c r="L119" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M119" s="2" t="inlineStr"/>
+      <c r="N119" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:50</t>
+        </is>
+      </c>
+      <c r="O119" s="2" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>C55</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>核心管道</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>英文CSV脱敏保持非敏感列: Department列不变</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Department列无敏感信息</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>1.全类型Mask脱敏 2.对比原Department列</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>Department列所有行保持原文</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>scenarios/csv/english_employee.csv</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I120" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>desensitize_english_csv.rs</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr"/>
+      <c r="L120" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M120" s="2" t="inlineStr"/>
+      <c r="N120" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:50</t>
+        </is>
+      </c>
+      <c r="O120" s="2" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>C56</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>核心管道</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>英文CSV脱敏后全文无原始敏感信息泄漏</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>全类型Replace配置</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>1.收集所有原始敏感文本 2.Replace脱敏 3.全文搜索原值</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>原文本在新文本中不存在</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>scenarios/csv/english_employee.csv</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I121" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>desensitize_english_csv.rs</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr"/>
+      <c r="L121" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M121" s="2" t="inlineStr"/>
+      <c r="N121" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:50</t>
+        </is>
+      </c>
+      <c r="O121" s="2" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>C57</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>核心管道</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>英文XLSX导入结构: us_compliance_audit.xlsx</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>1.parse_excel 2.校验结构</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>headers非空, 有数据行</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>scenarios/xlsx/us_compliance_audit.xlsx</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I122" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>desensitize_english_xlsx.rs</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr"/>
+      <c r="L122" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M122" s="2" t="inlineStr"/>
+      <c r="N122" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:50</t>
+        </is>
+      </c>
+      <c r="O122" s="2" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>C58</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>核心管道</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>英文XLSX正则识别类型: SSN或Email</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>英文引擎</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>1.检测 2.验证至少识别一种关键类型</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>items非空, 含SSN或Email</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>scenarios/xlsx/us_compliance_audit.xlsx</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I123" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>desensitize_english_xlsx.rs</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr"/>
+      <c r="L123" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M123" s="2" t="inlineStr"/>
+      <c r="N123" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:50</t>
+        </is>
+      </c>
+      <c r="O123" s="2" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>C59</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>核心管道</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>英文XLSX全类型Mask脱敏</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>已识别多种类型</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>1.SSN/UsPhone/Email/CreditCard/IBAN/ZIP全Mask 2.验证</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>所有mapping含*, replaced≠original</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>scenarios/xlsx/us_compliance_audit.xlsx</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I124" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>desensitize_english_xlsx.rs</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr"/>
+      <c r="L124" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M124" s="2" t="inlineStr"/>
+      <c r="N124" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:50</t>
+        </is>
+      </c>
+      <c r="O124" s="2" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>C60</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>核心管道</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>英文XLSX律所客户表Replace: law_firm_client_intake</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>律所客户数据</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>1.Replace策略 2.验证无泄漏</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>脱敏后原值不在文本中</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>scenarios/xlsx/law_firm_client_intake.xlsx</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I125" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>desensitize_english_xlsx.rs</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr"/>
+      <c r="L125" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M125" s="2" t="inlineStr"/>
+      <c r="N125" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:50</t>
+        </is>
+      </c>
+      <c r="O125" s="2" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>C61</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>核心管道</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>英文DOCX段落导入: attorney_engagement_letter</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>1.parse_docx 2.校验paragraphs</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>段落非空, 文本长度&gt;100</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>scenarios/docx/attorney_engagement_letter.docx</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I126" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>desensitize_english_docx.rs</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr"/>
+      <c r="L126" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M126" s="2" t="inlineStr"/>
+      <c r="N126" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:50</t>
+        </is>
+      </c>
+      <c r="O126" s="2" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>C62</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>核心管道</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>英文DOCX正则识别联系方式</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>律所协议文档</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>1.检测 2.校验含Email/UsPhone/SSN</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>至少含一种联系方式类型</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>scenarios/docx/attorney_engagement_letter.docx</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I127" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>desensitize_english_docx.rs</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr"/>
+      <c r="L127" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="inlineStr"/>
+      <c r="N127" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:50</t>
+        </is>
+      </c>
+      <c r="O127" s="2" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>C63</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>核心管道</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>英文DOCX Replace脱敏保持段落结构与样式</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>律所协议</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>1.Replace 2.对比段落数/样式</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>段落数一致, 每段style不变</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>scenarios/docx/attorney_engagement_letter.docx</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I128" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>desensitize_english_docx.rs</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr"/>
+      <c r="L128" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M128" s="2" t="inlineStr"/>
+      <c r="N128" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:50</t>
+        </is>
+      </c>
+      <c r="O128" s="2" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>C64</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>核心管道</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>英文DOCX脱敏后全文无泄漏</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>已识别敏感信息</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>1.Replace 2.全段落搜索原值</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>脱敏mapping对应原值不在新文本中</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>scenarios/docx/attorney_engagement_letter.docx</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I129" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>desensitize_english_docx.rs</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="inlineStr"/>
+      <c r="L129" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M129" s="2" t="inlineStr"/>
+      <c r="N129" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:50</t>
+        </is>
+      </c>
+      <c r="O129" s="2" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>C65</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>核心管道</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>英文DOCX诉讼备忘录脱敏: litigation_discovery_memo</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>段落+表格混合</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>1.Replace 2.验证段落发生变化</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>mappings非空, 有段落变化</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>scenarios/docx/litigation_discovery_memo.docx</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I130" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>desensitize_english_docx.rs</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr"/>
+      <c r="L130" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M130" s="2" t="inlineStr"/>
+      <c r="N130" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:50</t>
+        </is>
+      </c>
+      <c r="O130" s="2" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>C66</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>核心管道</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>英文SSN嵌入长数字串中不误匹配</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Language::En引擎</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>1.detect_text(12539-48-26714) 2.按类型筛选</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>应无匹配或符合边界规则</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>(内联文本)</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I131" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>boundary_english.rs</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr"/>
+      <c r="L131" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M131" s="2" t="inlineStr"/>
+      <c r="N131" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:50</t>
+        </is>
+      </c>
+      <c r="O131" s="2" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>C67</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>核心管道</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>英文UsPhone在长数字串中不误匹配</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Language::En引擎</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>1.detect_text(长连续数字) 2.按类型筛选</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>应无匹配或符合边界规则</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>(内联文本)</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I132" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>boundary_english.rs</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr"/>
+      <c r="L132" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M132" s="2" t="inlineStr"/>
+      <c r="N132" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:50</t>
+        </is>
+      </c>
+      <c r="O132" s="2" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>C68</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>核心管道</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>英文ZipCode在长数字串中不误匹配</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Language::En引擎</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>1.detect_text(长交易ID) 2.按类型筛选</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>应无匹配或符合边界规则</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>(内联文本)</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I133" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>boundary_english.rs</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr"/>
+      <c r="L133" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M133" s="2" t="inlineStr"/>
+      <c r="N133" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:50</t>
+        </is>
+      </c>
+      <c r="O133" s="2" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>C69</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>核心管道</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>英文引擎拒绝无效IPv4: 999.999.999.999</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Language::En引擎</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>1.detect_text(每段&gt;255) 2.按类型筛选</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>应无匹配或符合边界规则</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>(内联文本)</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I134" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>boundary_english.rs</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr"/>
+      <c r="L134" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M134" s="2" t="inlineStr"/>
+      <c r="N134" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:50</t>
+        </is>
+      </c>
+      <c r="O134" s="2" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>C70</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>核心管道</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>英文引擎Luhn校验拒绝无效信用卡</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Language::En引擎</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>1.detect_text(1234-5678-9012-3456) 2.按类型筛选</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>应无匹配或符合边界规则</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>(内联文本)</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I135" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>boundary_english.rs</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="inlineStr"/>
+      <c r="L135" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M135" s="2" t="inlineStr"/>
+      <c r="N135" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:50</t>
+        </is>
+      </c>
+      <c r="O135" s="2" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>C71</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>核心管道</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>英文纯文本零误报</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Language::En引擎</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>1.detect_text(莎士比亚风格段落) 2.按类型筛选</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>应无匹配或符合边界规则</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>(内联文本)</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I136" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>boundary_english.rs</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr"/>
+      <c r="L136" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M136" s="2" t="inlineStr"/>
+      <c r="N136" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:50</t>
+        </is>
+      </c>
+      <c r="O136" s="2" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>C72</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>核心管道</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>英文会议纪要普通文本零误报</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Language::En引擎</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>1.detect_text(Meeting minutes) 2.按类型筛选</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>应无匹配或符合边界规则</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>(内联文本)</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I137" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>boundary_english.rs</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr"/>
+      <c r="L137" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M137" s="2" t="inlineStr"/>
+      <c r="N137" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:50</t>
+        </is>
+      </c>
+      <c r="O137" s="2" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>C73</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>核心管道</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>英文空Spreadsheet/Document不崩溃</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Language::En引擎</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>1.detect_text(empty) 2.按类型筛选</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>应无匹配或符合边界规则</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>(内联文本)</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I138" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>boundary_english.rs</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr"/>
+      <c r="L138" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M138" s="2" t="inlineStr"/>
+      <c r="N138" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:50</t>
+        </is>
+      </c>
+      <c r="O138" s="2" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>C74</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>核心管道</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>英文SSN短文本Mask全部掩码</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Language::En引擎</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>1.detect_text(AB, 空字符串) 2.按类型筛选</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>应无匹配或符合边界规则</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>(内联文本)</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I139" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>boundary_english.rs</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr"/>
+      <c r="L139" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M139" s="2" t="inlineStr"/>
+      <c r="N139" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:50</t>
+        </is>
+      </c>
+      <c r="O139" s="2" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>C75</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>核心管道</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>英文Email短文本Mask边界</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Language::En引擎</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>1.detect_text(a@b.co) 2.按类型筛选</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>应无匹配或符合边界规则</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>(内联文本)</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I140" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>boundary_english.rs</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr"/>
+      <c r="L140" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M140" s="2" t="inlineStr"/>
+      <c r="N140" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:50</t>
+        </is>
+      </c>
+      <c r="O140" s="2" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>C76</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>核心管道</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>英文多类型混合识别: SSN+UsPhone+Email+ZIP</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Language::En引擎</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>1.detect_text(单句含4种) 2.按类型筛选</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>应无匹配或符合边界规则</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>(内联文本)</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I141" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>boundary_english.rs</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="inlineStr"/>
+      <c r="L141" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M141" s="2" t="inlineStr"/>
+      <c r="N141" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:50</t>
+        </is>
+      </c>
+      <c r="O141" s="2" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>C77</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>核心管道</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>英文引擎独立性: 不匹配中文手机/身份证/车牌</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Language::En引擎</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>1.detect_text(中文混入) 2.按类型筛选</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>应无匹配或符合边界规则</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>(内联文本)</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I142" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>boundary_english.rs</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="inlineStr"/>
+      <c r="L142" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M142" s="2" t="inlineStr"/>
+      <c r="N142" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:50</t>
+        </is>
+      </c>
+      <c r="O142" s="2" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>C78</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>核心管道</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>英文SSN非标准分隔符拒绝: 空格/点号</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>Language::En引擎</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>1.detect_text(539 48 2671) 2.按类型筛选</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>应无匹配或符合边界规则</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>(内联文本)</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I143" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>boundary_english.rs</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="inlineStr"/>
+      <c r="L143" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M143" s="2" t="inlineStr"/>
+      <c r="N143" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:50</t>
+        </is>
+      </c>
+      <c r="O143" s="2" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>C79</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>核心管道</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>英文Email无效格式拒绝: 缺@或缺TLD</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Language::En引擎</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>1.detect_text(john.test.com) 2.按类型筛选</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>应无匹配或符合边界规则</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>(内联文本)</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I144" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>boundary_english.rs</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr"/>
+      <c r="L144" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M144" s="2" t="inlineStr"/>
+      <c r="N144" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:50</t>
+        </is>
+      </c>
+      <c r="O144" s="2" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>K05</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>一致性替换</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>相同SSN跨行一致性替换</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>3行相同SSN</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>1.Replace 2.对比3行替换值</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>3行替换值相同, mapping.occurrences=3</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>(内联构造)</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I145" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>consistency_english.rs</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr"/>
+      <c r="L145" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M145" s="2" t="inlineStr"/>
+      <c r="N145" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:50</t>
+        </is>
+      </c>
+      <c r="O145" s="2" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>K06</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>一致性替换</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>不同SSN差异替换, 相同SSN保持一致</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>3行2个不同SSN</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>1.Replace 2.对比</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>相同值同替, 不同值异替</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>(内联构造)</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I146" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>consistency_english.rs</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="inlineStr"/>
+      <c r="L146" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M146" s="2" t="inlineStr"/>
+      <c r="N146" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:50</t>
+        </is>
+      </c>
+      <c r="O146" s="2" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>K07</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>一致性替换</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>英文Email跨列一致性: 主邮箱与CC邮箱</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>2列交叉Email</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>1.Replace PersonName 2.对比(0,0)=(1,1)</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>跨列相同Email替换值一致</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>(内联构造)</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I147" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>consistency_english.rs</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="inlineStr"/>
+      <c r="L147" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M147" s="2" t="inlineStr"/>
+      <c r="N147" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:50</t>
+        </is>
+      </c>
+      <c r="O147" s="2" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>K08</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>一致性替换</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>英文多类型混合一致性: SSN+UsPhone+Email</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>2行同数据3类型</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>1.全Replace 2.验证3列跨行一致</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>3类型各跨行一致, 产生3条映射</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>(内联构造)</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I148" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>consistency_english.rs</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="inlineStr"/>
+      <c r="L148" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M148" s="2" t="inlineStr"/>
+      <c r="N148" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:50</t>
+        </is>
+      </c>
+      <c r="O148" s="2" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>策略切换</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>英文Mask策略: SSN+UsPhone+Email组合Mask</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>english_employee.csv</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>1.3种类型Mask 2.验证*符号和长度</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>所有mapping策略=Mask含*</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>scenarios/csv/english_employee.csv</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I149" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>strategy_switching_english.rs</t>
+        </is>
+      </c>
+      <c r="K149" s="2" t="inlineStr"/>
+      <c r="L149" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M149" s="2" t="inlineStr"/>
+      <c r="N149" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:50</t>
+        </is>
+      </c>
+      <c r="O149" s="2" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>策略切换</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>英文Replace策略假数据格式合法</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>已识别SSN/UsPhone/Email/Passport</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>1.全Replace Fake 2.验证格式</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>Email含@, 所有替换≠原值</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>scenarios/csv/english_employee.csv</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I150" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>strategy_switching_english.rs</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="inlineStr"/>
+      <c r="L150" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M150" s="2" t="inlineStr"/>
+      <c r="N150" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:50</t>
+        </is>
+      </c>
+      <c r="O150" s="2" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>策略切换</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>英文Generalize地址: 保留城市+州+邮编</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>街道级地址</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>1.apply_generalize_for_language En</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>'742 Elm St, SF, CA 94102'→'San Francisco, CA 94102'</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>(内联)</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I151" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="inlineStr">
+        <is>
+          <t>strategy_switching_english.rs</t>
+        </is>
+      </c>
+      <c r="K151" s="2" t="inlineStr"/>
+      <c r="L151" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M151" s="2" t="inlineStr"/>
+      <c r="N151" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:50</t>
+        </is>
+      </c>
+      <c r="O151" s="2" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>策略切换</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>英文Generalize SSN: 保留后4位</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>11字符SSN</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>1.apply_generalize_for_language</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>'123-45-6789'→'***-**-6789'</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>(内联)</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I152" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>strategy_switching_english.rs</t>
+        </is>
+      </c>
+      <c r="K152" s="2" t="inlineStr"/>
+      <c r="L152" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M152" s="2" t="inlineStr"/>
+      <c r="N152" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:50</t>
+        </is>
+      </c>
+      <c r="O152" s="2" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>S13</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>策略切换</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>英文Generalize ZIP: 保留前3位</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>5位/ZIP+4</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>1.apply_generalize_for_language</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>'94102'→'941**', '94102-1234'→'941**'</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>(内联)</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I153" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>strategy_switching_english.rs</t>
+        </is>
+      </c>
+      <c r="K153" s="2" t="inlineStr"/>
+      <c r="L153" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M153" s="2" t="inlineStr"/>
+      <c r="N153" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:50</t>
+        </is>
+      </c>
+      <c r="O153" s="2" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>S14</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>策略切换</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>英文Generalize UK Postcode: 保留外码</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>SW1A 1AA</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>1.apply_generalize_for_language</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>'SW1A 1AA'→'SW1A ***'</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>(内联)</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I154" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>strategy_switching_english.rs</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr"/>
+      <c r="L154" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M154" s="2" t="inlineStr"/>
+      <c r="N154" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:50</t>
+        </is>
+      </c>
+      <c r="O154" s="2" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>S15</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>策略切换</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>英文Generalize Title: 5种分类</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>各级职位</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>1.CEO/Engineer/HeadOf/Manager/Assistant分别泛化</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>Senior Executive/Technical Staff/Director-Level/Management/Staff</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>(内联)</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I155" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>strategy_switching_english.rs</t>
+        </is>
+      </c>
+      <c r="K155" s="2" t="inlineStr"/>
+      <c r="L155" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M155" s="2" t="inlineStr"/>
+      <c r="N155" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:50</t>
+        </is>
+      </c>
+      <c r="O155" s="2" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>S16</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>策略切换</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>英文Generalize UsPhone: 前半保留后半*</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>(415) 293-8847</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>1.apply_generalize_for_language</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>含*, ≠原值</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>(内联)</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I156" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="inlineStr">
+        <is>
+          <t>strategy_switching_english.rs</t>
+        </is>
+      </c>
+      <c r="K156" s="2" t="inlineStr"/>
+      <c r="L156" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M156" s="2" t="inlineStr"/>
+      <c r="N156" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:50</t>
+        </is>
+      </c>
+      <c r="O156" s="2" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>S17</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>策略切换</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>英文策略切换Mask→Replace结果不同</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>同一SSN</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>1.Mask 2.Replace 3.对比同原值mapping</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>Mask结果含*, Replace结果不含*, 互不相等</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>scenarios/csv/english_employee.csv</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I157" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="inlineStr">
+        <is>
+          <t>strategy_switching_english.rs</t>
+        </is>
+      </c>
+      <c r="K157" s="2" t="inlineStr"/>
+      <c r="L157" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M157" s="2" t="inlineStr"/>
+      <c r="N157" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:50</t>
+        </is>
+      </c>
+      <c r="O157" s="2" t="n"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>S18</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>策略切换</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>英文SSN Mask参数: prefix=3/suffix=4/全掩码</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>123-45-6789</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>1.apply_mask三种参数 2.对比</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>三种参数结果不同, 全掩码为*****</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>(内联)</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I158" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="inlineStr">
+        <is>
+          <t>strategy_switching_english.rs</t>
+        </is>
+      </c>
+      <c r="K158" s="2" t="inlineStr"/>
+      <c r="L158" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M158" s="2" t="inlineStr"/>
+      <c r="N158" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:50</t>
+        </is>
+      </c>
+      <c r="O158" s="2" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>S19</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>策略切换</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>英文Email Mask参数: keep_prefix/keep_suffix</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>john@test.com</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>1.apply_mask(1,0)(2,4)</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>首字母保留/前2后4保留.com</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>(内联)</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I159" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="inlineStr">
+        <is>
+          <t>strategy_switching_english.rs</t>
+        </is>
+      </c>
+      <c r="K159" s="2" t="inlineStr"/>
+      <c r="L159" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M159" s="2" t="inlineStr"/>
+      <c r="N159" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:50</t>
+        </is>
+      </c>
+      <c r="O159" s="2" t="n"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>策略切换</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>英文Replace风格对NER类型有效(Fake/Mou/Ordinal)</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>PersonName</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>1.apply_replace三种style</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>三种风格都替换原值</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>(内联)</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I160" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="inlineStr">
+        <is>
+          <t>strategy_switching_english.rs</t>
+        </is>
+      </c>
+      <c r="K160" s="2" t="inlineStr"/>
+      <c r="L160" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M160" s="2" t="inlineStr"/>
+      <c r="N160" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:50</t>
+        </is>
+      </c>
+      <c r="O160" s="2" t="n"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>S21</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>策略切换</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>英文Replace对正则类型产生有效替换(SSN/Email/UsPhone)</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>正则识别类型</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>1.apply_replace Fake</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>SSN/Email/Phone均≠原值, Email含@</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>(内联)</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I161" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="inlineStr">
+        <is>
+          <t>strategy_switching_english.rs</t>
+        </is>
+      </c>
+      <c r="K161" s="2" t="inlineStr"/>
+      <c r="L161" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M161" s="2" t="inlineStr"/>
+      <c r="N161" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:50</t>
+        </is>
+      </c>
+      <c r="O161" s="2" t="n"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>S22</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>策略切换</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>[BUG]英文Title泛化substring子串污染bug</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>'Director of Marketing'</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>1.apply_generalize_for_language 2.期望Director-Level</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>实际返回Senior Executive, 子串'cto'污染, #[ignore]标记</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>(内联)</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I162" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="inlineStr">
+        <is>
+          <t>strategy_switching_english.rs</t>
+        </is>
+      </c>
+      <c r="K162" s="2" t="inlineStr"/>
+      <c r="L162" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M162" s="2" t="inlineStr"/>
+      <c r="N162" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17 21:32</t>
+        </is>
+      </c>
+      <c r="O162" s="2" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>T14</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>类型过滤</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>英文全类型启用识别SSN+UsPhone+Email+IBAN/Passport</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>全量扫描</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>1.检测 2.按类型计数</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>至少4种类型被识别</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>scenarios/csv/english_employee.csv</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I163" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="inlineStr">
+        <is>
+          <t>type_filtering_english.rs</t>
+        </is>
+      </c>
+      <c r="K163" s="2" t="inlineStr"/>
+      <c r="L163" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M163" s="2" t="inlineStr"/>
+      <c r="N163" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:50</t>
+        </is>
+      </c>
+      <c r="O163" s="2" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>T15</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>类型过滤</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>英文仅启用SSN: 过滤后只含Ssn</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>enabled=[Ssn]</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>1.过滤 2.类型校验</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>filtered非空, 所有item=Ssn</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>scenarios/csv/english_employee.csv</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I164" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="inlineStr">
+        <is>
+          <t>type_filtering_english.rs</t>
+        </is>
+      </c>
+      <c r="K164" s="2" t="inlineStr"/>
+      <c r="L164" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M164" s="2" t="inlineStr"/>
+      <c r="N164" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:50</t>
+        </is>
+      </c>
+      <c r="O164" s="2" t="n"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>T16</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>类型过滤</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>英文仅启用UsPhone</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>enabled=[UsPhone]</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>1.过滤 2.类型校验</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>filtered所有item=UsPhone</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>scenarios/csv/english_employee.csv</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I165" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="inlineStr">
+        <is>
+          <t>type_filtering_english.rs</t>
+        </is>
+      </c>
+      <c r="K165" s="2" t="inlineStr"/>
+      <c r="L165" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M165" s="2" t="inlineStr"/>
+      <c r="N165" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:50</t>
+        </is>
+      </c>
+      <c r="O165" s="2" t="n"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>T17</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>类型过滤</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>英文全关全开对称性</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>enabled=[]/None</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>1.空列表过滤 2.None=全量</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>空列表→0项, None→≥20项</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>scenarios/csv/english_employee.csv</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I166" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="inlineStr">
+        <is>
+          <t>type_filtering_english.rs</t>
+        </is>
+      </c>
+      <c r="K166" s="2" t="inlineStr"/>
+      <c r="L166" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M166" s="2" t="inlineStr"/>
+      <c r="N166" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:50</t>
+        </is>
+      </c>
+      <c r="O166" s="2" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>T18</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>类型过滤</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>英文禁用单类型SSN: 其他类型保留</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>all-except-Ssn</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>1.过滤 2.校验排除Ssn</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>无Ssn, UsPhone/Email保留</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>scenarios/csv/english_employee.csv</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I167" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="inlineStr">
+        <is>
+          <t>type_filtering_english.rs</t>
+        </is>
+      </c>
+      <c r="K167" s="2" t="inlineStr"/>
+      <c r="L167" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M167" s="2" t="inlineStr"/>
+      <c r="N167" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:50</t>
+        </is>
+      </c>
+      <c r="O167" s="2" t="n"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>T19</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>类型过滤</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>英文enabled_types含未知类型: 不报错仅忽略</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>[Ssn, UnknownTypeXYZ]</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>1.过滤</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>正常返回Ssn结果</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>scenarios/csv/english_employee.csv</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I168" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>type_filtering_english.rs</t>
+        </is>
+      </c>
+      <c r="K168" s="2" t="inlineStr"/>
+      <c r="L168" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M168" s="2" t="inlineStr"/>
+      <c r="N168" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:50</t>
+        </is>
+      </c>
+      <c r="O168" s="2" t="n"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>类型过滤</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>英文enabled_types=None等价全量</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>None参数</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>1.过滤 2.长度对比</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>结果数量=全量, 类型≥3</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>scenarios/csv/english_employee.csv</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I169" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>type_filtering_english.rs</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr"/>
+      <c r="L169" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="inlineStr"/>
+      <c r="N169" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:50</t>
+        </is>
+      </c>
+      <c r="O169" s="2" t="n"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>T21</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>类型过滤</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>英文过滤Ssn后脱敏: SSN列保持原文</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>排除Ssn的items</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>1.UsPhone/Email Replace 2.对比SSN列</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>SSN列所有行保持原文, Phone列被替换</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>scenarios/csv/english_employee.csv</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I170" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>type_filtering_english.rs</t>
+        </is>
+      </c>
+      <c r="K170" s="2" t="inlineStr"/>
+      <c r="L170" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M170" s="2" t="inlineStr"/>
+      <c r="N170" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17 20:50</t>
+        </is>
+      </c>
+      <c r="O170" s="2" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:O49"/>

--- a/e2e/testcases.xlsx
+++ b/e2e/testcases.xlsx
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O183"/>
+  <dimension ref="A1:O178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2600,30 +2600,22 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I30" s="8" t="inlineStr">
-        <is>
-          <t>已覆盖</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>consistency_workspace.rs</t>
-        </is>
-      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr">
         <is>
           <t>csv 中手机号每人不同，需创建含重复值的 fixture</t>
         </is>
       </c>
-      <c r="L30" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
+      <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr"/>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>2026-04-25 20:36</t>
+          <t>2026-04-04 15:28</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr"/>
@@ -2671,30 +2663,22 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I31" s="8" t="inlineStr">
-        <is>
-          <t>已覆盖</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>consistency_workspace.rs</t>
-        </is>
-      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr">
         <is>
           <t>需创建专用 fixture</t>
         </is>
       </c>
-      <c r="L31" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
+      <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr"/>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>2026-04-25 20:36</t>
+          <t>2026-04-04 15:36</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr"/>
@@ -3226,32 +3210,20 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="I39" s="4" t="inlineStr">
-        <is>
-          <t>部分覆盖</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>batch_processing.rs (#[ignore] 占位 — 需前端 batch session 状态机)</t>
-        </is>
-      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>跳过</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>#[ignore] — 需前端 batch session 状态机，后端 API 无对应概念</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-25 20:36</t>
-        </is>
-      </c>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="n"/>
+      <c r="N39" s="2" t="n"/>
       <c r="O39" s="2" t="n"/>
     </row>
     <row r="40">
@@ -12313,109 +12285,103 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>C80</t>
+          <t>B06</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>核心管道</t>
+          <t>批量处理</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>英文文档完整管道 — 三路识别 + Replace 替换全链路验证</t>
+          <t>全自动：0 敏感项文件 confirmed 且不生成导出</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>AppLanguage=En；NER 模型已加载；fixture 含至少 4 个英文 PersonName/OrgName/Address/Title</t>
+          <t>已创建工作区；输出目录已选择</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>1. 导入 attorney_engagement_letter.docx
-2. 调 detect_by_regex / detect_by_dict / detect_by_ner 三路识别
-3. 收集 NER items 中的 4 类 NER 实体（PersonName/OrgName/Address/Title）
-4. 配 Strategy::Replace { Fake } 调 apply_desensitize
-5. 检查 — 对 NER 识别到的每个实体，其原文在脱敏后文档中不再出现</t>
+          <t>1. 拖入 1 个无敏感内容的 txt 文件
+2. BatchModeSelector 选 auto（默认）
+3. 选择输出目录 → 点击开始批量
+4. 等待结果报告出现</t>
         </is>
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
-          <t>ner_items.len() &gt; 0（NER 必须有产出，不能因加载失败被吞掉）；对 NER 识别到的每一个 PersonName/OrgName/Address/Title item，脱敏后文档中不再包含 item.text 原文（即真的发生了替换）；替换后输出全部不含汉字。注：本用例验证'真的发生了替换'这一功能 bug，不验证 NER 召回率（distilbert-ner 在法律文书上召回率约 60-80%，未识别的实体保持原文是模型限制非 bug）</t>
+          <t>文件状态 confirmed；sensitiveCount=0；outputPath 为空（不生成导出文件）；结果报告中该行以 confirmed 样式呈现</t>
         </is>
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>scenarios/docx/attorney_engagement_letter.docx</t>
+          <t>batch/no_sensitive_notes.txt</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="I171" s="8" t="inlineStr">
-        <is>
-          <t>已覆盖</t>
-        </is>
-      </c>
-      <c r="J171" s="2" t="inlineStr">
-        <is>
-          <t>full_pipeline_english.rs</t>
-        </is>
-      </c>
-      <c r="K171" s="2" t="inlineStr"/>
-      <c r="L171" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M171" s="2" t="inlineStr"/>
-      <c r="N171" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-25 20:36</t>
-        </is>
-      </c>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr"/>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>useBatchAutoProcess.ts:104 的 0 敏感项短路分支</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="n"/>
+      <c r="N171" s="2" t="n"/>
       <c r="O171" s="2" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>S23</t>
+          <t>B07</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>策略切换</t>
+          <t>批量处理</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>EN Replace Fake — PersonName 输出含空格、纯 ASCII、不含汉字</t>
+          <t>全自动：混合格式批量（xlsx+csv+docx+txt）4 个全部成功</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>AppLanguage=En；NER 已识别出 4 个英文 PersonName（James Anderson 等）</t>
+          <t>已创建工作区；输出目录已选择</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>1. 导入 attorney_engagement_letter.docx
-2. 三路识别后筛 PersonName items
-3. 配 Strategy::Replace { style: Fake } 调 apply_desensitize
-4. 取每个 PersonName 替换后的输出</t>
+          <t>1. 同时拖入 batch_01.xlsx / batch_02.csv / batch_03.docx / no_sensitive_notes.txt
+2. BatchModeSelector 选 auto
+3. 选择输出目录 → 点击开始批量</t>
         </is>
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>每个替换值满足：(a) 不含汉字 (b) 含空格分隔 First Last (c) 不等于原文 (d) 不是 'John Doe'/'Jane Doe'（那是 Mou 占位）</t>
+          <t>4 个文件全部 confirmed；前 3 个有 outputPath 且导出文件存在；第 4 个 sensitiveCount=0 且无导出文件</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>scenarios/docx/attorney_engagement_letter.docx</t>
+          <t>batch/batch_01.xlsx, batch/batch_02.csv, batch/batch_03.docx, batch/no_sensitive_notes.txt</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
@@ -12423,67 +12389,62 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I172" s="8" t="inlineStr">
-        <is>
-          <t>已覆盖</t>
-        </is>
-      </c>
-      <c r="J172" s="2" t="inlineStr">
-        <is>
-          <t>strategy_switching_en_replace.rs</t>
-        </is>
-      </c>
-      <c r="K172" s="2" t="inlineStr"/>
-      <c r="L172" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M172" s="2" t="inlineStr"/>
-      <c r="N172" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-25 20:36</t>
-        </is>
-      </c>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="inlineStr"/>
+      <c r="K172" s="2" t="inlineStr">
+        <is>
+          <t>多格式混合走共享 runDesensitizePipeline</t>
+        </is>
+      </c>
+      <c r="L172" s="2" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="M172" s="2" t="n"/>
+      <c r="N172" s="2" t="n"/>
       <c r="O172" s="2" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>S24</t>
+          <t>B08</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>策略切换</t>
+          <t>批量处理</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>EN Replace Fake — OrgName 输出以 EN 字典 suffix 结尾</t>
+          <t>全自动：加密文件标记 failed 且显示加密跳过文案</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>AppLanguage=En；NER 已识别出 4 个英文 OrgName</t>
+          <t>已创建工作区；输出目录已选择</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>1. 导入 attorney_engagement_letter.docx
-2. 筛 OrgName items
-3. 配 Strategy::Replace { style: Fake }
-4. 校验每个替换值末尾的 suffix</t>
+          <t>1. 拖入 sample_encrypted.xlsx（需要密码）
+2. BatchModeSelector 选 auto
+3. 选择输出目录 → 点击开始批量</t>
         </is>
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
-          <t>每个替换值末尾 ∈ EN_ORG_SUFFIXES (Inc./Corp./LLC/LLP/Ltd./Group/Holdings/Partners/Associates/International/Co.)；不含汉字；不等于原文</t>
+          <t>文件状态 failed；errorMessage 为 i18n key hook.encryptedSkipped 的文案（"已加密，已跳过"）；结果报告显示该行为 failed 且可见重试按钮</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>scenarios/docx/attorney_engagement_letter.docx</t>
+          <t>sample_encrypted.xlsx</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
@@ -12491,135 +12452,125 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I173" s="8" t="inlineStr">
-        <is>
-          <t>已覆盖</t>
-        </is>
-      </c>
-      <c r="J173" s="2" t="inlineStr">
-        <is>
-          <t>strategy_switching_en_replace.rs</t>
-        </is>
-      </c>
-      <c r="K173" s="2" t="inlineStr"/>
-      <c r="L173" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M173" s="2" t="inlineStr"/>
-      <c r="N173" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-25 20:36</t>
-        </is>
-      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr"/>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>useBatchAutoProcess.ts:130 parseEncryptedError 分支</t>
+        </is>
+      </c>
+      <c r="L173" s="2" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="n"/>
+      <c r="N173" s="2" t="n"/>
       <c r="O173" s="2" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>S25</t>
+          <t>B09</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>策略切换</t>
+          <t>批量处理</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>EN Replace Fake — Address 输出含逗号、不含汉字</t>
+          <t>全自动：并发上限（同时 processing 不超过 MAX_CONCURRENCY=3）</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>AppLanguage=En；NER 已识别出 3 个英文 Address</t>
+          <t>已创建工作区；输出目录已选择</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>1. 导入 attorney_engagement_letter.docx
-2. 筛 Address items
-3. 配 Strategy::Replace { style: Fake }
-4. 校验每个替换值的形态</t>
+          <t>1. 拖入 5 个文件
+2. mock import_file 或 apply_desensitize 延迟 200ms 并在进入/退出时记录当前 processing 计数
+3. 开始批量
+4. 观察处理期间 processing 状态的文件数峰值</t>
         </is>
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t>每个替换值满足：(a) 不含汉字 (b) 形如 '&lt;number&gt; &lt;street&gt;, &lt;city&gt;'（含至少一个逗号分隔街道与城市）(c) 不等于原文</t>
+          <t>任一时刻 status=processing 的文件数 ≤ 3；最终 5 个文件全部 confirmed</t>
         </is>
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>scenarios/docx/attorney_engagement_letter.docx</t>
+          <t>mock</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="I174" s="8" t="inlineStr">
-        <is>
-          <t>已覆盖</t>
-        </is>
-      </c>
-      <c r="J174" s="2" t="inlineStr">
-        <is>
-          <t>strategy_switching_en_replace.rs</t>
-        </is>
-      </c>
-      <c r="K174" s="2" t="inlineStr"/>
-      <c r="L174" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M174" s="2" t="inlineStr"/>
-      <c r="N174" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-25 20:36</t>
-        </is>
-      </c>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="inlineStr"/>
+      <c r="K174" s="2" t="inlineStr">
+        <is>
+          <t>batchScheduler.ts Promise 池；types/index.ts MAX_CONCURRENCY=3</t>
+        </is>
+      </c>
+      <c r="L174" s="2" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="M174" s="2" t="n"/>
+      <c r="N174" s="2" t="n"/>
       <c r="O174" s="2" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>S26</t>
+          <t>B10</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>策略切换</t>
+          <t>批量处理</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>EN Replace Fake — Title 输出在英文 titles 池内</t>
+          <t>全自动结束后抽查：点击 confirmed tab 进入 comparison 只读视图</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>AppLanguage=En；NER 已识别出 3 种英文 Title (Senior Partner / Associate Attorney / Managing Partner)</t>
+          <t>批量全自动已结束，至少 1 个 confirmed 文件</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>1. 导入 attorney_engagement_letter.docx
-2. 筛 Title items
-3. 配 Strategy::Replace { style: Fake }
-4. 校验每个替换值</t>
+          <t>1. 批量完成后 FileQueueTabs 可见
+2. 点击任一 status=confirmed 的 tab</t>
         </is>
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
-          <t>每个替换值满足：(a) 不含汉字 (b) 在 fake_data/en/titles.json 池内（或附 wrap 后缀）(c) 不等于原文</t>
+          <t>centerView 切换为 'comparison'；currentResult 与 currentFileContent 被设置为该文件的结果；toast 显示 viewOnly 文案（只读抽查）；comparison 视图不提供导出按钮</t>
         </is>
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>scenarios/docx/attorney_engagement_letter.docx</t>
+          <t>mock</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
@@ -12627,574 +12578,215 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="I175" s="8" t="inlineStr">
-        <is>
-          <t>已覆盖</t>
-        </is>
-      </c>
-      <c r="J175" s="2" t="inlineStr">
-        <is>
-          <t>strategy_switching_en_replace.rs</t>
-        </is>
-      </c>
-      <c r="K175" s="2" t="inlineStr"/>
-      <c r="L175" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M175" s="2" t="inlineStr"/>
-      <c r="N175" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-25 20:36</t>
-        </is>
-      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr"/>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>FileQueueTabs.tsx:66-78 的 auto 模式 tab 点击分支；WorkspaceLayout.tsx:384</t>
+        </is>
+      </c>
+      <c r="L175" s="2" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="n"/>
+      <c r="N175" s="2" t="n"/>
       <c r="O175" s="2" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>S27</t>
+          <t>B11</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>策略切换</t>
+          <t>批量处理</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>EN Replace Mou — PersonName 性别轮换 John Doe / Jane Doe / John Doe 2 / Jane Doe 2</t>
+          <t>全自动：单文件也走完整批量流水线</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>AppLanguage=En；NER 已识别出 4 个英文 PersonName；Strategy::Replace 默认 consistent: true，即同一原文复用替换值，4 个 unique 原文消费 4 次 mou_name_en counter</t>
+          <t>已创建工作区</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>1. 导入 attorney_engagement_letter.docx
-2. 三路识别 → 筛 PersonName items，按 unique 原文聚合
-3. 配 Strategy::Replace { style: Mou }
-4. 取每个 unique PersonName 的替换值，组成集合</t>
+          <t>1. 拖入 1 个文件
+2. BatchModeSelector 正常显示 auto/manual 选项
+3. 选 auto → 选输出目录 → 开始批量</t>
         </is>
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>4 个 unique PersonName 替换值集合 == {'John Doe', 'Jane Doe', 'John Doe 2', 'Jane Doe 2'}；用集合断言（不依赖 NER items 出现顺序），覆盖性别二选一轮换 + 第 N 对加序号的契约</t>
+          <t>单文件同样经过 BatchModeSelector → BatchProgressBar → BatchResultReport 三阶段；结果报告显示 1 行 confirmed</t>
         </is>
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>scenarios/docx/attorney_engagement_letter.docx</t>
+          <t>batch/batch_01.xlsx</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="I176" s="8" t="inlineStr">
-        <is>
-          <t>已覆盖</t>
-        </is>
-      </c>
-      <c r="J176" s="2" t="inlineStr">
-        <is>
-          <t>strategy_switching_en_replace.rs</t>
-        </is>
-      </c>
-      <c r="K176" s="2" t="inlineStr"/>
-      <c r="L176" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M176" s="2" t="inlineStr"/>
-      <c r="N176" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-25 20:36</t>
-        </is>
-      </c>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="inlineStr"/>
+      <c r="K176" s="2" t="inlineStr">
+        <is>
+          <t>确认单文件不会走捷径跳过批量 UI</t>
+        </is>
+      </c>
+      <c r="L176" s="2" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="M176" s="2" t="n"/>
+      <c r="N176" s="2" t="n"/>
       <c r="O176" s="2" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>S28</t>
+          <t>B12</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>策略切换</t>
+          <t>批量处理</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>EN Replace Mou — OrgName 保留原文 suffix，无 suffix 兜底 Acme Co.</t>
+          <t>全自动中途修改策略：已启动的文件保留原策略，新启动的文件用新策略</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>AppLanguage=En；fixture 含 4 个 OrgName: Mitchell, Chen &amp; Park LLP / Pacific Coast Medical Center / Harrison &amp; Associates LLP / TechVenture Capital Partners；其中 LLP 命中表（第 1+2 次）、Partners 命中表（第 1 次）、Center 不在表（走兜底）</t>
+          <t>已创建工作区；输出目录已选择</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>1. 导入 attorney_engagement_letter.docx
-2. 三路识别 → 筛 OrgName items，按 unique 原文聚合
-3. 配 Strategy::Replace { style: Mou }
-4. 取每个 unique OrgName 的替换值，组成集合</t>
+          <t>1. 拖入 5 个文件，apply_desensitize mock 延迟 200ms
+2. 开始批量
+3. 首批 3 个进入 processing 后立即调用 workspaceStore.updateStrategy 修改策略
+4. 等待全部结束并断言各文件使用的策略</t>
         </is>
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
-          <t>4 个 unique OrgName 替换值集合 == {'Acme Partners', 'Acme LLP', 'Acme LLP 2', 'Acme Co.'}；TechVenture Capital Partners → 'Acme Partners'（命中 Partners suffix，counter mou_org_en_Partners=1）；Mitchell, Chen &amp; Park LLP → 'Acme LLP'（counter mou_org_en_LLP=1）；Harrison &amp; Associates LLP → 'Acme LLP 2'（counter mou_org_en_LLP=2）；Pacific Coast Medical Center → 'Acme Co.'（末尾 Center 不在 EN_ORG_SUFFIXES，走兜底，counter mou_org_en_Co.=1）</t>
+          <t>首批 3 个文件使用旧策略（进入 worker 前快照）；后续 2 个文件使用新策略（worker 内 getState() 取最新 snapshot）</t>
         </is>
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>scenarios/docx/attorney_engagement_letter.docx</t>
+          <t>mock</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="I177" s="8" t="inlineStr">
-        <is>
-          <t>已覆盖</t>
-        </is>
-      </c>
-      <c r="J177" s="2" t="inlineStr">
-        <is>
-          <t>strategy_switching_en_replace.rs</t>
-        </is>
-      </c>
-      <c r="K177" s="2" t="inlineStr"/>
-      <c r="L177" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M177" s="2" t="inlineStr"/>
-      <c r="N177" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-25 20:36</t>
-        </is>
-      </c>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="inlineStr"/>
+      <c r="K177" s="2" t="inlineStr">
+        <is>
+          <t>useBatchAutoProcess.ts:86-87 每文件 getState 的最新快照语义</t>
+        </is>
+      </c>
+      <c r="L177" s="2" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="M177" s="2" t="n"/>
+      <c r="N177" s="2" t="n"/>
       <c r="O177" s="2" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>S29</t>
+          <t>B13</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>策略切换</t>
+          <t>批量处理</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>EN Replace Mou — Address 输出 [REDACTED CITY] 序号化</t>
+          <t>全自动：批量全部失败场景，结果报告正确渲染</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>AppLanguage=En；NER 已识别出 3 个英文 Address</t>
+          <t>已创建工作区；输出目录已选择</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>1. 导入 attorney_engagement_letter.docx
-2. 筛 Address items（按出现顺序）
-3. 配 Strategy::Replace { style: Mou }
-4. 校验替换值序列</t>
+          <t>1. 拖入 5 个文件，mock import_file 每次均 throw
+2. 开始批量
+3. 等待结果报告</t>
         </is>
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>前 3 个 unique Address 替换值依次为：'[REDACTED CITY]', '[REDACTED CITY] 2', '[REDACTED CITY] 3'</t>
+          <t>5 个文件全部 failed；每行显示 errorMessage；每行可见 btn-retry-file；汇总 toast 显示 success=0 failed=5 aborted=0</t>
         </is>
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>scenarios/docx/attorney_engagement_letter.docx</t>
+          <t>mock</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="I178" s="8" t="inlineStr">
-        <is>
-          <t>已覆盖</t>
-        </is>
-      </c>
-      <c r="J178" s="2" t="inlineStr">
-        <is>
-          <t>strategy_switching_en_replace.rs</t>
-        </is>
-      </c>
-      <c r="K178" s="2" t="inlineStr"/>
-      <c r="L178" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M178" s="2" t="inlineStr"/>
-      <c r="N178" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-25 20:36</t>
-        </is>
-      </c>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="inlineStr"/>
+      <c r="K178" s="2" t="inlineStr">
+        <is>
+          <t>批量完成后的 toast 汇总逻辑；BatchResultReport 的 failed 分支渲染</t>
+        </is>
+      </c>
+      <c r="L178" s="2" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="M178" s="2" t="n"/>
+      <c r="N178" s="2" t="n"/>
       <c r="O178" s="2" t="n"/>
-    </row>
-    <row r="179">
-      <c r="A179" s="2" t="inlineStr">
-        <is>
-          <t>S30</t>
-        </is>
-      </c>
-      <c r="B179" s="2" t="inlineStr">
-        <is>
-          <t>策略切换</t>
-        </is>
-      </c>
-      <c r="C179" s="2" t="inlineStr">
-        <is>
-          <t>EN Replace Mou — Title 输出 [REDACTED TITLE] 序号化</t>
-        </is>
-      </c>
-      <c r="D179" s="2" t="inlineStr">
-        <is>
-          <t>AppLanguage=En；NER 已识别出 3 种英文 Title</t>
-        </is>
-      </c>
-      <c r="E179" s="2" t="inlineStr">
-        <is>
-          <t>1. 导入 attorney_engagement_letter.docx
-2. 筛 Title items（按 unique 原文）
-3. 配 Strategy::Replace { style: Mou }
-4. 校验替换值序列</t>
-        </is>
-      </c>
-      <c r="F179" s="2" t="inlineStr">
-        <is>
-          <t>前 3 个 unique Title 替换值依次为：'[REDACTED TITLE]', '[REDACTED TITLE] 2', '[REDACTED TITLE] 3'</t>
-        </is>
-      </c>
-      <c r="G179" s="2" t="inlineStr">
-        <is>
-          <t>scenarios/docx/attorney_engagement_letter.docx</t>
-        </is>
-      </c>
-      <c r="H179" s="2" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="I179" s="8" t="inlineStr">
-        <is>
-          <t>已覆盖</t>
-        </is>
-      </c>
-      <c r="J179" s="2" t="inlineStr">
-        <is>
-          <t>strategy_switching_en_replace.rs</t>
-        </is>
-      </c>
-      <c r="K179" s="2" t="inlineStr"/>
-      <c r="L179" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M179" s="2" t="inlineStr"/>
-      <c r="N179" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-25 20:36</t>
-        </is>
-      </c>
-      <c r="O179" s="2" t="n"/>
-    </row>
-    <row r="180">
-      <c r="A180" s="2" t="inlineStr">
-        <is>
-          <t>S31</t>
-        </is>
-      </c>
-      <c r="B180" s="2" t="inlineStr">
-        <is>
-          <t>策略切换</t>
-        </is>
-      </c>
-      <c r="C180" s="2" t="inlineStr">
-        <is>
-          <t>EN Replace Ordinal — 静默降级为 Fake，不输出 'Person A' / 'Company A' / 'Address 1' / 'Title 1'</t>
-        </is>
-      </c>
-      <c r="D180" s="2" t="inlineStr">
-        <is>
-          <t>AppLanguage=En；同 fixture 4 类 NER 实体齐全</t>
-        </is>
-      </c>
-      <c r="E180" s="2" t="inlineStr">
-        <is>
-          <t>1. 导入 attorney_engagement_letter.docx
-2. 三路识别
-3. 4 类 NER 实体配 Strategy::Replace { style: Ordinal }
-4. 取每个 NER 实体的 Ordinal 输出，断言形态等同 Fake（即降级生效，未输出 'Person A' 这类原始 ordinal 形态）</t>
-        </is>
-      </c>
-      <c r="F180" s="2" t="inlineStr">
-        <is>
-          <t>PersonName 输出含空格、不以 'Person ' 开头；OrgName 输出末尾在 EN_ORG_SUFFIXES、不以 'Company ' 开头；Address 输出含逗号、不以 'Address ' 开头；Title 输出不以 'Title ' 开头；所有输出不含汉字（即降级为 Fake 等效行为）</t>
-        </is>
-      </c>
-      <c r="G180" s="2" t="inlineStr">
-        <is>
-          <t>scenarios/docx/attorney_engagement_letter.docx</t>
-        </is>
-      </c>
-      <c r="H180" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="I180" s="8" t="inlineStr">
-        <is>
-          <t>已覆盖</t>
-        </is>
-      </c>
-      <c r="J180" s="2" t="inlineStr">
-        <is>
-          <t>strategy_switching_en_replace.rs</t>
-        </is>
-      </c>
-      <c r="K180" s="2" t="inlineStr"/>
-      <c r="L180" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M180" s="2" t="inlineStr"/>
-      <c r="N180" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-25 20:36</t>
-        </is>
-      </c>
-      <c r="O180" s="2" t="n"/>
-    </row>
-    <row r="181">
-      <c r="A181" s="2" t="inlineStr">
-        <is>
-          <t>K09</t>
-        </is>
-      </c>
-      <c r="B181" s="2" t="inlineStr">
-        <is>
-          <t>一致性替换</t>
-        </is>
-      </c>
-      <c r="C181" s="2" t="inlineStr">
-        <is>
-          <t>中英 counter 隔离 — 文档含中英混合 PersonName，counter 中独立计数 PersonName_zh + PersonName_en</t>
-        </is>
-      </c>
-      <c r="D181" s="2" t="inlineStr">
-        <is>
-          <t>AppLanguage 任意（替换走 apply_replace 内部 detect_language(text) 自动判断，不依赖 AppLanguage）；fixture mixed_bilingual.xlsx baseline 标注 4 个中文 PersonName + 4 个英文 PersonName；实际 NER 识别数依赖模型（当前 distilbert-ner 对中文识别可能为零，因此本用例的语义聚焦于'识别到的部分如何分桶'，不强求识别完整性</t>
-        </is>
-      </c>
-      <c r="E181" s="2" t="inlineStr">
-        <is>
-          <t>1. 导入 mixed_bilingual.xlsx
-2. 三路识别 → 8 个 PersonName items（4 中 4 英）
-3. 配 Strategy::Replace { style: Fake } 调 apply_desensitize（开启 consistent，绑定工作区以触发 counter 持久化）
-4. 读 workspace.replace_counters，检查 PersonName_zh 与 PersonName_en 分别计数</t>
-        </is>
-      </c>
-      <c r="F181" s="2" t="inlineStr">
-        <is>
-          <t>对 NER 识别到的每个 PersonName item：含汉字 → 进 PersonName_zh counter；纯 ASCII → 进 PersonName_en counter；两个 counter 互不串扰；PersonName_zh + PersonName_en 之和 == apply_replace 实际消费次数（即所有识别出的 unique PersonName 数）；中文 item 替换值含汉字（来自中文 fake 池）；英文 item 替换值含空格、纯 ASCII（来自英文 fake 池）；若 NER 完全识别不出某语言（如英文模型识别不到中文），对应 counter 缺失或为 0 是模型问题非 bug</t>
-        </is>
-      </c>
-      <c r="G181" s="2" t="inlineStr">
-        <is>
-          <t>scenarios/xlsx/mixed_bilingual.xlsx</t>
-        </is>
-      </c>
-      <c r="H181" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="I181" s="8" t="inlineStr">
-        <is>
-          <t>已覆盖</t>
-        </is>
-      </c>
-      <c r="J181" s="2" t="inlineStr">
-        <is>
-          <t>consistency_bilingual.rs</t>
-        </is>
-      </c>
-      <c r="K181" s="2" t="inlineStr"/>
-      <c r="L181" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M181" s="2" t="inlineStr"/>
-      <c r="N181" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-25 20:36</t>
-        </is>
-      </c>
-      <c r="O181" s="2" t="n"/>
-    </row>
-    <row r="182">
-      <c r="A182" s="2" t="inlineStr">
-        <is>
-          <t>C81</t>
-        </is>
-      </c>
-      <c r="B182" s="2" t="inlineStr">
-        <is>
-          <t>核心管道</t>
-        </is>
-      </c>
-      <c r="C182" s="2" t="inlineStr">
-        <is>
-          <t>英文文档在 NER degraded 模式下 — regex/dict 仍能识别替换 SSN/UsPhone/Email 等正则类型</t>
-        </is>
-      </c>
-      <c r="D182" s="2" t="inlineStr">
-        <is>
-          <t>测试路径：Rust 集成测试（tests/*.rs），通过构造 NerEngineState(Arc::new(Mutex::new(NerEngine::degraded()))) 注入降级引擎；AppLanguage=En；fixture 含 SSN/UsPhone/Email/CreditCard/Iban；前端 Tauri command 路径无法替换 NER 引擎，本用例不能走 Playwright e2e</t>
-        </is>
-      </c>
-      <c r="E182" s="2" t="inlineStr">
-        <is>
-          <t>1. 用 NerEngine::degraded() 替换 NER 引擎
-2. 导入 attorney_engagement_letter.docx
-3. 三路识别 — NER 应返回空，regex/dict 应正常
-4. SSN/UsPhone/Email/CreditCard/Iban 配 Strategy::Mask 调 apply_desensitize
-5. 检查脱敏后这些类型已被 Mask（带 *）</t>
-        </is>
-      </c>
-      <c r="F182" s="2" t="inlineStr">
-        <is>
-          <t>ner_items.len() == 0；regex_items.len() &gt; 0（识别到至少 SSN + UsPhone + Email）；脱敏后 SSN/UsPhone/Email 等正则类型在文档中已被 Mask 替换；PersonName/OrgName 等 NER 类型因未识别故保持原文（可接受降级行为，不是 bug）</t>
-        </is>
-      </c>
-      <c r="G182" s="2" t="inlineStr">
-        <is>
-          <t>scenarios/docx/attorney_engagement_letter.docx</t>
-        </is>
-      </c>
-      <c r="H182" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="I182" s="8" t="inlineStr">
-        <is>
-          <t>已覆盖</t>
-        </is>
-      </c>
-      <c r="J182" s="2" t="inlineStr">
-        <is>
-          <t>full_pipeline_english.rs</t>
-        </is>
-      </c>
-      <c r="K182" s="2" t="inlineStr"/>
-      <c r="L182" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M182" s="2" t="inlineStr"/>
-      <c r="N182" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-25 20:36</t>
-        </is>
-      </c>
-      <c r="O182" s="2" t="n"/>
-    </row>
-    <row r="183">
-      <c r="A183" s="2" t="inlineStr">
-        <is>
-          <t>B06</t>
-        </is>
-      </c>
-      <c r="B183" s="2" t="inlineStr">
-        <is>
-          <t>批量处理</t>
-        </is>
-      </c>
-      <c r="C183" s="2" t="inlineStr">
-        <is>
-          <t>批量脱敏 — 多个英文文档批处理后 NER 实体应被替换（覆盖用户报告的批量没替换 bug）</t>
-        </is>
-      </c>
-      <c r="D183" s="2" t="inlineStr">
-        <is>
-          <t>测试路径：Playwright e2e（e2e/tests/）— 走前端 useBatchAutoProcess Hook，更接近真实用户场景；或后端 Rust 集成测试 — 模拟批量调用 detect_by_* + apply_desensitize 串联；AppLanguage=En；NER 已加载；batch session 含 2 个英文 fixture (docx + xlsx)</t>
-        </is>
-      </c>
-      <c r="E183" s="2" t="inlineStr">
-        <is>
-          <t>1. 批量导入 attorney_engagement_letter.docx + law_firm_client_intake.xlsx
-2. 走 useBatchAutoProcess pipeline（regex + dict + NER 三路 + apply_desensitize）
-3. 检查每个文件的 desensitizeResult.summary.by_type
-4. 检查每个文件的 mappings 中包含 PersonName/OrgName 类型条目</t>
-        </is>
-      </c>
-      <c r="F183" s="2" t="inlineStr">
-        <is>
-          <t>批量结果中每个文件的 mappings 至少包含一条 PersonName 类型映射（即真的发生了 NER 替换）；脱敏后文档中所有 baseline PersonName 原文不存在；替换值符合英文 Fake 形态（含空格、纯 ASCII）；覆盖批量调用链路与单文件等价</t>
-        </is>
-      </c>
-      <c r="G183" s="2" t="inlineStr">
-        <is>
-          <t>scenarios/docx/attorney_engagement_letter.docx</t>
-        </is>
-      </c>
-      <c r="H183" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="I183" s="8" t="inlineStr">
-        <is>
-          <t>已覆盖</t>
-        </is>
-      </c>
-      <c r="J183" s="2" t="inlineStr">
-        <is>
-          <t>batch_processing.rs</t>
-        </is>
-      </c>
-      <c r="K183" s="2" t="inlineStr"/>
-      <c r="L183" s="8" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="M183" s="2" t="inlineStr"/>
-      <c r="N183" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-25 20:36</t>
-        </is>
-      </c>
-      <c r="O183" s="2" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:O49"/>

--- a/e2e/testcases.xlsx
+++ b/e2e/testcases.xlsx
@@ -12326,24 +12326,32 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I171" s="2" t="inlineStr">
-        <is>
-          <t>未覆盖</t>
-        </is>
-      </c>
-      <c r="J171" s="2" t="inlineStr"/>
+      <c r="I171" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>test_batch_auto.py</t>
+        </is>
+      </c>
       <c r="K171" s="2" t="inlineStr">
         <is>
           <t>useBatchAutoProcess.ts:104 的 0 敏感项短路分支</t>
         </is>
       </c>
-      <c r="L171" s="2" t="inlineStr">
-        <is>
-          <t>未执行</t>
-        </is>
-      </c>
-      <c r="M171" s="2" t="n"/>
-      <c r="N171" s="2" t="n"/>
+      <c r="L171" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="inlineStr"/>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-23 20:53</t>
+        </is>
+      </c>
       <c r="O171" s="2" t="n"/>
     </row>
     <row r="172">
@@ -12389,24 +12397,32 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I172" s="2" t="inlineStr">
-        <is>
-          <t>未覆盖</t>
-        </is>
-      </c>
-      <c r="J172" s="2" t="inlineStr"/>
+      <c r="I172" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>test_batch_auto.py</t>
+        </is>
+      </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
           <t>多格式混合走共享 runDesensitizePipeline</t>
         </is>
       </c>
-      <c r="L172" s="2" t="inlineStr">
-        <is>
-          <t>未执行</t>
-        </is>
-      </c>
-      <c r="M172" s="2" t="n"/>
-      <c r="N172" s="2" t="n"/>
+      <c r="L172" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M172" s="2" t="inlineStr"/>
+      <c r="N172" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-23 20:53</t>
+        </is>
+      </c>
       <c r="O172" s="2" t="n"/>
     </row>
     <row r="173">
@@ -12452,24 +12468,32 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I173" s="2" t="inlineStr">
-        <is>
-          <t>未覆盖</t>
-        </is>
-      </c>
-      <c r="J173" s="2" t="inlineStr"/>
+      <c r="I173" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>test_batch_auto.py</t>
+        </is>
+      </c>
       <c r="K173" s="2" t="inlineStr">
         <is>
           <t>useBatchAutoProcess.ts:130 parseEncryptedError 分支</t>
         </is>
       </c>
-      <c r="L173" s="2" t="inlineStr">
-        <is>
-          <t>未执行</t>
-        </is>
-      </c>
-      <c r="M173" s="2" t="n"/>
-      <c r="N173" s="2" t="n"/>
+      <c r="L173" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="inlineStr"/>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-23 20:53</t>
+        </is>
+      </c>
       <c r="O173" s="2" t="n"/>
     </row>
     <row r="174">
@@ -12516,24 +12540,32 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="I174" s="2" t="inlineStr">
-        <is>
-          <t>未覆盖</t>
-        </is>
-      </c>
-      <c r="J174" s="2" t="inlineStr"/>
+      <c r="I174" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="inlineStr">
+        <is>
+          <t>test_batch_auto.py</t>
+        </is>
+      </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
           <t>batchScheduler.ts Promise 池；types/index.ts MAX_CONCURRENCY=3</t>
         </is>
       </c>
-      <c r="L174" s="2" t="inlineStr">
-        <is>
-          <t>未执行</t>
-        </is>
-      </c>
-      <c r="M174" s="2" t="n"/>
-      <c r="N174" s="2" t="n"/>
+      <c r="L174" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M174" s="2" t="inlineStr"/>
+      <c r="N174" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-23 20:53</t>
+        </is>
+      </c>
       <c r="O174" s="2" t="n"/>
     </row>
     <row r="175">
@@ -12578,24 +12610,32 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="I175" s="2" t="inlineStr">
-        <is>
-          <t>未覆盖</t>
-        </is>
-      </c>
-      <c r="J175" s="2" t="inlineStr"/>
+      <c r="I175" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>test_batch_auto.py</t>
+        </is>
+      </c>
       <c r="K175" s="2" t="inlineStr">
         <is>
           <t>FileQueueTabs.tsx:66-78 的 auto 模式 tab 点击分支；WorkspaceLayout.tsx:384</t>
         </is>
       </c>
-      <c r="L175" s="2" t="inlineStr">
-        <is>
-          <t>未执行</t>
-        </is>
-      </c>
-      <c r="M175" s="2" t="n"/>
-      <c r="N175" s="2" t="n"/>
+      <c r="L175" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="inlineStr"/>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-23 20:53</t>
+        </is>
+      </c>
       <c r="O175" s="2" t="n"/>
     </row>
     <row r="176">
@@ -12641,24 +12681,32 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="I176" s="2" t="inlineStr">
-        <is>
-          <t>未覆盖</t>
-        </is>
-      </c>
-      <c r="J176" s="2" t="inlineStr"/>
+      <c r="I176" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="inlineStr">
+        <is>
+          <t>test_batch_auto.py</t>
+        </is>
+      </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
           <t>确认单文件不会走捷径跳过批量 UI</t>
         </is>
       </c>
-      <c r="L176" s="2" t="inlineStr">
-        <is>
-          <t>未执行</t>
-        </is>
-      </c>
-      <c r="M176" s="2" t="n"/>
-      <c r="N176" s="2" t="n"/>
+      <c r="L176" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M176" s="2" t="inlineStr"/>
+      <c r="N176" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-23 20:53</t>
+        </is>
+      </c>
       <c r="O176" s="2" t="n"/>
     </row>
     <row r="177">
@@ -12705,24 +12753,32 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="I177" s="2" t="inlineStr">
-        <is>
-          <t>未覆盖</t>
-        </is>
-      </c>
-      <c r="J177" s="2" t="inlineStr"/>
+      <c r="I177" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="inlineStr">
+        <is>
+          <t>test_batch_auto.py</t>
+        </is>
+      </c>
       <c r="K177" s="2" t="inlineStr">
         <is>
           <t>useBatchAutoProcess.ts:86-87 每文件 getState 的最新快照语义</t>
         </is>
       </c>
-      <c r="L177" s="2" t="inlineStr">
-        <is>
-          <t>未执行</t>
-        </is>
-      </c>
-      <c r="M177" s="2" t="n"/>
-      <c r="N177" s="2" t="n"/>
+      <c r="L177" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M177" s="2" t="inlineStr"/>
+      <c r="N177" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-23 20:53</t>
+        </is>
+      </c>
       <c r="O177" s="2" t="n"/>
     </row>
     <row r="178">
@@ -12768,24 +12824,32 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="I178" s="2" t="inlineStr">
-        <is>
-          <t>未覆盖</t>
-        </is>
-      </c>
-      <c r="J178" s="2" t="inlineStr"/>
+      <c r="I178" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="inlineStr">
+        <is>
+          <t>test_batch_auto.py</t>
+        </is>
+      </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
           <t>批量完成后的 toast 汇总逻辑；BatchResultReport 的 failed 分支渲染</t>
         </is>
       </c>
-      <c r="L178" s="2" t="inlineStr">
-        <is>
-          <t>未执行</t>
-        </is>
-      </c>
-      <c r="M178" s="2" t="n"/>
-      <c r="N178" s="2" t="n"/>
+      <c r="L178" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M178" s="2" t="inlineStr"/>
+      <c r="N178" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-23 20:53</t>
+        </is>
+      </c>
       <c r="O178" s="2" t="n"/>
     </row>
   </sheetData>

--- a/e2e/testcases.xlsx
+++ b/e2e/testcases.xlsx
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O170"/>
+  <dimension ref="A1:O183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -12281,6 +12281,788 @@
         </is>
       </c>
       <c r="O170" s="2" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>C80</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>核心管道</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>英文文档完整管道 — 三路识别 + Replace 替换全链路验证</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>AppLanguage=En；NER 模型已加载；fixture 含至少 4 个英文 PersonName/OrgName/Address/Title</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>1. 导入 attorney_engagement_letter.docx
+2. 调 detect_by_regex / detect_by_dict / detect_by_ner 三路识别
+3. 收集 NER items 中的 4 类 NER 实体（PersonName/OrgName/Address/Title）
+4. 配 Strategy::Replace { Fake } 调 apply_desensitize
+5. 检查 — 对 NER 识别到的每个实体，其原文在脱敏后文档中不再出现</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>ner_items.len() &gt; 0（NER 必须有产出，不能因加载失败被吞掉）；对 NER 识别到的每一个 PersonName/OrgName/Address/Title item，脱敏后文档中不再包含 item.text 原文（即真的发生了替换）；替换后输出全部不含汉字。注：本用例验证'真的发生了替换'这一功能 bug，不验证 NER 召回率（distilbert-ner 在法律文书上召回率约 60-80%，未识别的实体保持原文是模型限制非 bug）</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>scenarios/docx/attorney_engagement_letter.docx</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr"/>
+      <c r="K171" s="2" t="inlineStr"/>
+      <c r="L171" s="2" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="n"/>
+      <c r="N171" s="2" t="n"/>
+      <c r="O171" s="2" t="n"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>S23</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>策略切换</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>EN Replace Fake — PersonName 输出含空格、纯 ASCII、不含汉字</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>AppLanguage=En；NER 已识别出 4 个英文 PersonName（James Anderson 等）</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>1. 导入 attorney_engagement_letter.docx
+2. 三路识别后筛 PersonName items
+3. 配 Strategy::Replace { style: Fake } 调 apply_desensitize
+4. 取每个 PersonName 替换后的输出</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>每个替换值满足：(a) 不含汉字 (b) 含空格分隔 First Last (c) 不等于原文 (d) 不是 'John Doe'/'Jane Doe'（那是 Mou 占位）</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>scenarios/docx/attorney_engagement_letter.docx</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="inlineStr"/>
+      <c r="K172" s="2" t="inlineStr"/>
+      <c r="L172" s="2" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="M172" s="2" t="n"/>
+      <c r="N172" s="2" t="n"/>
+      <c r="O172" s="2" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>S24</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>策略切换</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>EN Replace Fake — OrgName 输出以 EN 字典 suffix 结尾</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>AppLanguage=En；NER 已识别出 4 个英文 OrgName</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>1. 导入 attorney_engagement_letter.docx
+2. 筛 OrgName items
+3. 配 Strategy::Replace { style: Fake }
+4. 校验每个替换值末尾的 suffix</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>每个替换值末尾 ∈ EN_ORG_SUFFIXES (Inc./Corp./LLC/LLP/Ltd./Group/Holdings/Partners/Associates/International/Co.)；不含汉字；不等于原文</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>scenarios/docx/attorney_engagement_letter.docx</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr"/>
+      <c r="K173" s="2" t="inlineStr"/>
+      <c r="L173" s="2" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="n"/>
+      <c r="N173" s="2" t="n"/>
+      <c r="O173" s="2" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>S25</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>策略切换</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>EN Replace Fake — Address 输出含逗号、不含汉字</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>AppLanguage=En；NER 已识别出 3 个英文 Address</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>1. 导入 attorney_engagement_letter.docx
+2. 筛 Address items
+3. 配 Strategy::Replace { style: Fake }
+4. 校验每个替换值的形态</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>每个替换值满足：(a) 不含汉字 (b) 形如 '&lt;number&gt; &lt;street&gt;, &lt;city&gt;'（含至少一个逗号分隔街道与城市）(c) 不等于原文</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>scenarios/docx/attorney_engagement_letter.docx</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="inlineStr"/>
+      <c r="K174" s="2" t="inlineStr"/>
+      <c r="L174" s="2" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="M174" s="2" t="n"/>
+      <c r="N174" s="2" t="n"/>
+      <c r="O174" s="2" t="n"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>S26</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>策略切换</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>EN Replace Fake — Title 输出在英文 titles 池内</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>AppLanguage=En；NER 已识别出 3 种英文 Title (Senior Partner / Associate Attorney / Managing Partner)</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>1. 导入 attorney_engagement_letter.docx
+2. 筛 Title items
+3. 配 Strategy::Replace { style: Fake }
+4. 校验每个替换值</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>每个替换值满足：(a) 不含汉字 (b) 在 fake_data/en/titles.json 池内（或附 wrap 后缀）(c) 不等于原文</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>scenarios/docx/attorney_engagement_letter.docx</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr"/>
+      <c r="K175" s="2" t="inlineStr"/>
+      <c r="L175" s="2" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="n"/>
+      <c r="N175" s="2" t="n"/>
+      <c r="O175" s="2" t="n"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>S27</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>策略切换</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>EN Replace Mou — PersonName 性别轮换 John Doe / Jane Doe / John Doe 2 / Jane Doe 2</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>AppLanguage=En；NER 已识别出 4 个英文 PersonName；Strategy::Replace 默认 consistent: true，即同一原文复用替换值，4 个 unique 原文消费 4 次 mou_name_en counter</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>1. 导入 attorney_engagement_letter.docx
+2. 三路识别 → 筛 PersonName items，按 unique 原文聚合
+3. 配 Strategy::Replace { style: Mou }
+4. 取每个 unique PersonName 的替换值，组成集合</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>4 个 unique PersonName 替换值集合 == {'John Doe', 'Jane Doe', 'John Doe 2', 'Jane Doe 2'}；用集合断言（不依赖 NER items 出现顺序），覆盖性别二选一轮换 + 第 N 对加序号的契约</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>scenarios/docx/attorney_engagement_letter.docx</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="inlineStr"/>
+      <c r="K176" s="2" t="inlineStr"/>
+      <c r="L176" s="2" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="M176" s="2" t="n"/>
+      <c r="N176" s="2" t="n"/>
+      <c r="O176" s="2" t="n"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>S28</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>策略切换</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>EN Replace Mou — OrgName 保留原文 suffix，无 suffix 兜底 Acme Co.</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>AppLanguage=En；fixture 含 4 个 OrgName: Mitchell, Chen &amp; Park LLP / Pacific Coast Medical Center / Harrison &amp; Associates LLP / TechVenture Capital Partners；其中 LLP 命中表（第 1+2 次）、Partners 命中表（第 1 次）、Center 不在表（走兜底）</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>1. 导入 attorney_engagement_letter.docx
+2. 三路识别 → 筛 OrgName items，按 unique 原文聚合
+3. 配 Strategy::Replace { style: Mou }
+4. 取每个 unique OrgName 的替换值，组成集合</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>4 个 unique OrgName 替换值集合 == {'Acme Partners', 'Acme LLP', 'Acme LLP 2', 'Acme Co.'}；TechVenture Capital Partners → 'Acme Partners'（命中 Partners suffix，counter mou_org_en_Partners=1）；Mitchell, Chen &amp; Park LLP → 'Acme LLP'（counter mou_org_en_LLP=1）；Harrison &amp; Associates LLP → 'Acme LLP 2'（counter mou_org_en_LLP=2）；Pacific Coast Medical Center → 'Acme Co.'（末尾 Center 不在 EN_ORG_SUFFIXES，走兜底，counter mou_org_en_Co.=1）</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>scenarios/docx/attorney_engagement_letter.docx</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="inlineStr"/>
+      <c r="K177" s="2" t="inlineStr"/>
+      <c r="L177" s="2" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="M177" s="2" t="n"/>
+      <c r="N177" s="2" t="n"/>
+      <c r="O177" s="2" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>S29</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>策略切换</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>EN Replace Mou — Address 输出 [REDACTED CITY] 序号化</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>AppLanguage=En；NER 已识别出 3 个英文 Address</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>1. 导入 attorney_engagement_letter.docx
+2. 筛 Address items（按出现顺序）
+3. 配 Strategy::Replace { style: Mou }
+4. 校验替换值序列</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>前 3 个 unique Address 替换值依次为：'[REDACTED CITY]', '[REDACTED CITY] 2', '[REDACTED CITY] 3'</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>scenarios/docx/attorney_engagement_letter.docx</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="inlineStr"/>
+      <c r="K178" s="2" t="inlineStr"/>
+      <c r="L178" s="2" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="M178" s="2" t="n"/>
+      <c r="N178" s="2" t="n"/>
+      <c r="O178" s="2" t="n"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>S30</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>策略切换</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>EN Replace Mou — Title 输出 [REDACTED TITLE] 序号化</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>AppLanguage=En；NER 已识别出 3 种英文 Title</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>1. 导入 attorney_engagement_letter.docx
+2. 筛 Title items（按 unique 原文）
+3. 配 Strategy::Replace { style: Mou }
+4. 校验替换值序列</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>前 3 个 unique Title 替换值依次为：'[REDACTED TITLE]', '[REDACTED TITLE] 2', '[REDACTED TITLE] 3'</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>scenarios/docx/attorney_engagement_letter.docx</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="J179" s="2" t="inlineStr"/>
+      <c r="K179" s="2" t="inlineStr"/>
+      <c r="L179" s="2" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="M179" s="2" t="n"/>
+      <c r="N179" s="2" t="n"/>
+      <c r="O179" s="2" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>S31</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>策略切换</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>EN Replace Ordinal — 静默降级为 Fake，不输出 'Person A' / 'Company A' / 'Address 1' / 'Title 1'</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>AppLanguage=En；同 fixture 4 类 NER 实体齐全</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>1. 导入 attorney_engagement_letter.docx
+2. 三路识别
+3. 4 类 NER 实体配 Strategy::Replace { style: Ordinal }
+4. 取每个 NER 实体的 Ordinal 输出，断言形态等同 Fake（即降级生效，未输出 'Person A' 这类原始 ordinal 形态）</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>PersonName 输出含空格、不以 'Person ' 开头；OrgName 输出末尾在 EN_ORG_SUFFIXES、不以 'Company ' 开头；Address 输出含逗号、不以 'Address ' 开头；Title 输出不以 'Title ' 开头；所有输出不含汉字（即降级为 Fake 等效行为）</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>scenarios/docx/attorney_engagement_letter.docx</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="J180" s="2" t="inlineStr"/>
+      <c r="K180" s="2" t="inlineStr"/>
+      <c r="L180" s="2" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="M180" s="2" t="n"/>
+      <c r="N180" s="2" t="n"/>
+      <c r="O180" s="2" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>K09</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>一致性替换</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>中英 counter 隔离 — 文档含中英混合 PersonName，counter 中独立计数 PersonName_zh + PersonName_en</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>AppLanguage 任意（替换走 apply_replace 内部 detect_language(text) 自动判断，不依赖 AppLanguage）；fixture mixed_bilingual.xlsx baseline 标注 4 个中文 PersonName + 4 个英文 PersonName；实际 NER 识别数依赖模型（当前 distilbert-ner 对中文识别可能为零，因此本用例的语义聚焦于'识别到的部分如何分桶'，不强求识别完整性</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>1. 导入 mixed_bilingual.xlsx
+2. 三路识别 → 8 个 PersonName items（4 中 4 英）
+3. 配 Strategy::Replace { style: Fake } 调 apply_desensitize（开启 consistent，绑定工作区以触发 counter 持久化）
+4. 读 workspace.replace_counters，检查 PersonName_zh 与 PersonName_en 分别计数</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>对 NER 识别到的每个 PersonName item：含汉字 → 进 PersonName_zh counter；纯 ASCII → 进 PersonName_en counter；两个 counter 互不串扰；PersonName_zh + PersonName_en 之和 == apply_replace 实际消费次数（即所有识别出的 unique PersonName 数）；中文 item 替换值含汉字（来自中文 fake 池）；英文 item 替换值含空格、纯 ASCII（来自英文 fake 池）；若 NER 完全识别不出某语言（如英文模型识别不到中文），对应 counter 缺失或为 0 是模型问题非 bug</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>scenarios/xlsx/mixed_bilingual.xlsx</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="inlineStr"/>
+      <c r="K181" s="2" t="inlineStr"/>
+      <c r="L181" s="2" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="M181" s="2" t="n"/>
+      <c r="N181" s="2" t="n"/>
+      <c r="O181" s="2" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>C81</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>核心管道</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>英文文档在 NER degraded 模式下 — regex/dict 仍能识别替换 SSN/UsPhone/Email 等正则类型</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>测试路径：Rust 集成测试（tests/*.rs），通过构造 NerEngineState(Arc::new(Mutex::new(NerEngine::degraded()))) 注入降级引擎；AppLanguage=En；fixture 含 SSN/UsPhone/Email/CreditCard/Iban；前端 Tauri command 路径无法替换 NER 引擎，本用例不能走 Playwright e2e</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>1. 用 NerEngine::degraded() 替换 NER 引擎
+2. 导入 attorney_engagement_letter.docx
+3. 三路识别 — NER 应返回空，regex/dict 应正常
+4. SSN/UsPhone/Email/CreditCard/Iban 配 Strategy::Mask 调 apply_desensitize
+5. 检查脱敏后这些类型已被 Mask（带 *）</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>ner_items.len() == 0；regex_items.len() &gt; 0（识别到至少 SSN + UsPhone + Email）；脱敏后 SSN/UsPhone/Email 等正则类型在文档中已被 Mask 替换；PersonName/OrgName 等 NER 类型因未识别故保持原文（可接受降级行为，不是 bug）</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>scenarios/docx/attorney_engagement_letter.docx</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="J182" s="2" t="inlineStr"/>
+      <c r="K182" s="2" t="inlineStr"/>
+      <c r="L182" s="2" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="M182" s="2" t="n"/>
+      <c r="N182" s="2" t="n"/>
+      <c r="O182" s="2" t="n"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>B06</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>批量处理</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>批量脱敏 — 多个英文文档批处理后 NER 实体应被替换（覆盖用户报告的批量没替换 bug）</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>测试路径：Playwright e2e（e2e/tests/）— 走前端 useBatchAutoProcess Hook，更接近真实用户场景；或后端 Rust 集成测试 — 模拟批量调用 detect_by_* + apply_desensitize 串联；AppLanguage=En；NER 已加载；batch session 含 2 个英文 fixture (docx + xlsx)</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>1. 批量导入 attorney_engagement_letter.docx + law_firm_client_intake.xlsx
+2. 走 useBatchAutoProcess pipeline（regex + dict + NER 三路 + apply_desensitize）
+3. 检查每个文件的 desensitizeResult.summary.by_type
+4. 检查每个文件的 mappings 中包含 PersonName/OrgName 类型条目</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>批量结果中每个文件的 mappings 至少包含一条 PersonName 类型映射（即真的发生了 NER 替换）；脱敏后文档中所有 baseline PersonName 原文不存在；替换值符合英文 Fake 形态（含空格、纯 ASCII）；覆盖批量调用链路与单文件等价</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>scenarios/docx/attorney_engagement_letter.docx</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="inlineStr">
+        <is>
+          <t>未覆盖</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="inlineStr"/>
+      <c r="K183" s="2" t="inlineStr"/>
+      <c r="L183" s="2" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="M183" s="2" t="n"/>
+      <c r="N183" s="2" t="n"/>
+      <c r="O183" s="2" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:O49"/>

--- a/e2e/testcases.xlsx
+++ b/e2e/testcases.xlsx
@@ -2600,22 +2600,30 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I30" s="6" t="inlineStr">
-        <is>
-          <t>未覆盖</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr"/>
+      <c r="I30" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>consistency_workspace.rs</t>
+        </is>
+      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
           <t>csv 中手机号每人不同，需创建含重复值的 fixture</t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr"/>
+      <c r="L30" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M30" s="2" t="inlineStr"/>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:28</t>
+          <t>2026-04-25 20:36</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr"/>
@@ -2663,22 +2671,30 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I31" s="6" t="inlineStr">
-        <is>
-          <t>未覆盖</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr"/>
+      <c r="I31" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>consistency_workspace.rs</t>
+        </is>
+      </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
           <t>需创建专用 fixture</t>
         </is>
       </c>
-      <c r="L31" s="2" t="inlineStr"/>
+      <c r="L31" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
       <c r="M31" s="2" t="inlineStr"/>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>2026-04-04 15:36</t>
+          <t>2026-04-25 20:36</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr"/>
@@ -3210,20 +3226,32 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="I39" s="6" t="inlineStr">
-        <is>
-          <t>未覆盖</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr"/>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>部分覆盖</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>batch_processing.rs (#[ignore] 占位 — 需前端 batch session 状态机)</t>
+        </is>
+      </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>未执行</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="n"/>
-      <c r="N39" s="2" t="n"/>
+          <t>跳过</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>#[ignore] — 需前端 batch session 状态机，后端 API 无对应概念</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-25 20:36</t>
+        </is>
+      </c>
       <c r="O39" s="2" t="n"/>
     </row>
     <row r="40">
@@ -12327,20 +12355,28 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I171" s="2" t="inlineStr">
-        <is>
-          <t>未覆盖</t>
-        </is>
-      </c>
-      <c r="J171" s="2" t="inlineStr"/>
+      <c r="I171" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>full_pipeline_english.rs</t>
+        </is>
+      </c>
       <c r="K171" s="2" t="inlineStr"/>
-      <c r="L171" s="2" t="inlineStr">
-        <is>
-          <t>未执行</t>
-        </is>
-      </c>
-      <c r="M171" s="2" t="n"/>
-      <c r="N171" s="2" t="n"/>
+      <c r="L171" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="inlineStr"/>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-25 20:36</t>
+        </is>
+      </c>
       <c r="O171" s="2" t="n"/>
     </row>
     <row r="172">
@@ -12387,20 +12423,28 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I172" s="2" t="inlineStr">
-        <is>
-          <t>未覆盖</t>
-        </is>
-      </c>
-      <c r="J172" s="2" t="inlineStr"/>
+      <c r="I172" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>strategy_switching_en_replace.rs</t>
+        </is>
+      </c>
       <c r="K172" s="2" t="inlineStr"/>
-      <c r="L172" s="2" t="inlineStr">
-        <is>
-          <t>未执行</t>
-        </is>
-      </c>
-      <c r="M172" s="2" t="n"/>
-      <c r="N172" s="2" t="n"/>
+      <c r="L172" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M172" s="2" t="inlineStr"/>
+      <c r="N172" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-25 20:36</t>
+        </is>
+      </c>
       <c r="O172" s="2" t="n"/>
     </row>
     <row r="173">
@@ -12447,20 +12491,28 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I173" s="2" t="inlineStr">
-        <is>
-          <t>未覆盖</t>
-        </is>
-      </c>
-      <c r="J173" s="2" t="inlineStr"/>
+      <c r="I173" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>strategy_switching_en_replace.rs</t>
+        </is>
+      </c>
       <c r="K173" s="2" t="inlineStr"/>
-      <c r="L173" s="2" t="inlineStr">
-        <is>
-          <t>未执行</t>
-        </is>
-      </c>
-      <c r="M173" s="2" t="n"/>
-      <c r="N173" s="2" t="n"/>
+      <c r="L173" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="inlineStr"/>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-25 20:36</t>
+        </is>
+      </c>
       <c r="O173" s="2" t="n"/>
     </row>
     <row r="174">
@@ -12507,20 +12559,28 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I174" s="2" t="inlineStr">
-        <is>
-          <t>未覆盖</t>
-        </is>
-      </c>
-      <c r="J174" s="2" t="inlineStr"/>
+      <c r="I174" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="inlineStr">
+        <is>
+          <t>strategy_switching_en_replace.rs</t>
+        </is>
+      </c>
       <c r="K174" s="2" t="inlineStr"/>
-      <c r="L174" s="2" t="inlineStr">
-        <is>
-          <t>未执行</t>
-        </is>
-      </c>
-      <c r="M174" s="2" t="n"/>
-      <c r="N174" s="2" t="n"/>
+      <c r="L174" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M174" s="2" t="inlineStr"/>
+      <c r="N174" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-25 20:36</t>
+        </is>
+      </c>
       <c r="O174" s="2" t="n"/>
     </row>
     <row r="175">
@@ -12567,20 +12627,28 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="I175" s="2" t="inlineStr">
-        <is>
-          <t>未覆盖</t>
-        </is>
-      </c>
-      <c r="J175" s="2" t="inlineStr"/>
+      <c r="I175" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>strategy_switching_en_replace.rs</t>
+        </is>
+      </c>
       <c r="K175" s="2" t="inlineStr"/>
-      <c r="L175" s="2" t="inlineStr">
-        <is>
-          <t>未执行</t>
-        </is>
-      </c>
-      <c r="M175" s="2" t="n"/>
-      <c r="N175" s="2" t="n"/>
+      <c r="L175" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="inlineStr"/>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-25 20:36</t>
+        </is>
+      </c>
       <c r="O175" s="2" t="n"/>
     </row>
     <row r="176">
@@ -12627,20 +12695,28 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I176" s="2" t="inlineStr">
-        <is>
-          <t>未覆盖</t>
-        </is>
-      </c>
-      <c r="J176" s="2" t="inlineStr"/>
+      <c r="I176" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="inlineStr">
+        <is>
+          <t>strategy_switching_en_replace.rs</t>
+        </is>
+      </c>
       <c r="K176" s="2" t="inlineStr"/>
-      <c r="L176" s="2" t="inlineStr">
-        <is>
-          <t>未执行</t>
-        </is>
-      </c>
-      <c r="M176" s="2" t="n"/>
-      <c r="N176" s="2" t="n"/>
+      <c r="L176" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M176" s="2" t="inlineStr"/>
+      <c r="N176" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-25 20:36</t>
+        </is>
+      </c>
       <c r="O176" s="2" t="n"/>
     </row>
     <row r="177">
@@ -12687,20 +12763,28 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I177" s="2" t="inlineStr">
-        <is>
-          <t>未覆盖</t>
-        </is>
-      </c>
-      <c r="J177" s="2" t="inlineStr"/>
+      <c r="I177" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="inlineStr">
+        <is>
+          <t>strategy_switching_en_replace.rs</t>
+        </is>
+      </c>
       <c r="K177" s="2" t="inlineStr"/>
-      <c r="L177" s="2" t="inlineStr">
-        <is>
-          <t>未执行</t>
-        </is>
-      </c>
-      <c r="M177" s="2" t="n"/>
-      <c r="N177" s="2" t="n"/>
+      <c r="L177" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M177" s="2" t="inlineStr"/>
+      <c r="N177" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-25 20:36</t>
+        </is>
+      </c>
       <c r="O177" s="2" t="n"/>
     </row>
     <row r="178">
@@ -12747,20 +12831,28 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="I178" s="2" t="inlineStr">
-        <is>
-          <t>未覆盖</t>
-        </is>
-      </c>
-      <c r="J178" s="2" t="inlineStr"/>
+      <c r="I178" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="inlineStr">
+        <is>
+          <t>strategy_switching_en_replace.rs</t>
+        </is>
+      </c>
       <c r="K178" s="2" t="inlineStr"/>
-      <c r="L178" s="2" t="inlineStr">
-        <is>
-          <t>未执行</t>
-        </is>
-      </c>
-      <c r="M178" s="2" t="n"/>
-      <c r="N178" s="2" t="n"/>
+      <c r="L178" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M178" s="2" t="inlineStr"/>
+      <c r="N178" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-25 20:36</t>
+        </is>
+      </c>
       <c r="O178" s="2" t="n"/>
     </row>
     <row r="179">
@@ -12807,20 +12899,28 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="I179" s="2" t="inlineStr">
-        <is>
-          <t>未覆盖</t>
-        </is>
-      </c>
-      <c r="J179" s="2" t="inlineStr"/>
+      <c r="I179" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J179" s="2" t="inlineStr">
+        <is>
+          <t>strategy_switching_en_replace.rs</t>
+        </is>
+      </c>
       <c r="K179" s="2" t="inlineStr"/>
-      <c r="L179" s="2" t="inlineStr">
-        <is>
-          <t>未执行</t>
-        </is>
-      </c>
-      <c r="M179" s="2" t="n"/>
-      <c r="N179" s="2" t="n"/>
+      <c r="L179" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M179" s="2" t="inlineStr"/>
+      <c r="N179" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-25 20:36</t>
+        </is>
+      </c>
       <c r="O179" s="2" t="n"/>
     </row>
     <row r="180">
@@ -12867,20 +12967,28 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I180" s="2" t="inlineStr">
-        <is>
-          <t>未覆盖</t>
-        </is>
-      </c>
-      <c r="J180" s="2" t="inlineStr"/>
+      <c r="I180" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J180" s="2" t="inlineStr">
+        <is>
+          <t>strategy_switching_en_replace.rs</t>
+        </is>
+      </c>
       <c r="K180" s="2" t="inlineStr"/>
-      <c r="L180" s="2" t="inlineStr">
-        <is>
-          <t>未执行</t>
-        </is>
-      </c>
-      <c r="M180" s="2" t="n"/>
-      <c r="N180" s="2" t="n"/>
+      <c r="L180" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M180" s="2" t="inlineStr"/>
+      <c r="N180" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-25 20:36</t>
+        </is>
+      </c>
       <c r="O180" s="2" t="n"/>
     </row>
     <row r="181">
@@ -12927,20 +13035,28 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I181" s="2" t="inlineStr">
-        <is>
-          <t>未覆盖</t>
-        </is>
-      </c>
-      <c r="J181" s="2" t="inlineStr"/>
+      <c r="I181" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="inlineStr">
+        <is>
+          <t>consistency_bilingual.rs</t>
+        </is>
+      </c>
       <c r="K181" s="2" t="inlineStr"/>
-      <c r="L181" s="2" t="inlineStr">
-        <is>
-          <t>未执行</t>
-        </is>
-      </c>
-      <c r="M181" s="2" t="n"/>
-      <c r="N181" s="2" t="n"/>
+      <c r="L181" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M181" s="2" t="inlineStr"/>
+      <c r="N181" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-25 20:36</t>
+        </is>
+      </c>
       <c r="O181" s="2" t="n"/>
     </row>
     <row r="182">
@@ -12988,20 +13104,28 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I182" s="2" t="inlineStr">
-        <is>
-          <t>未覆盖</t>
-        </is>
-      </c>
-      <c r="J182" s="2" t="inlineStr"/>
+      <c r="I182" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J182" s="2" t="inlineStr">
+        <is>
+          <t>full_pipeline_english.rs</t>
+        </is>
+      </c>
       <c r="K182" s="2" t="inlineStr"/>
-      <c r="L182" s="2" t="inlineStr">
-        <is>
-          <t>未执行</t>
-        </is>
-      </c>
-      <c r="M182" s="2" t="n"/>
-      <c r="N182" s="2" t="n"/>
+      <c r="L182" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M182" s="2" t="inlineStr"/>
+      <c r="N182" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-25 20:36</t>
+        </is>
+      </c>
       <c r="O182" s="2" t="n"/>
     </row>
     <row r="183">
@@ -13048,20 +13172,28 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I183" s="2" t="inlineStr">
-        <is>
-          <t>未覆盖</t>
-        </is>
-      </c>
-      <c r="J183" s="2" t="inlineStr"/>
+      <c r="I183" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="inlineStr">
+        <is>
+          <t>batch_processing.rs</t>
+        </is>
+      </c>
       <c r="K183" s="2" t="inlineStr"/>
-      <c r="L183" s="2" t="inlineStr">
-        <is>
-          <t>未执行</t>
-        </is>
-      </c>
-      <c r="M183" s="2" t="n"/>
-      <c r="N183" s="2" t="n"/>
+      <c r="L183" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M183" s="2" t="inlineStr"/>
+      <c r="N183" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-25 20:36</t>
+        </is>
+      </c>
       <c r="O183" s="2" t="n"/>
     </row>
   </sheetData>

--- a/e2e/testcases.xlsx
+++ b/e2e/testcases.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试用例" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fixture数据基线" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖率统计" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="测试用例" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Fixture数据基线" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="覆盖率统计" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'测试用例'!$A$1:$O$49</definedName>
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O178"/>
+  <dimension ref="A1:O191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -12851,6 +12851,892 @@
         </is>
       </c>
       <c r="O178" s="2" t="n"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>C80</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>核心管道</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>英文文档完整管道 — 三路识别 + Replace 替换全链路验证</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>AppLanguage=En；NER 模型已加载；fixture 含至少 4 个英文 PersonName/OrgName/Address/Title</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>1. 导入 attorney_engagement_letter.docx
+2. 调 detect_by_regex / detect_by_dict / detect_by_ner 三路识别
+3. 收集 NER items 中的 4 类 NER 实体（PersonName/OrgName/Address/Title）
+4. 配 Strategy::Replace { Fake } 调 apply_desensitize
+5. 检查 — 对 NER 识别到的每个实体，其原文在脱敏后文档中不再出现</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>ner_items.len() &gt; 0（NER 必须有产出，不能因加载失败被吞掉）；对 NER 识别到的每一个 PersonName/OrgName/Address/Title item，脱敏后文档中不再包含 item.text 原文（即真的发生了替换）；替换后输出全部不含汉字。注：本用例验证'真的发生了替换'这一功能 bug，不验证 NER 召回率（distilbert-ner 在法律文书上召回率约 60-80%，未识别的实体保持原文是模型限制非 bug）</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>scenarios/docx/attorney_engagement_letter.docx</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I179" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J179" s="2" t="inlineStr">
+        <is>
+          <t>full_pipeline_english.rs</t>
+        </is>
+      </c>
+      <c r="K179" s="2" t="n"/>
+      <c r="L179" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M179" s="2" t="n"/>
+      <c r="N179" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-25 20:36</t>
+        </is>
+      </c>
+      <c r="O179" s="2" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>S23</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>策略切换</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>EN Replace Fake — PersonName 输出含空格、纯 ASCII、不含汉字</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>AppLanguage=En；NER 已识别出 4 个英文 PersonName（James Anderson 等）</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>1. 导入 attorney_engagement_letter.docx
+2. 三路识别后筛 PersonName items
+3. 配 Strategy::Replace { style: Fake } 调 apply_desensitize
+4. 取每个 PersonName 替换后的输出</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>每个替换值满足：(a) 不含汉字 (b) 含空格分隔 First Last (c) 不等于原文 (d) 不是 'John Doe'/'Jane Doe'（那是 Mou 占位）</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>scenarios/docx/attorney_engagement_letter.docx</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I180" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J180" s="2" t="inlineStr">
+        <is>
+          <t>strategy_switching_en_replace.rs</t>
+        </is>
+      </c>
+      <c r="K180" s="2" t="n"/>
+      <c r="L180" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M180" s="2" t="n"/>
+      <c r="N180" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-25 20:36</t>
+        </is>
+      </c>
+      <c r="O180" s="2" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>S24</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>策略切换</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>EN Replace Fake — OrgName 输出以 EN 字典 suffix 结尾</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>AppLanguage=En；NER 已识别出 4 个英文 OrgName</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>1. 导入 attorney_engagement_letter.docx
+2. 筛 OrgName items
+3. 配 Strategy::Replace { style: Fake }
+4. 校验每个替换值末尾的 suffix</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>每个替换值末尾 ∈ EN_ORG_SUFFIXES (Inc./Corp./LLC/LLP/Ltd./Group/Holdings/Partners/Associates/International/Co.)；不含汉字；不等于原文</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>scenarios/docx/attorney_engagement_letter.docx</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I181" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="inlineStr">
+        <is>
+          <t>strategy_switching_en_replace.rs</t>
+        </is>
+      </c>
+      <c r="K181" s="2" t="n"/>
+      <c r="L181" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M181" s="2" t="n"/>
+      <c r="N181" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-25 20:36</t>
+        </is>
+      </c>
+      <c r="O181" s="2" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>S25</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>策略切换</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>EN Replace Fake — Address 输出含逗号、不含汉字</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>AppLanguage=En；NER 已识别出 3 个英文 Address</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>1. 导入 attorney_engagement_letter.docx
+2. 筛 Address items
+3. 配 Strategy::Replace { style: Fake }
+4. 校验每个替换值的形态</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>每个替换值满足：(a) 不含汉字 (b) 形如 '&lt;number&gt; &lt;street&gt;, &lt;city&gt;'（含至少一个逗号分隔街道与城市）(c) 不等于原文</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>scenarios/docx/attorney_engagement_letter.docx</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I182" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J182" s="2" t="inlineStr">
+        <is>
+          <t>strategy_switching_en_replace.rs</t>
+        </is>
+      </c>
+      <c r="K182" s="2" t="n"/>
+      <c r="L182" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M182" s="2" t="n"/>
+      <c r="N182" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-25 20:36</t>
+        </is>
+      </c>
+      <c r="O182" s="2" t="n"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>S26</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>策略切换</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>EN Replace Fake — Title 输出在英文 titles 池内</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>AppLanguage=En；NER 已识别出 3 种英文 Title (Senior Partner / Associate Attorney / Managing Partner)</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>1. 导入 attorney_engagement_letter.docx
+2. 筛 Title items
+3. 配 Strategy::Replace { style: Fake }
+4. 校验每个替换值</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>每个替换值满足：(a) 不含汉字 (b) 在 fake_data/en/titles.json 池内（或附 wrap 后缀）(c) 不等于原文</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>scenarios/docx/attorney_engagement_letter.docx</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I183" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="inlineStr">
+        <is>
+          <t>strategy_switching_en_replace.rs</t>
+        </is>
+      </c>
+      <c r="K183" s="2" t="n"/>
+      <c r="L183" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M183" s="2" t="n"/>
+      <c r="N183" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-25 20:36</t>
+        </is>
+      </c>
+      <c r="O183" s="2" t="n"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>S27</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>策略切换</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>EN Replace Mou — PersonName 性别轮换 John Doe / Jane Doe / John Doe 2 / Jane Doe 2</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>AppLanguage=En；NER 已识别出 4 个英文 PersonName；Strategy::Replace 默认 consistent: true，即同一原文复用替换值，4 个 unique 原文消费 4 次 mou_name_en counter</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>1. 导入 attorney_engagement_letter.docx
+2. 三路识别 → 筛 PersonName items，按 unique 原文聚合
+3. 配 Strategy::Replace { style: Mou }
+4. 取每个 unique PersonName 的替换值，组成集合</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>4 个 unique PersonName 替换值集合 == {'John Doe', 'Jane Doe', 'John Doe 2', 'Jane Doe 2'}；用集合断言（不依赖 NER items 出现顺序），覆盖性别二选一轮换 + 第 N 对加序号的契约</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>scenarios/docx/attorney_engagement_letter.docx</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I184" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J184" s="2" t="inlineStr">
+        <is>
+          <t>strategy_switching_en_replace.rs</t>
+        </is>
+      </c>
+      <c r="K184" s="2" t="n"/>
+      <c r="L184" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M184" s="2" t="n"/>
+      <c r="N184" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-25 20:36</t>
+        </is>
+      </c>
+      <c r="O184" s="2" t="n"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>S28</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>策略切换</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>EN Replace Mou — OrgName 保留原文 suffix，无 suffix 兜底 Acme Co.</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>AppLanguage=En；fixture 含 4 个 OrgName: Mitchell, Chen &amp; Park LLP / Pacific Coast Medical Center / Harrison &amp; Associates LLP / TechVenture Capital Partners；其中 LLP 命中表（第 1+2 次）、Partners 命中表（第 1 次）、Center 不在表（走兜底）</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>1. 导入 attorney_engagement_letter.docx
+2. 三路识别 → 筛 OrgName items，按 unique 原文聚合
+3. 配 Strategy::Replace { style: Mou }
+4. 取每个 unique OrgName 的替换值，组成集合</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>4 个 unique OrgName 替换值集合 == {'Acme Partners', 'Acme LLP', 'Acme LLP 2', 'Acme Co.'}；TechVenture Capital Partners → 'Acme Partners'（命中 Partners suffix，counter mou_org_en_Partners=1）；Mitchell, Chen &amp; Park LLP → 'Acme LLP'（counter mou_org_en_LLP=1）；Harrison &amp; Associates LLP → 'Acme LLP 2'（counter mou_org_en_LLP=2）；Pacific Coast Medical Center → 'Acme Co.'（末尾 Center 不在 EN_ORG_SUFFIXES，走兜底，counter mou_org_en_Co.=1）</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>scenarios/docx/attorney_engagement_letter.docx</t>
+        </is>
+      </c>
+      <c r="H185" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I185" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J185" s="2" t="inlineStr">
+        <is>
+          <t>strategy_switching_en_replace.rs</t>
+        </is>
+      </c>
+      <c r="K185" s="2" t="n"/>
+      <c r="L185" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M185" s="2" t="n"/>
+      <c r="N185" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-25 20:36</t>
+        </is>
+      </c>
+      <c r="O185" s="2" t="n"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>S29</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>策略切换</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>EN Replace Mou — Address 输出 [REDACTED CITY] 序号化</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>AppLanguage=En；NER 已识别出 3 个英文 Address</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>1. 导入 attorney_engagement_letter.docx
+2. 筛 Address items（按出现顺序）
+3. 配 Strategy::Replace { style: Mou }
+4. 校验替换值序列</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>前 3 个 unique Address 替换值依次为：'[REDACTED CITY]', '[REDACTED CITY] 2', '[REDACTED CITY] 3'</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t>scenarios/docx/attorney_engagement_letter.docx</t>
+        </is>
+      </c>
+      <c r="H186" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I186" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J186" s="2" t="inlineStr">
+        <is>
+          <t>strategy_switching_en_replace.rs</t>
+        </is>
+      </c>
+      <c r="K186" s="2" t="n"/>
+      <c r="L186" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M186" s="2" t="n"/>
+      <c r="N186" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-25 20:36</t>
+        </is>
+      </c>
+      <c r="O186" s="2" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>S30</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>策略切换</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>EN Replace Mou — Title 输出 [REDACTED TITLE] 序号化</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>AppLanguage=En；NER 已识别出 3 种英文 Title</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>1. 导入 attorney_engagement_letter.docx
+2. 筛 Title items（按 unique 原文）
+3. 配 Strategy::Replace { style: Mou }
+4. 校验替换值序列</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>前 3 个 unique Title 替换值依次为：'[REDACTED TITLE]', '[REDACTED TITLE] 2', '[REDACTED TITLE] 3'</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t>scenarios/docx/attorney_engagement_letter.docx</t>
+        </is>
+      </c>
+      <c r="H187" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I187" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J187" s="2" t="inlineStr">
+        <is>
+          <t>strategy_switching_en_replace.rs</t>
+        </is>
+      </c>
+      <c r="K187" s="2" t="n"/>
+      <c r="L187" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M187" s="2" t="n"/>
+      <c r="N187" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-25 20:36</t>
+        </is>
+      </c>
+      <c r="O187" s="2" t="n"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>S31</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>策略切换</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>EN Replace Ordinal — 静默降级为 Fake，不输出 'Person A' / 'Company A' / 'Address 1' / 'Title 1'</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>AppLanguage=En；同 fixture 4 类 NER 实体齐全</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>1. 导入 attorney_engagement_letter.docx
+2. 三路识别
+3. 4 类 NER 实体配 Strategy::Replace { style: Ordinal }
+4. 取每个 NER 实体的 Ordinal 输出，断言形态等同 Fake（即降级生效，未输出 'Person A' 这类原始 ordinal 形态）</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>PersonName 输出含空格、不以 'Person ' 开头；OrgName 输出末尾在 EN_ORG_SUFFIXES、不以 'Company ' 开头；Address 输出含逗号、不以 'Address ' 开头；Title 输出不以 'Title ' 开头；所有输出不含汉字（即降级为 Fake 等效行为）</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>scenarios/docx/attorney_engagement_letter.docx</t>
+        </is>
+      </c>
+      <c r="H188" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I188" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J188" s="2" t="inlineStr">
+        <is>
+          <t>strategy_switching_en_replace.rs</t>
+        </is>
+      </c>
+      <c r="K188" s="2" t="n"/>
+      <c r="L188" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M188" s="2" t="n"/>
+      <c r="N188" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-25 20:36</t>
+        </is>
+      </c>
+      <c r="O188" s="2" t="n"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>K09</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>一致性替换</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>中英 counter 隔离 — 文档含中英混合 PersonName，counter 中独立计数 PersonName_zh + PersonName_en</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>AppLanguage 任意（替换走 apply_replace 内部 detect_language(text) 自动判断，不依赖 AppLanguage）；fixture mixed_bilingual.xlsx baseline 标注 4 个中文 PersonName + 4 个英文 PersonName；实际 NER 识别数依赖模型（当前 distilbert-ner 对中文识别可能为零，因此本用例的语义聚焦于'识别到的部分如何分桶'，不强求识别完整性</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>1. 导入 mixed_bilingual.xlsx
+2. 三路识别 → 8 个 PersonName items（4 中 4 英）
+3. 配 Strategy::Replace { style: Fake } 调 apply_desensitize（开启 consistent，绑定工作区以触发 counter 持久化）
+4. 读 workspace.replace_counters，检查 PersonName_zh 与 PersonName_en 分别计数</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>对 NER 识别到的每个 PersonName item：含汉字 → 进 PersonName_zh counter；纯 ASCII → 进 PersonName_en counter；两个 counter 互不串扰；PersonName_zh + PersonName_en 之和 == apply_replace 实际消费次数（即所有识别出的 unique PersonName 数）；中文 item 替换值含汉字（来自中文 fake 池）；英文 item 替换值含空格、纯 ASCII（来自英文 fake 池）；若 NER 完全识别不出某语言（如英文模型识别不到中文），对应 counter 缺失或为 0 是模型问题非 bug</t>
+        </is>
+      </c>
+      <c r="G189" s="2" t="inlineStr">
+        <is>
+          <t>scenarios/xlsx/mixed_bilingual.xlsx</t>
+        </is>
+      </c>
+      <c r="H189" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="I189" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J189" s="2" t="inlineStr">
+        <is>
+          <t>consistency_bilingual.rs</t>
+        </is>
+      </c>
+      <c r="K189" s="2" t="n"/>
+      <c r="L189" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M189" s="2" t="n"/>
+      <c r="N189" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-25 20:36</t>
+        </is>
+      </c>
+      <c r="O189" s="2" t="n"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>C81</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>核心管道</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>英文文档在 NER degraded 模式下 — regex/dict 仍能识别替换 SSN/UsPhone/Email 等正则类型</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>测试路径：Rust 集成测试（tests/*.rs），通过构造 NerEngineState(Arc::new(Mutex::new(NerEngine::degraded()))) 注入降级引擎；AppLanguage=En；fixture 含 SSN/UsPhone/Email/CreditCard/Iban；前端 Tauri command 路径无法替换 NER 引擎，本用例不能走 Playwright e2e</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>1. 用 NerEngine::degraded() 替换 NER 引擎
+2. 导入 attorney_engagement_letter.docx
+3. 三路识别 — NER 应返回空，regex/dict 应正常
+4. SSN/UsPhone/Email/CreditCard/Iban 配 Strategy::Mask 调 apply_desensitize
+5. 检查脱敏后这些类型已被 Mask（带 *）</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>ner_items.len() == 0；regex_items.len() &gt; 0（识别到至少 SSN + UsPhone + Email）；脱敏后 SSN/UsPhone/Email 等正则类型在文档中已被 Mask 替换；PersonName/OrgName 等 NER 类型因未识别故保持原文（可接受降级行为，不是 bug）</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t>scenarios/docx/attorney_engagement_letter.docx</t>
+        </is>
+      </c>
+      <c r="H190" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I190" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J190" s="2" t="inlineStr">
+        <is>
+          <t>full_pipeline_english.rs</t>
+        </is>
+      </c>
+      <c r="K190" s="2" t="n"/>
+      <c r="L190" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M190" s="2" t="n"/>
+      <c r="N190" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-25 20:36</t>
+        </is>
+      </c>
+      <c r="O190" s="2" t="n"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>B14</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>批量处理</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>批量脱敏 — 多个英文文档批处理后 NER 实体应被替换（覆盖用户报告的批量没替换 bug）</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>测试路径：Playwright e2e（e2e/tests/）— 走前端 useBatchAutoProcess Hook，更接近真实用户场景；或后端 Rust 集成测试 — 模拟批量调用 detect_by_* + apply_desensitize 串联；AppLanguage=En；NER 已加载；batch session 含 2 个英文 fixture (docx + xlsx)</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>1. 批量导入 attorney_engagement_letter.docx + law_firm_client_intake.xlsx
+2. 走 useBatchAutoProcess pipeline（regex + dict + NER 三路 + apply_desensitize）
+3. 检查每个文件的 desensitizeResult.summary.by_type
+4. 检查每个文件的 mappings 中包含 PersonName/OrgName 类型条目</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>批量结果中每个文件的 mappings 至少包含一条 PersonName 类型映射（即真的发生了 NER 替换）；脱敏后文档中所有 baseline PersonName 原文不存在；替换值符合英文 Fake 形态（含空格、纯 ASCII）；覆盖批量调用链路与单文件等价</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t>scenarios/docx/attorney_engagement_letter.docx</t>
+        </is>
+      </c>
+      <c r="H191" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I191" s="8" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J191" s="2" t="inlineStr">
+        <is>
+          <t>batch_processing.rs</t>
+        </is>
+      </c>
+      <c r="K191" s="2" t="n"/>
+      <c r="L191" s="8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M191" s="2" t="n"/>
+      <c r="N191" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-25 20:36</t>
+        </is>
+      </c>
+      <c r="O191" s="2" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:O49"/>

--- a/e2e/testcases.xlsx
+++ b/e2e/testcases.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="测试用例" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Fixture数据基线" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="覆盖率统计" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试用例" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fixture数据基线" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖率统计" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'测试用例'!$A$1:$O$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'测试用例'!$A$1:$O$195</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Fixture数据基线'!$A$1:$F$50</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -36,7 +36,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -85,6 +85,12 @@
         <bgColor rgb="00D3F9D8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -104,7 +110,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -133,6 +139,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -498,7 +508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O191"/>
+  <dimension ref="A1:O195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -13738,8 +13748,296 @@
       </c>
       <c r="O191" s="2" t="n"/>
     </row>
+    <row r="192">
+      <c r="A192" s="10" t="inlineStr">
+        <is>
+          <t>C82</t>
+        </is>
+      </c>
+      <c r="B192" s="10" t="inlineStr">
+        <is>
+          <t>核心管道</t>
+        </is>
+      </c>
+      <c r="C192" s="10" t="inlineStr">
+        <is>
+          <t>防 silent passthrough — 单文件场景跨格式回归（用户痛点 #1）</t>
+        </is>
+      </c>
+      <c r="D192" s="10" t="inlineStr">
+        <is>
+          <t>NER 模型已加载；fixture sample.* 已存在；测试路径双侧覆盖：Rust 全管线集成测 + Playwright 前端管线 mock 测</t>
+        </is>
+      </c>
+      <c r="E192" s="10" t="inlineStr">
+        <is>
+          <t>1. 解析 fixture（xlsx/csv/docx/txt）
+2. 三路识别（regex + dict + NER）
+3. apply_desensitize 走 Replace+Fake
+4. 断言: result.content 与原文不同 + summary.total &gt; 0 + mappings 非空</t>
+        </is>
+      </c>
+      <c r="F192" s="10" t="inlineStr">
+        <is>
+          <t>脱敏后 content 与原文 flatten 文本严格不等（assert_ne!）；summary.total &gt; 0 且 mappings 数 ≥ summary.total/2；识别项数达到基线（xlsx/csv ≥ 20，docx/txt ≥ 8）；任一断言失败精确报告对应原因（漏识别 / 策略 noop / 静默 passthrough）</t>
+        </is>
+      </c>
+      <c r="G192" s="10" t="inlineStr">
+        <is>
+          <t>sample.xlsx, sample.csv, sample.docx, sample.txt</t>
+        </is>
+      </c>
+      <c r="H192" s="10" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I192" s="10" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J192" s="10" t="inlineStr">
+        <is>
+          <t>regression_no_passthrough.rs + e2e/tests/test_no_silent_passthrough.py</t>
+        </is>
+      </c>
+      <c r="K192" s="10" t="inlineStr">
+        <is>
+          <t>防止「测试都过但 UI 全部都没有替换」复发；新加 fixture 时复用 assert_no_silent_passthrough helper</t>
+        </is>
+      </c>
+      <c r="L192" s="10" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M192" s="11" t="n"/>
+      <c r="N192" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-01 10:56</t>
+        </is>
+      </c>
+      <c r="O192" s="11" t="n"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="10" t="inlineStr">
+        <is>
+          <t>C83</t>
+        </is>
+      </c>
+      <c r="B193" s="10" t="inlineStr">
+        <is>
+          <t>核心管道</t>
+        </is>
+      </c>
+      <c r="C193" s="10" t="inlineStr">
+        <is>
+          <t>前端脱敏管线 IPC 调用顺序与状态机完整性</t>
+        </is>
+      </c>
+      <c r="D193" s="10" t="inlineStr">
+        <is>
+          <t>Vite dev server 已起；__E2E_IPC_OVERRIDES__ 注入完整管线 mock；__DIMKEY_STORE__ 已暴露</t>
+        </is>
+      </c>
+      <c r="E193" s="10" t="inlineStr">
+        <is>
+          <t>1. 注入完整 mock（import_file + detect_by_* + apply_desensitize + add_processing_record）
+2. reset_ipc_log
+3. 调 window.__DIMKEY_PROCESS_FILE__
+4. 等待 view 切到 comparison
+5. 读 __E2E_IPC_LOG__ 与 store state</t>
+        </is>
+      </c>
+      <c r="F193" s="10" t="inlineStr">
+        <is>
+          <t>IPC 顺序: import_file &lt; detect_by_regex &lt; apply_desensitize &lt; add_processing_record；processingStep 终态为 'done'；centerView 终态为 'comparison'；store.currentResult 不为 null；summary.total 与 mappings.length 一致</t>
+        </is>
+      </c>
+      <c r="G193" s="10" t="inlineStr">
+        <is>
+          <t>sample.txt（mock 注入内容）</t>
+        </is>
+      </c>
+      <c r="H193" s="10" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I193" s="10" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J193" s="10" t="inlineStr">
+        <is>
+          <t>e2e/tests/test_no_silent_passthrough.py</t>
+        </is>
+      </c>
+      <c r="K193" s="10" t="inlineStr">
+        <is>
+          <t>覆盖前端 hook useAutoDesensitize 的状态机正确性；与 batch_auto 形成互补（B14 走批量路径）</t>
+        </is>
+      </c>
+      <c r="L193" s="10" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M193" s="11" t="n"/>
+      <c r="N193" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-01 10:56</t>
+        </is>
+      </c>
+      <c r="O193" s="11" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="10" t="inlineStr">
+        <is>
+          <t>C84</t>
+        </is>
+      </c>
+      <c r="B194" s="10" t="inlineStr">
+        <is>
+          <t>核心管道</t>
+        </is>
+      </c>
+      <c r="C194" s="10" t="inlineStr">
+        <is>
+          <t>Meta — 反向验证 silent passthrough 能被测试体系抓到</t>
+        </is>
+      </c>
+      <c r="D194" s="10" t="inlineStr">
+        <is>
+          <t>完整管线 mock 注入；apply_desensitize 故意返回 content === 原文（「假装替换了」）</t>
+        </is>
+      </c>
+      <c r="E194" s="10" t="inlineStr">
+        <is>
+          <t>1. 注入 silent_passthrough mock（apply_desensitize 返回 content 等于原文，但 summary.total = 1）
+2. 触发 processFile
+3. 等 view 切到 comparison
+4. 调 assert_desensitization_applied(min_replacements=1)</t>
+        </is>
+      </c>
+      <c r="F194" s="10" t="inlineStr">
+        <is>
+          <t>assert_desensitization_applied 必须 raise AssertionError，错误消息包含「脱敏后内容与原文完全相同」；这是断言体系的元测试 — 防止 helper 被误改后失去抓 bug 能力</t>
+        </is>
+      </c>
+      <c r="G194" s="10" t="inlineStr">
+        <is>
+          <t>sample.txt（mock 注入伪造结果）</t>
+        </is>
+      </c>
+      <c r="H194" s="10" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I194" s="10" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J194" s="10" t="inlineStr">
+        <is>
+          <t>e2e/tests/test_no_silent_passthrough.py::test_silent_passthrough_is_caught</t>
+        </is>
+      </c>
+      <c r="K194" s="10" t="inlineStr">
+        <is>
+          <t>Meta-test：测试用来验证测试本身。一旦某次 PR 改坏了 assert_desensitization_applied，本用例会立刻失败</t>
+        </is>
+      </c>
+      <c r="L194" s="10" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M194" s="11" t="n"/>
+      <c r="N194" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-01 10:56</t>
+        </is>
+      </c>
+      <c r="O194" s="11" t="n"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="10" t="inlineStr">
+        <is>
+          <t>PK01</t>
+        </is>
+      </c>
+      <c r="B195" s="10" t="inlineStr">
+        <is>
+          <t>发版打包</t>
+        </is>
+      </c>
+      <c r="C195" s="10" t="inlineStr">
+        <is>
+          <t>macOS Bundle 资源完整性 smoke check（用户痛点 #2）</t>
+        </is>
+      </c>
+      <c r="D195" s="10" t="inlineStr">
+        <is>
+          <t>已执行 cargo tauri build；产物在 src-tauri/target/release/bundle/macos/Dimkey.app；脚本依赖 stat / hdiutil（macOS 自带）</t>
+        </is>
+      </c>
+      <c r="E195" s="10" t="inlineStr">
+        <is>
+          <t>1. 跑 ./scripts/verify-bundle.sh &lt;Dimkey.app&gt; macos
+2. 检查 4 项: ner/model.onnx ≥ 30MB; ner/tokenizer.json + id2label.json + model_config.json 全在; pdfium/libpdfium.dylib ≥ 1MB; Contents/MacOS/Dimkey 可执行
+3. release-macos.sh 自动调用 build 后 + tar.gz 解压后 + DMG 挂载后三处校验</t>
+        </is>
+      </c>
+      <c r="F195" s="10" t="inlineStr">
+        <is>
+          <t>任一资源缺失或体积异常 → exit 1 拒绝发布；脚本在 release-macos.sh 三个挂钩点都跑（避免打包过程丢失）；DMG 校验通过 hdiutil attach 临时挂载实现</t>
+        </is>
+      </c>
+      <c r="G195" s="10" t="inlineStr">
+        <is>
+          <t>n/a（校验对象为构建产物本身）</t>
+        </is>
+      </c>
+      <c r="H195" s="10" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I195" s="10" t="inlineStr">
+        <is>
+          <t>已覆盖</t>
+        </is>
+      </c>
+      <c r="J195" s="10" t="inlineStr">
+        <is>
+          <t>scripts/verify-bundle.sh + scripts/release-macos.sh</t>
+        </is>
+      </c>
+      <c r="K195" s="10" t="inlineStr">
+        <is>
+          <t>首次跑就抓到当前 src-tauri/resources/pdfium/ 只有 .gitkeep 的真实 bug；防止「打包后模型文件都没带」复发</t>
+        </is>
+      </c>
+      <c r="L195" s="10" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="M195" s="11" t="n"/>
+      <c r="N195" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-01 10:56</t>
+        </is>
+      </c>
+      <c r="O195" s="11" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O49"/>
+  <autoFilter ref="A1:O195"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -54200,7 +54498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -54246,272 +54544,296 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>核心管道</t>
+          <t>UI交互</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D2" s="2" t="n">
-        <v>4</v>
-      </c>
       <c r="E2" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>4/9 (部分)</t>
+          <t>5/6</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>策略切换</t>
+          <t>一致性替换</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>7/9</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>类型过滤</t>
+          <t>列级规则</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C4" s="2" t="n">
         <v>4</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>4/6</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>字典/白名单</t>
+          <t>发版打包</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>1/1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>列级规则</t>
+          <t>字典/白名单</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>10/10</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>一致性替换</t>
+          <t>工作区管理</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>5/6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>还原</t>
+          <t>批量处理</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C8" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="E8" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1/4 (部分)</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>批量处理</t>
+          <t>核心管道</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>4</v>
+        <v>84</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>84/84</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>工作区管理</t>
+          <t>策略切换</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="C10" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="D10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="E10" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1/5 (部分)</t>
+          <t>31/31</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>UI交互</t>
+          <t>类型过滤</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>21/21</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr"/>
-      <c r="B12" s="2" t="inlineStr"/>
-      <c r="C12" s="2" t="inlineStr"/>
-      <c r="D12" s="2" t="inlineStr"/>
-      <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="2" t="inlineStr"/>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>还原</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>6/6</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="2" t="n"/>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="2" t="n"/>
+      <c r="F13" s="2" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>7/48 (14.6%)</t>
+      <c r="B14" t="n">
+        <v>194</v>
+      </c>
+      <c r="C14" t="n">
+        <v>186</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>8</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>186/194 (95.9%)</t>
         </is>
       </c>
     </row>
